--- a/observations-summary.xlsx
+++ b/observations-summary.xlsx
@@ -12,7 +12,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2827" uniqueCount="88">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2838" uniqueCount="113">
   <si>
     <t>Profile</t>
   </si>
@@ -200,12 +200,51 @@
     <t>Ophthalmic OCT Macula</t>
   </si>
   <si>
+    <t>LOINC#57119-0</t>
+  </si>
+  <si>
+    <t>LOINC#57109-1</t>
+  </si>
+  <si>
+    <t>LOINC#57108-3</t>
+  </si>
+  <si>
+    <t>LOINC#57110-9</t>
+  </si>
+  <si>
+    <t>LOINC#57111-7</t>
+  </si>
+  <si>
+    <t>LOINC#57112-5</t>
+  </si>
+  <si>
+    <t>LOINC#57113-3</t>
+  </si>
+  <si>
+    <t>LOINC#57114-1</t>
+  </si>
+  <si>
+    <t>LOINC#57115-8</t>
+  </si>
+  <si>
+    <t>LOINC#57116-6</t>
+  </si>
+  <si>
+    <t>LOINC#57117-4</t>
+  </si>
+  <si>
+    <t>LOINC#57118-2</t>
+  </si>
+  <si>
     <t>ophthalmic-oct-rnfl</t>
   </si>
   <si>
     <t>Ophthalmic OCT RNFL</t>
   </si>
   <si>
+    <t>LOINC#86291-2</t>
+  </si>
+  <si>
     <t>integer</t>
   </si>
   <si>
@@ -221,13 +260,49 @@
     <t>Ophthalmic Specular Microscopy</t>
   </si>
   <si>
+    <t>LOINC#100086-8</t>
+  </si>
+  <si>
+    <t>LOINC#100070-2</t>
+  </si>
+  <si>
+    <t>LOINC#100076-9</t>
+  </si>
+  <si>
+    <t>LOINC#100072-8</t>
+  </si>
+  <si>
+    <t>LOINC#100074-4</t>
+  </si>
+  <si>
+    <t>LOINC#79825-6</t>
+  </si>
+  <si>
+    <t>LOINC#100078-5</t>
+  </si>
+  <si>
+    <t>LOINC#100080-1</t>
+  </si>
+  <si>
+    <t>LOINC#100082-7</t>
+  </si>
+  <si>
+    <t>LOINC#100084-3</t>
+  </si>
+  <si>
     <t>ophthalmic-visual-acuity</t>
   </si>
   <si>
     <t>Ophthalmic Visual Acuity</t>
   </si>
   <si>
+    <t>LOINC#98497-1</t>
+  </si>
+  <si>
     <t>Quantityĵ, CodeableConceptĵ, Ratioĵ</t>
+  </si>
+  <si>
+    <t>LOINC#79908-0</t>
   </si>
   <si>
     <t>boolean</t>
@@ -409,7 +484,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <dimension ref="A1:K257"/>
+  <dimension ref="A1:K258"/>
   <sheetFormatPr defaultRowHeight="15.0"/>
   <sheetData>
     <row r="1">
@@ -5746,10 +5821,10 @@
         <v>14</v>
       </c>
       <c r="E153" t="s" s="2">
-        <v>14</v>
+        <v>62</v>
       </c>
       <c r="F153" t="s" s="2">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="G153" t="s" s="2">
         <v>21</v>
@@ -5781,7 +5856,7 @@
         <v>14</v>
       </c>
       <c r="E154" t="s" s="2">
-        <v>14</v>
+        <v>63</v>
       </c>
       <c r="F154" t="s" s="2">
         <v>14</v>
@@ -5816,7 +5891,7 @@
         <v>14</v>
       </c>
       <c r="E155" t="s" s="2">
-        <v>14</v>
+        <v>64</v>
       </c>
       <c r="F155" t="s" s="2">
         <v>14</v>
@@ -5921,7 +5996,7 @@
         <v>14</v>
       </c>
       <c r="E158" t="s" s="2">
-        <v>14</v>
+        <v>65</v>
       </c>
       <c r="F158" t="s" s="2">
         <v>14</v>
@@ -5956,7 +6031,7 @@
         <v>14</v>
       </c>
       <c r="E159" t="s" s="2">
-        <v>14</v>
+        <v>66</v>
       </c>
       <c r="F159" t="s" s="2">
         <v>14</v>
@@ -5991,7 +6066,7 @@
         <v>14</v>
       </c>
       <c r="E160" t="s" s="2">
-        <v>14</v>
+        <v>67</v>
       </c>
       <c r="F160" t="s" s="2">
         <v>14</v>
@@ -6026,7 +6101,7 @@
         <v>14</v>
       </c>
       <c r="E161" t="s" s="2">
-        <v>14</v>
+        <v>68</v>
       </c>
       <c r="F161" t="s" s="2">
         <v>14</v>
@@ -6061,7 +6136,7 @@
         <v>14</v>
       </c>
       <c r="E162" t="s" s="2">
-        <v>14</v>
+        <v>69</v>
       </c>
       <c r="F162" t="s" s="2">
         <v>14</v>
@@ -6096,7 +6171,7 @@
         <v>14</v>
       </c>
       <c r="E163" t="s" s="2">
-        <v>14</v>
+        <v>70</v>
       </c>
       <c r="F163" t="s" s="2">
         <v>14</v>
@@ -6131,7 +6206,7 @@
         <v>14</v>
       </c>
       <c r="E164" t="s" s="2">
-        <v>14</v>
+        <v>71</v>
       </c>
       <c r="F164" t="s" s="2">
         <v>14</v>
@@ -6166,7 +6241,7 @@
         <v>14</v>
       </c>
       <c r="E165" t="s" s="2">
-        <v>14</v>
+        <v>72</v>
       </c>
       <c r="F165" t="s" s="2">
         <v>14</v>
@@ -6201,7 +6276,7 @@
         <v>14</v>
       </c>
       <c r="E166" t="s" s="2">
-        <v>14</v>
+        <v>73</v>
       </c>
       <c r="F166" t="s" s="2">
         <v>14</v>
@@ -6539,10 +6614,10 @@
     </row>
     <row r="176">
       <c r="A176" t="s" s="2">
-        <v>62</v>
+        <v>74</v>
       </c>
       <c r="B176" t="s" s="2">
-        <v>63</v>
+        <v>75</v>
       </c>
       <c r="C176" t="s" s="2">
         <v>13</v>
@@ -6551,10 +6626,10 @@
         <v>14</v>
       </c>
       <c r="E176" t="s" s="2">
-        <v>14</v>
+        <v>76</v>
       </c>
       <c r="F176" t="s" s="2">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="G176" t="s" s="2">
         <v>21</v>
@@ -6577,7 +6652,7 @@
         <v>14</v>
       </c>
       <c r="B177" t="s" s="2">
-        <v>63</v>
+        <v>75</v>
       </c>
       <c r="C177" t="s" s="2">
         <v>14</v>
@@ -6612,7 +6687,7 @@
         <v>14</v>
       </c>
       <c r="B178" t="s" s="2">
-        <v>63</v>
+        <v>75</v>
       </c>
       <c r="C178" t="s" s="2">
         <v>14</v>
@@ -6647,7 +6722,7 @@
         <v>14</v>
       </c>
       <c r="B179" t="s" s="2">
-        <v>63</v>
+        <v>75</v>
       </c>
       <c r="C179" t="s" s="2">
         <v>14</v>
@@ -6682,7 +6757,7 @@
         <v>14</v>
       </c>
       <c r="B180" t="s" s="2">
-        <v>63</v>
+        <v>75</v>
       </c>
       <c r="C180" t="s" s="2">
         <v>14</v>
@@ -6717,7 +6792,7 @@
         <v>14</v>
       </c>
       <c r="B181" t="s" s="2">
-        <v>63</v>
+        <v>75</v>
       </c>
       <c r="C181" t="s" s="2">
         <v>14</v>
@@ -6752,7 +6827,7 @@
         <v>14</v>
       </c>
       <c r="B182" t="s" s="2">
-        <v>63</v>
+        <v>75</v>
       </c>
       <c r="C182" t="s" s="2">
         <v>14</v>
@@ -6787,7 +6862,7 @@
         <v>14</v>
       </c>
       <c r="B183" t="s" s="2">
-        <v>63</v>
+        <v>75</v>
       </c>
       <c r="C183" t="s" s="2">
         <v>14</v>
@@ -6822,7 +6897,7 @@
         <v>14</v>
       </c>
       <c r="B184" t="s" s="2">
-        <v>63</v>
+        <v>75</v>
       </c>
       <c r="C184" t="s" s="2">
         <v>14</v>
@@ -6857,7 +6932,7 @@
         <v>14</v>
       </c>
       <c r="B185" t="s" s="2">
-        <v>63</v>
+        <v>75</v>
       </c>
       <c r="C185" t="s" s="2">
         <v>14</v>
@@ -6892,7 +6967,7 @@
         <v>14</v>
       </c>
       <c r="B186" t="s" s="2">
-        <v>63</v>
+        <v>75</v>
       </c>
       <c r="C186" t="s" s="2">
         <v>14</v>
@@ -6927,7 +7002,7 @@
         <v>14</v>
       </c>
       <c r="B187" t="s" s="2">
-        <v>63</v>
+        <v>75</v>
       </c>
       <c r="C187" t="s" s="2">
         <v>14</v>
@@ -6962,7 +7037,7 @@
         <v>14</v>
       </c>
       <c r="B188" t="s" s="2">
-        <v>63</v>
+        <v>75</v>
       </c>
       <c r="C188" t="s" s="2">
         <v>14</v>
@@ -6997,7 +7072,7 @@
         <v>14</v>
       </c>
       <c r="B189" t="s" s="2">
-        <v>63</v>
+        <v>75</v>
       </c>
       <c r="C189" t="s" s="2">
         <v>14</v>
@@ -7032,7 +7107,7 @@
         <v>14</v>
       </c>
       <c r="B190" t="s" s="2">
-        <v>63</v>
+        <v>75</v>
       </c>
       <c r="C190" t="s" s="2">
         <v>14</v>
@@ -7067,7 +7142,7 @@
         <v>14</v>
       </c>
       <c r="B191" t="s" s="2">
-        <v>63</v>
+        <v>75</v>
       </c>
       <c r="C191" t="s" s="2">
         <v>14</v>
@@ -7102,7 +7177,7 @@
         <v>14</v>
       </c>
       <c r="B192" t="s" s="2">
-        <v>63</v>
+        <v>75</v>
       </c>
       <c r="C192" t="s" s="2">
         <v>14</v>
@@ -7137,7 +7212,7 @@
         <v>14</v>
       </c>
       <c r="B193" t="s" s="2">
-        <v>63</v>
+        <v>75</v>
       </c>
       <c r="C193" t="s" s="2">
         <v>14</v>
@@ -7172,7 +7247,7 @@
         <v>14</v>
       </c>
       <c r="B194" t="s" s="2">
-        <v>63</v>
+        <v>75</v>
       </c>
       <c r="C194" t="s" s="2">
         <v>14</v>
@@ -7190,7 +7265,7 @@
         <v>14</v>
       </c>
       <c r="H194" t="s" s="2">
-        <v>64</v>
+        <v>77</v>
       </c>
       <c r="I194" t="s" s="2">
         <v>18</v>
@@ -7207,7 +7282,7 @@
         <v>14</v>
       </c>
       <c r="B195" t="s" s="2">
-        <v>63</v>
+        <v>75</v>
       </c>
       <c r="C195" t="s" s="2">
         <v>14</v>
@@ -7242,7 +7317,7 @@
         <v>14</v>
       </c>
       <c r="B196" t="s" s="2">
-        <v>63</v>
+        <v>75</v>
       </c>
       <c r="C196" t="s" s="2">
         <v>14</v>
@@ -7277,7 +7352,7 @@
         <v>14</v>
       </c>
       <c r="B197" t="s" s="2">
-        <v>63</v>
+        <v>75</v>
       </c>
       <c r="C197" t="s" s="2">
         <v>14</v>
@@ -7312,7 +7387,7 @@
         <v>14</v>
       </c>
       <c r="B198" t="s" s="2">
-        <v>63</v>
+        <v>75</v>
       </c>
       <c r="C198" t="s" s="2">
         <v>14</v>
@@ -7347,7 +7422,7 @@
         <v>14</v>
       </c>
       <c r="B199" t="s" s="2">
-        <v>63</v>
+        <v>75</v>
       </c>
       <c r="C199" t="s" s="2">
         <v>14</v>
@@ -7382,7 +7457,7 @@
         <v>14</v>
       </c>
       <c r="B200" t="s" s="2">
-        <v>63</v>
+        <v>75</v>
       </c>
       <c r="C200" t="s" s="2">
         <v>14</v>
@@ -7417,7 +7492,7 @@
         <v>14</v>
       </c>
       <c r="B201" t="s" s="2">
-        <v>63</v>
+        <v>75</v>
       </c>
       <c r="C201" t="s" s="2">
         <v>14</v>
@@ -7449,10 +7524,10 @@
     </row>
     <row r="202">
       <c r="A202" t="s" s="2">
-        <v>65</v>
+        <v>78</v>
       </c>
       <c r="B202" t="s" s="2">
-        <v>66</v>
+        <v>79</v>
       </c>
       <c r="C202" t="s" s="2">
         <v>13</v>
@@ -7487,7 +7562,7 @@
         <v>14</v>
       </c>
       <c r="B203" t="s" s="2">
-        <v>66</v>
+        <v>79</v>
       </c>
       <c r="C203" t="s" s="2">
         <v>14</v>
@@ -7522,7 +7597,7 @@
         <v>14</v>
       </c>
       <c r="B204" t="s" s="2">
-        <v>66</v>
+        <v>79</v>
       </c>
       <c r="C204" t="s" s="2">
         <v>14</v>
@@ -7557,7 +7632,7 @@
         <v>14</v>
       </c>
       <c r="B205" t="s" s="2">
-        <v>66</v>
+        <v>79</v>
       </c>
       <c r="C205" t="s" s="2">
         <v>14</v>
@@ -7592,7 +7667,7 @@
         <v>14</v>
       </c>
       <c r="B206" t="s" s="2">
-        <v>66</v>
+        <v>79</v>
       </c>
       <c r="C206" t="s" s="2">
         <v>14</v>
@@ -7627,7 +7702,7 @@
         <v>14</v>
       </c>
       <c r="B207" t="s" s="2">
-        <v>66</v>
+        <v>79</v>
       </c>
       <c r="C207" t="s" s="2">
         <v>14</v>
@@ -7662,7 +7737,7 @@
         <v>14</v>
       </c>
       <c r="B208" t="s" s="2">
-        <v>66</v>
+        <v>79</v>
       </c>
       <c r="C208" t="s" s="2">
         <v>14</v>
@@ -7697,7 +7772,7 @@
         <v>14</v>
       </c>
       <c r="B209" t="s" s="2">
-        <v>66</v>
+        <v>79</v>
       </c>
       <c r="C209" t="s" s="2">
         <v>14</v>
@@ -7732,7 +7807,7 @@
         <v>14</v>
       </c>
       <c r="B210" t="s" s="2">
-        <v>66</v>
+        <v>79</v>
       </c>
       <c r="C210" t="s" s="2">
         <v>14</v>
@@ -7767,7 +7842,7 @@
         <v>14</v>
       </c>
       <c r="B211" t="s" s="2">
-        <v>66</v>
+        <v>79</v>
       </c>
       <c r="C211" t="s" s="2">
         <v>14</v>
@@ -7802,7 +7877,7 @@
         <v>14</v>
       </c>
       <c r="B212" t="s" s="2">
-        <v>66</v>
+        <v>79</v>
       </c>
       <c r="C212" t="s" s="2">
         <v>14</v>
@@ -7837,7 +7912,7 @@
         <v>14</v>
       </c>
       <c r="B213" t="s" s="2">
-        <v>66</v>
+        <v>79</v>
       </c>
       <c r="C213" t="s" s="2">
         <v>14</v>
@@ -7872,7 +7947,7 @@
         <v>14</v>
       </c>
       <c r="B214" t="s" s="2">
-        <v>66</v>
+        <v>79</v>
       </c>
       <c r="C214" t="s" s="2">
         <v>14</v>
@@ -7907,7 +7982,7 @@
         <v>14</v>
       </c>
       <c r="B215" t="s" s="2">
-        <v>66</v>
+        <v>79</v>
       </c>
       <c r="C215" t="s" s="2">
         <v>14</v>
@@ -7942,7 +8017,7 @@
         <v>14</v>
       </c>
       <c r="B216" t="s" s="2">
-        <v>66</v>
+        <v>79</v>
       </c>
       <c r="C216" t="s" s="2">
         <v>14</v>
@@ -7977,7 +8052,7 @@
         <v>14</v>
       </c>
       <c r="B217" t="s" s="2">
-        <v>66</v>
+        <v>79</v>
       </c>
       <c r="C217" t="s" s="2">
         <v>14</v>
@@ -8012,7 +8087,7 @@
         <v>14</v>
       </c>
       <c r="B218" t="s" s="2">
-        <v>66</v>
+        <v>79</v>
       </c>
       <c r="C218" t="s" s="2">
         <v>14</v>
@@ -8047,7 +8122,7 @@
         <v>14</v>
       </c>
       <c r="B219" t="s" s="2">
-        <v>66</v>
+        <v>79</v>
       </c>
       <c r="C219" t="s" s="2">
         <v>14</v>
@@ -8082,7 +8157,7 @@
         <v>14</v>
       </c>
       <c r="B220" t="s" s="2">
-        <v>66</v>
+        <v>79</v>
       </c>
       <c r="C220" t="s" s="2">
         <v>14</v>
@@ -8117,7 +8192,7 @@
         <v>14</v>
       </c>
       <c r="B221" t="s" s="2">
-        <v>66</v>
+        <v>79</v>
       </c>
       <c r="C221" t="s" s="2">
         <v>14</v>
@@ -8152,7 +8227,7 @@
         <v>14</v>
       </c>
       <c r="B222" t="s" s="2">
-        <v>66</v>
+        <v>79</v>
       </c>
       <c r="C222" t="s" s="2">
         <v>14</v>
@@ -8187,7 +8262,7 @@
         <v>14</v>
       </c>
       <c r="B223" t="s" s="2">
-        <v>66</v>
+        <v>79</v>
       </c>
       <c r="C223" t="s" s="2">
         <v>14</v>
@@ -8222,7 +8297,7 @@
         <v>14</v>
       </c>
       <c r="B224" t="s" s="2">
-        <v>66</v>
+        <v>79</v>
       </c>
       <c r="C224" t="s" s="2">
         <v>14</v>
@@ -8257,7 +8332,7 @@
         <v>14</v>
       </c>
       <c r="B225" t="s" s="2">
-        <v>66</v>
+        <v>79</v>
       </c>
       <c r="C225" t="s" s="2">
         <v>14</v>
@@ -8292,7 +8367,7 @@
         <v>14</v>
       </c>
       <c r="B226" t="s" s="2">
-        <v>66</v>
+        <v>79</v>
       </c>
       <c r="C226" t="s" s="2">
         <v>14</v>
@@ -8327,7 +8402,7 @@
         <v>14</v>
       </c>
       <c r="B227" t="s" s="2">
-        <v>66</v>
+        <v>79</v>
       </c>
       <c r="C227" t="s" s="2">
         <v>14</v>
@@ -8359,10 +8434,10 @@
     </row>
     <row r="228">
       <c r="A228" t="s" s="2">
-        <v>67</v>
+        <v>80</v>
       </c>
       <c r="B228" t="s" s="2">
-        <v>68</v>
+        <v>81</v>
       </c>
       <c r="C228" t="s" s="2">
         <v>13</v>
@@ -8397,7 +8472,7 @@
         <v>14</v>
       </c>
       <c r="B229" t="s" s="2">
-        <v>68</v>
+        <v>81</v>
       </c>
       <c r="C229" t="s" s="2">
         <v>14</v>
@@ -8432,7 +8507,7 @@
         <v>14</v>
       </c>
       <c r="B230" t="s" s="2">
-        <v>68</v>
+        <v>81</v>
       </c>
       <c r="C230" t="s" s="2">
         <v>14</v>
@@ -8441,7 +8516,7 @@
         <v>14</v>
       </c>
       <c r="E230" t="s" s="2">
-        <v>14</v>
+        <v>82</v>
       </c>
       <c r="F230" t="s" s="2">
         <v>14</v>
@@ -8450,7 +8525,7 @@
         <v>14</v>
       </c>
       <c r="H230" t="s" s="2">
-        <v>30</v>
+        <v>26</v>
       </c>
       <c r="I230" t="s" s="2">
         <v>18</v>
@@ -8467,7 +8542,7 @@
         <v>14</v>
       </c>
       <c r="B231" t="s" s="2">
-        <v>68</v>
+        <v>81</v>
       </c>
       <c r="C231" t="s" s="2">
         <v>14</v>
@@ -8476,7 +8551,7 @@
         <v>14</v>
       </c>
       <c r="E231" t="s" s="2">
-        <v>14</v>
+        <v>83</v>
       </c>
       <c r="F231" t="s" s="2">
         <v>14</v>
@@ -8502,7 +8577,7 @@
         <v>14</v>
       </c>
       <c r="B232" t="s" s="2">
-        <v>68</v>
+        <v>81</v>
       </c>
       <c r="C232" t="s" s="2">
         <v>14</v>
@@ -8511,7 +8586,7 @@
         <v>14</v>
       </c>
       <c r="E232" t="s" s="2">
-        <v>14</v>
+        <v>84</v>
       </c>
       <c r="F232" t="s" s="2">
         <v>14</v>
@@ -8537,7 +8612,7 @@
         <v>14</v>
       </c>
       <c r="B233" t="s" s="2">
-        <v>68</v>
+        <v>81</v>
       </c>
       <c r="C233" t="s" s="2">
         <v>14</v>
@@ -8546,7 +8621,7 @@
         <v>14</v>
       </c>
       <c r="E233" t="s" s="2">
-        <v>14</v>
+        <v>85</v>
       </c>
       <c r="F233" t="s" s="2">
         <v>14</v>
@@ -8572,7 +8647,7 @@
         <v>14</v>
       </c>
       <c r="B234" t="s" s="2">
-        <v>68</v>
+        <v>81</v>
       </c>
       <c r="C234" t="s" s="2">
         <v>14</v>
@@ -8581,7 +8656,7 @@
         <v>14</v>
       </c>
       <c r="E234" t="s" s="2">
-        <v>14</v>
+        <v>86</v>
       </c>
       <c r="F234" t="s" s="2">
         <v>14</v>
@@ -8607,7 +8682,7 @@
         <v>14</v>
       </c>
       <c r="B235" t="s" s="2">
-        <v>68</v>
+        <v>81</v>
       </c>
       <c r="C235" t="s" s="2">
         <v>14</v>
@@ -8616,7 +8691,7 @@
         <v>14</v>
       </c>
       <c r="E235" t="s" s="2">
-        <v>14</v>
+        <v>87</v>
       </c>
       <c r="F235" t="s" s="2">
         <v>14</v>
@@ -8642,7 +8717,7 @@
         <v>14</v>
       </c>
       <c r="B236" t="s" s="2">
-        <v>68</v>
+        <v>81</v>
       </c>
       <c r="C236" t="s" s="2">
         <v>14</v>
@@ -8651,7 +8726,7 @@
         <v>14</v>
       </c>
       <c r="E236" t="s" s="2">
-        <v>14</v>
+        <v>88</v>
       </c>
       <c r="F236" t="s" s="2">
         <v>14</v>
@@ -8677,7 +8752,7 @@
         <v>14</v>
       </c>
       <c r="B237" t="s" s="2">
-        <v>68</v>
+        <v>81</v>
       </c>
       <c r="C237" t="s" s="2">
         <v>14</v>
@@ -8686,7 +8761,7 @@
         <v>14</v>
       </c>
       <c r="E237" t="s" s="2">
-        <v>14</v>
+        <v>89</v>
       </c>
       <c r="F237" t="s" s="2">
         <v>14</v>
@@ -8712,7 +8787,7 @@
         <v>14</v>
       </c>
       <c r="B238" t="s" s="2">
-        <v>68</v>
+        <v>81</v>
       </c>
       <c r="C238" t="s" s="2">
         <v>14</v>
@@ -8721,7 +8796,7 @@
         <v>14</v>
       </c>
       <c r="E238" t="s" s="2">
-        <v>14</v>
+        <v>90</v>
       </c>
       <c r="F238" t="s" s="2">
         <v>14</v>
@@ -8744,28 +8819,28 @@
     </row>
     <row r="239">
       <c r="A239" t="s" s="2">
-        <v>69</v>
+        <v>14</v>
       </c>
       <c r="B239" t="s" s="2">
-        <v>70</v>
+        <v>81</v>
       </c>
       <c r="C239" t="s" s="2">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="D239" t="s" s="2">
         <v>14</v>
       </c>
       <c r="E239" t="s" s="2">
-        <v>14</v>
+        <v>91</v>
       </c>
       <c r="F239" t="s" s="2">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="G239" t="s" s="2">
-        <v>21</v>
+        <v>14</v>
       </c>
       <c r="H239" t="s" s="2">
-        <v>71</v>
+        <v>30</v>
       </c>
       <c r="I239" t="s" s="2">
         <v>18</v>
@@ -8779,28 +8854,28 @@
     </row>
     <row r="240">
       <c r="A240" t="s" s="2">
-        <v>14</v>
+        <v>92</v>
       </c>
       <c r="B240" t="s" s="2">
-        <v>70</v>
+        <v>93</v>
       </c>
       <c r="C240" t="s" s="2">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="D240" t="s" s="2">
         <v>14</v>
       </c>
       <c r="E240" t="s" s="2">
-        <v>14</v>
+        <v>94</v>
       </c>
       <c r="F240" t="s" s="2">
         <v>14</v>
       </c>
       <c r="G240" t="s" s="2">
-        <v>14</v>
+        <v>21</v>
       </c>
       <c r="H240" t="s" s="2">
-        <v>30</v>
+        <v>95</v>
       </c>
       <c r="I240" t="s" s="2">
         <v>18</v>
@@ -8817,7 +8892,7 @@
         <v>14</v>
       </c>
       <c r="B241" t="s" s="2">
-        <v>70</v>
+        <v>93</v>
       </c>
       <c r="C241" t="s" s="2">
         <v>14</v>
@@ -8835,7 +8910,7 @@
         <v>14</v>
       </c>
       <c r="H241" t="s" s="2">
-        <v>26</v>
+        <v>30</v>
       </c>
       <c r="I241" t="s" s="2">
         <v>18</v>
@@ -8852,7 +8927,7 @@
         <v>14</v>
       </c>
       <c r="B242" t="s" s="2">
-        <v>70</v>
+        <v>93</v>
       </c>
       <c r="C242" t="s" s="2">
         <v>14</v>
@@ -8887,7 +8962,7 @@
         <v>14</v>
       </c>
       <c r="B243" t="s" s="2">
-        <v>70</v>
+        <v>93</v>
       </c>
       <c r="C243" t="s" s="2">
         <v>14</v>
@@ -8896,7 +8971,7 @@
         <v>14</v>
       </c>
       <c r="E243" t="s" s="2">
-        <v>14</v>
+        <v>96</v>
       </c>
       <c r="F243" t="s" s="2">
         <v>14</v>
@@ -8922,7 +8997,7 @@
         <v>14</v>
       </c>
       <c r="B244" t="s" s="2">
-        <v>70</v>
+        <v>93</v>
       </c>
       <c r="C244" t="s" s="2">
         <v>14</v>
@@ -8940,7 +9015,7 @@
         <v>14</v>
       </c>
       <c r="H244" t="s" s="2">
-        <v>72</v>
+        <v>26</v>
       </c>
       <c r="I244" t="s" s="2">
         <v>18</v>
@@ -8954,13 +9029,13 @@
     </row>
     <row r="245">
       <c r="A245" t="s" s="2">
-        <v>73</v>
+        <v>14</v>
       </c>
       <c r="B245" t="s" s="2">
-        <v>74</v>
+        <v>93</v>
       </c>
       <c r="C245" t="s" s="2">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="D245" t="s" s="2">
         <v>14</v>
@@ -8969,13 +9044,13 @@
         <v>14</v>
       </c>
       <c r="F245" t="s" s="2">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="G245" t="s" s="2">
-        <v>21</v>
+        <v>14</v>
       </c>
       <c r="H245" t="s" s="2">
-        <v>22</v>
+        <v>97</v>
       </c>
       <c r="I245" t="s" s="2">
         <v>18</v>
@@ -8989,10 +9064,10 @@
     </row>
     <row r="246">
       <c r="A246" t="s" s="2">
-        <v>75</v>
+        <v>98</v>
       </c>
       <c r="B246" t="s" s="2">
-        <v>76</v>
+        <v>99</v>
       </c>
       <c r="C246" t="s" s="2">
         <v>13</v>
@@ -9001,16 +9076,16 @@
         <v>14</v>
       </c>
       <c r="E246" t="s" s="2">
-        <v>14</v>
+        <v>87</v>
       </c>
       <c r="F246" t="s" s="2">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="G246" t="s" s="2">
-        <v>16</v>
+        <v>21</v>
       </c>
       <c r="H246" t="s" s="2">
-        <v>14</v>
+        <v>22</v>
       </c>
       <c r="I246" t="s" s="2">
         <v>18</v>
@@ -9024,13 +9099,13 @@
     </row>
     <row r="247">
       <c r="A247" t="s" s="2">
-        <v>14</v>
+        <v>100</v>
       </c>
       <c r="B247" t="s" s="2">
-        <v>76</v>
+        <v>101</v>
       </c>
       <c r="C247" t="s" s="2">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="D247" t="s" s="2">
         <v>14</v>
@@ -9039,13 +9114,13 @@
         <v>14</v>
       </c>
       <c r="F247" t="s" s="2">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="G247" t="s" s="2">
-        <v>14</v>
+        <v>16</v>
       </c>
       <c r="H247" t="s" s="2">
-        <v>26</v>
+        <v>14</v>
       </c>
       <c r="I247" t="s" s="2">
         <v>18</v>
@@ -9062,7 +9137,7 @@
         <v>14</v>
       </c>
       <c r="B248" t="s" s="2">
-        <v>76</v>
+        <v>101</v>
       </c>
       <c r="C248" t="s" s="2">
         <v>14</v>
@@ -9094,13 +9169,13 @@
     </row>
     <row r="249">
       <c r="A249" t="s" s="2">
-        <v>77</v>
+        <v>14</v>
       </c>
       <c r="B249" t="s" s="2">
-        <v>78</v>
+        <v>101</v>
       </c>
       <c r="C249" t="s" s="2">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="D249" t="s" s="2">
         <v>14</v>
@@ -9109,13 +9184,13 @@
         <v>14</v>
       </c>
       <c r="F249" t="s" s="2">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="G249" t="s" s="2">
-        <v>16</v>
+        <v>14</v>
       </c>
       <c r="H249" t="s" s="2">
-        <v>14</v>
+        <v>26</v>
       </c>
       <c r="I249" t="s" s="2">
         <v>18</v>
@@ -9129,13 +9204,13 @@
     </row>
     <row r="250">
       <c r="A250" t="s" s="2">
-        <v>14</v>
+        <v>102</v>
       </c>
       <c r="B250" t="s" s="2">
-        <v>78</v>
+        <v>103</v>
       </c>
       <c r="C250" t="s" s="2">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="D250" t="s" s="2">
         <v>14</v>
@@ -9144,13 +9219,13 @@
         <v>14</v>
       </c>
       <c r="F250" t="s" s="2">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="G250" t="s" s="2">
-        <v>14</v>
+        <v>16</v>
       </c>
       <c r="H250" t="s" s="2">
-        <v>26</v>
+        <v>14</v>
       </c>
       <c r="I250" t="s" s="2">
         <v>18</v>
@@ -9167,7 +9242,7 @@
         <v>14</v>
       </c>
       <c r="B251" t="s" s="2">
-        <v>78</v>
+        <v>103</v>
       </c>
       <c r="C251" t="s" s="2">
         <v>14</v>
@@ -9199,13 +9274,13 @@
     </row>
     <row r="252">
       <c r="A252" t="s" s="2">
-        <v>79</v>
+        <v>14</v>
       </c>
       <c r="B252" t="s" s="2">
-        <v>80</v>
+        <v>103</v>
       </c>
       <c r="C252" t="s" s="2">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="D252" t="s" s="2">
         <v>14</v>
@@ -9214,13 +9289,13 @@
         <v>14</v>
       </c>
       <c r="F252" t="s" s="2">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="G252" t="s" s="2">
-        <v>16</v>
+        <v>14</v>
       </c>
       <c r="H252" t="s" s="2">
-        <v>55</v>
+        <v>26</v>
       </c>
       <c r="I252" t="s" s="2">
         <v>18</v>
@@ -9234,13 +9309,13 @@
     </row>
     <row r="253">
       <c r="A253" t="s" s="2">
-        <v>14</v>
+        <v>104</v>
       </c>
       <c r="B253" t="s" s="2">
-        <v>80</v>
+        <v>105</v>
       </c>
       <c r="C253" t="s" s="2">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="D253" t="s" s="2">
         <v>14</v>
@@ -9249,13 +9324,13 @@
         <v>14</v>
       </c>
       <c r="F253" t="s" s="2">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="G253" t="s" s="2">
-        <v>14</v>
+        <v>16</v>
       </c>
       <c r="H253" t="s" s="2">
-        <v>26</v>
+        <v>55</v>
       </c>
       <c r="I253" t="s" s="2">
         <v>18</v>
@@ -9269,13 +9344,13 @@
     </row>
     <row r="254">
       <c r="A254" t="s" s="2">
-        <v>81</v>
+        <v>14</v>
       </c>
       <c r="B254" t="s" s="2">
-        <v>82</v>
+        <v>105</v>
       </c>
       <c r="C254" t="s" s="2">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="D254" t="s" s="2">
         <v>14</v>
@@ -9284,13 +9359,13 @@
         <v>14</v>
       </c>
       <c r="F254" t="s" s="2">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="G254" t="s" s="2">
-        <v>21</v>
+        <v>14</v>
       </c>
       <c r="H254" t="s" s="2">
-        <v>14</v>
+        <v>26</v>
       </c>
       <c r="I254" t="s" s="2">
         <v>18</v>
@@ -9304,10 +9379,10 @@
     </row>
     <row r="255">
       <c r="A255" t="s" s="2">
-        <v>83</v>
+        <v>106</v>
       </c>
       <c r="B255" t="s" s="2">
-        <v>84</v>
+        <v>107</v>
       </c>
       <c r="C255" t="s" s="2">
         <v>13</v>
@@ -9322,7 +9397,7 @@
         <v>15</v>
       </c>
       <c r="G255" t="s" s="2">
-        <v>85</v>
+        <v>21</v>
       </c>
       <c r="H255" t="s" s="2">
         <v>14</v>
@@ -9339,10 +9414,10 @@
     </row>
     <row r="256">
       <c r="A256" t="s" s="2">
-        <v>86</v>
+        <v>108</v>
       </c>
       <c r="B256" t="s" s="2">
-        <v>87</v>
+        <v>109</v>
       </c>
       <c r="C256" t="s" s="2">
         <v>13</v>
@@ -9357,7 +9432,7 @@
         <v>15</v>
       </c>
       <c r="G256" t="s" s="2">
-        <v>16</v>
+        <v>110</v>
       </c>
       <c r="H256" t="s" s="2">
         <v>14</v>
@@ -9374,13 +9449,13 @@
     </row>
     <row r="257">
       <c r="A257" t="s" s="2">
-        <v>14</v>
+        <v>111</v>
       </c>
       <c r="B257" t="s" s="2">
-        <v>87</v>
+        <v>112</v>
       </c>
       <c r="C257" t="s" s="2">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="D257" t="s" s="2">
         <v>14</v>
@@ -9389,21 +9464,56 @@
         <v>14</v>
       </c>
       <c r="F257" t="s" s="2">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="G257" t="s" s="2">
-        <v>14</v>
+        <v>16</v>
       </c>
       <c r="H257" t="s" s="2">
+        <v>14</v>
+      </c>
+      <c r="I257" t="s" s="2">
+        <v>18</v>
+      </c>
+      <c r="J257" t="s" s="2">
+        <v>14</v>
+      </c>
+      <c r="K257" t="s" s="2">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="258">
+      <c r="A258" t="s" s="2">
+        <v>14</v>
+      </c>
+      <c r="B258" t="s" s="2">
+        <v>112</v>
+      </c>
+      <c r="C258" t="s" s="2">
+        <v>14</v>
+      </c>
+      <c r="D258" t="s" s="2">
+        <v>14</v>
+      </c>
+      <c r="E258" t="s" s="2">
+        <v>14</v>
+      </c>
+      <c r="F258" t="s" s="2">
+        <v>14</v>
+      </c>
+      <c r="G258" t="s" s="2">
+        <v>14</v>
+      </c>
+      <c r="H258" t="s" s="2">
         <v>26</v>
       </c>
-      <c r="I257" t="s" s="2">
-        <v>18</v>
-      </c>
-      <c r="J257" t="s" s="2">
-        <v>14</v>
-      </c>
-      <c r="K257" t="s" s="2">
+      <c r="I258" t="s" s="2">
+        <v>18</v>
+      </c>
+      <c r="J258" t="s" s="2">
+        <v>14</v>
+      </c>
+      <c r="K258" t="s" s="2">
         <v>14</v>
       </c>
     </row>

--- a/observations-summary.xlsx
+++ b/observations-summary.xlsx
@@ -12,7 +12,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2838" uniqueCount="113">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2992" uniqueCount="326">
   <si>
     <t>Profile</t>
   </si>
@@ -59,7 +59,7 @@
     <t/>
   </si>
   <si>
-    <t>http://hl7.org/fhir/ValueSet/observation-codes|4.0.1 (example)</t>
+    <t>FHIR4Eyes Code System#convergence-assessment</t>
   </si>
   <si>
     <t>dateTime, Period, Timing, instant</t>
@@ -77,6 +77,9 @@
     <t>Corrected Intraocular Pressure</t>
   </si>
   <si>
+    <t>FHIR4Eyes Code System#corrected-intraocular-pressure</t>
+  </si>
+  <si>
     <t>dateTimeĵ, Periodĵ, Timingĵ, instantĵ</t>
   </si>
   <si>
@@ -89,69 +92,411 @@
     <t>Cover Test</t>
   </si>
   <si>
+    <t>FHIR4Eyes Code System#cover-test</t>
+  </si>
+  <si>
     <t>CodeableConceptĵ, stringĵ</t>
   </si>
   <si>
+    <t>FHIR4Eyes Code System#correction-status</t>
+  </si>
+  <si>
     <t>CodeableConcept</t>
   </si>
   <si>
+    <t>FHIR4Eyes Code System#test-distance-category</t>
+  </si>
+  <si>
     <t>ct-anterior-chamber</t>
   </si>
   <si>
     <t>Corneal Tomography - Anterior Chamber</t>
   </si>
   <si>
+    <t>FHIR4Eyes Code System#corneal-tomography-anterior-chamber</t>
+  </si>
+  <si>
     <t>Quantity, CodeableConcept, string, boolean, integer, Range, Ratio, SampledData, time, dateTime, Period</t>
   </si>
   <si>
+    <t>FHIR4Eyes Code System#anterior-chamber-depth</t>
+  </si>
+  <si>
     <t>Quantity</t>
   </si>
   <si>
+    <t>FHIR4Eyes Code System#anterior-chamber-volume</t>
+  </si>
+  <si>
+    <t>FHIR4Eyes Code System#anterior-chamber-angle</t>
+  </si>
+  <si>
+    <t>FHIR4Eyes Code System#pupil-diameter</t>
+  </si>
+  <si>
+    <t>FHIR4Eyes Code System#lens-thickness</t>
+  </si>
+  <si>
     <t>ct-anterior-surface</t>
   </si>
   <si>
     <t>Corneal Tomography - Anterior Surface</t>
   </si>
   <si>
+    <t>FHIR4Eyes Code System#corneal-tomography-anterior-surface</t>
+  </si>
+  <si>
+    <t>FHIR4Eyes Code System#keratometry-k1</t>
+  </si>
+  <si>
+    <t>FHIR4Eyes Code System#keratometry-k1-axis</t>
+  </si>
+  <si>
+    <t>FHIR4Eyes Code System#keratometry-k1-radius</t>
+  </si>
+  <si>
+    <t>FHIR4Eyes Code System#keratometry-k2</t>
+  </si>
+  <si>
+    <t>FHIR4Eyes Code System#keratometry-k2-axis</t>
+  </si>
+  <si>
+    <t>FHIR4Eyes Code System#keratometry-k2-radius</t>
+  </si>
+  <si>
+    <t>FHIR4Eyes Code System#keratometry-km</t>
+  </si>
+  <si>
+    <t>FHIR4Eyes Code System#corneal-astigmatism</t>
+  </si>
+  <si>
+    <t>FHIR4Eyes Code System#keratometry-kmax</t>
+  </si>
+  <si>
+    <t>FHIR4Eyes Code System#simulated-keratometry</t>
+  </si>
+  <si>
+    <t>FHIR4Eyes Code System#corneal-radius-horizontal</t>
+  </si>
+  <si>
+    <t>FHIR4Eyes Code System#corneal-radius-vertical</t>
+  </si>
+  <si>
+    <t>FHIR4Eyes Code System#radius-minimum-curvature</t>
+  </si>
+  <si>
+    <t>FHIR4Eyes Code System#corneal-asphericity-q-anterior</t>
+  </si>
+  <si>
+    <t>FHIR4Eyes Code System#elevation-anterior</t>
+  </si>
+  <si>
+    <t>FHIR4Eyes Code System#best-fit-sphere-radius-anterior</t>
+  </si>
+  <si>
+    <t>FHIR4Eyes Code System#surface-regularity-index</t>
+  </si>
+  <si>
+    <t>FHIR4Eyes Code System#surface-asymmetry-index</t>
+  </si>
+  <si>
+    <t>FHIR4Eyes Code System#inferior-superior-asymmetry</t>
+  </si>
+  <si>
+    <t>FHIR4Eyes Code System#kisa-index</t>
+  </si>
+  <si>
+    <t>FHIR4Eyes Code System#keratometric-index</t>
+  </si>
+  <si>
+    <t>FHIR4Eyes Code System#topographic-pattern</t>
+  </si>
+  <si>
+    <t>FHIR4Eyes Code System#total-corneal-refractive-power</t>
+  </si>
+  <si>
+    <t>FHIR4Eyes Code System#true-net-power</t>
+  </si>
+  <si>
+    <t>FHIR4Eyes Code System#equivalent-keratometry-1mm</t>
+  </si>
+  <si>
+    <t>FHIR4Eyes Code System#equivalent-keratometry-3mm</t>
+  </si>
+  <si>
+    <t>FHIR4Eyes Code System#equivalent-keratometry-4-5mm</t>
+  </si>
+  <si>
+    <t>FHIR4Eyes Code System#corneal-mean-power-3mm-zone</t>
+  </si>
+  <si>
+    <t>FHIR4Eyes Code System#corneal-astigmatism-power-3mm-zone</t>
+  </si>
+  <si>
+    <t>FHIR4Eyes Code System#corneal-steep-axis-3mm-zone</t>
+  </si>
+  <si>
+    <t>FHIR4Eyes Code System#corneal-flat-axis-3mm-zone</t>
+  </si>
+  <si>
+    <t>FHIR4Eyes Code System#corneal-mean-power-5mm-zone</t>
+  </si>
+  <si>
+    <t>FHIR4Eyes Code System#corneal-astigmatism-power-5mm-zone</t>
+  </si>
+  <si>
+    <t>FHIR4Eyes Code System#corneal-steep-axis-5mm-zone</t>
+  </si>
+  <si>
+    <t>FHIR4Eyes Code System#corneal-flat-axis-5mm-zone</t>
+  </si>
+  <si>
+    <t>FHIR4Eyes Code System#total-corneal-astigmatism</t>
+  </si>
+  <si>
+    <t>FHIR4Eyes Code System#corneal-irregular-astigmatism</t>
+  </si>
+  <si>
+    <t>FHIR4Eyes Code System#corneal-hoa-rms</t>
+  </si>
+  <si>
+    <t>FHIR4Eyes Code System#angle-kappa</t>
+  </si>
+  <si>
+    <t>FHIR4Eyes Code System#angle-kappa-intercept</t>
+  </si>
+  <si>
     <t>string</t>
   </si>
   <si>
+    <t>FHIR4Eyes Code System#surgically-induced-astigmatism</t>
+  </si>
+  <si>
+    <t>FHIR4Eyes Code System#predicted-postoperative-corneal-astigmatism</t>
+  </si>
+  <si>
+    <t>FHIR4Eyes Code System#toric-iol-optimal-axis</t>
+  </si>
+  <si>
+    <t>FHIR4Eyes Code System#signal-strength</t>
+  </si>
+  <si>
+    <t>FHIR4Eyes Code System#corneal-vertex-location</t>
+  </si>
+  <si>
+    <t>FHIR4Eyes Code System#pupil-centroid-x</t>
+  </si>
+  <si>
+    <t>FHIR4Eyes Code System#pupil-centroid-y</t>
+  </si>
+  <si>
+    <t>FHIR4Eyes Code System#equivalent-pupil-radius</t>
+  </si>
+  <si>
+    <t>FHIR4Eyes Code System#corneal-topography-map-type</t>
+  </si>
+  <si>
+    <t>FHIR4Eyes Code System#corneal-analyzed-area</t>
+  </si>
+  <si>
+    <t>FHIR4Eyes Code System#corneal-eccentricity-index</t>
+  </si>
+  <si>
+    <t>FHIR4Eyes Code System#keratoconus-prediction-index</t>
+  </si>
+  <si>
+    <t>FHIR4Eyes Code System#potential-visual-acuity-decimal</t>
+  </si>
+  <si>
     <t>ct-densitometry</t>
   </si>
   <si>
     <t>Corneal Tomography - Densitometry</t>
   </si>
   <si>
+    <t>FHIR4Eyes Code System#corneal-densitometry</t>
+  </si>
+  <si>
+    <t>FHIR4Eyes Code System#corneal-densitometry-zone-0-2mm</t>
+  </si>
+  <si>
+    <t>FHIR4Eyes Code System#corneal-densitometry-zone-2-6mm</t>
+  </si>
+  <si>
+    <t>FHIR4Eyes Code System#corneal-densitometry-zone-6-10mm</t>
+  </si>
+  <si>
+    <t>FHIR4Eyes Code System#corneal-densitometry-total</t>
+  </si>
+  <si>
+    <t>FHIR4Eyes Code System#corneal-densitometry-anterior-layer</t>
+  </si>
+  <si>
+    <t>FHIR4Eyes Code System#corneal-densitometry-central-layer</t>
+  </si>
+  <si>
+    <t>FHIR4Eyes Code System#corneal-densitometry-posterior-layer</t>
+  </si>
+  <si>
     <t>ct-keratoconus-indices</t>
   </si>
   <si>
     <t>Corneal Tomography - Keratoconus Indices</t>
   </si>
   <si>
+    <t>FHIR4Eyes Code System#keratoconus-indices</t>
+  </si>
+  <si>
+    <t>FHIR4Eyes Code System#bad-d</t>
+  </si>
+  <si>
+    <t>FHIR4Eyes Code System#bad-df</t>
+  </si>
+  <si>
+    <t>FHIR4Eyes Code System#bad-db</t>
+  </si>
+  <si>
+    <t>FHIR4Eyes Code System#pachymetric-progression</t>
+  </si>
+  <si>
+    <t>FHIR4Eyes Code System#bad-dt</t>
+  </si>
+  <si>
+    <t>FHIR4Eyes Code System#bad-dy</t>
+  </si>
+  <si>
+    <t>FHIR4Eyes Code System#bad-classification</t>
+  </si>
+  <si>
+    <t>FHIR4Eyes Code System#enhanced-best-fit-sphere-radius-anterior</t>
+  </si>
+  <si>
+    <t>FHIR4Eyes Code System#enhanced-best-fit-sphere-radius-posterior</t>
+  </si>
+  <si>
+    <t>FHIR4Eyes Code System#amsler-krumeich-stage</t>
+  </si>
+  <si>
+    <t>FHIR4Eyes Code System#belin-abcd-grade</t>
+  </si>
+  <si>
+    <t>FHIR4Eyes Code System#index-surface-variance</t>
+  </si>
+  <si>
+    <t>FHIR4Eyes Code System#index-vertical-asymmetry</t>
+  </si>
+  <si>
+    <t>FHIR4Eyes Code System#keratoconus-index</t>
+  </si>
+  <si>
+    <t>FHIR4Eyes Code System#center-keratoconus-index</t>
+  </si>
+  <si>
+    <t>FHIR4Eyes Code System#index-height-asymmetry</t>
+  </si>
+  <si>
+    <t>FHIR4Eyes Code System#index-height-decentration</t>
+  </si>
+  <si>
+    <t>FHIR4Eyes Code System#radius-minimum-sagittal</t>
+  </si>
+  <si>
+    <t>FHIR4Eyes Code System#topographic-keratoconus-classification</t>
+  </si>
+  <si>
     <t>ct-pachymetry</t>
   </si>
   <si>
     <t>Corneal Tomography - Pachymetry</t>
   </si>
   <si>
+    <t>FHIR4Eyes Code System#corneal-tomography-pachymetry</t>
+  </si>
+  <si>
+    <t>FHIR4Eyes Code System#central-corneal-thickness</t>
+  </si>
+  <si>
+    <t>FHIR4Eyes Code System#corneal-thickness-pupil-centre</t>
+  </si>
+  <si>
+    <t>FHIR4Eyes Code System#corneal-thickness-thinnest</t>
+  </si>
+  <si>
+    <t>FHIR4Eyes Code System#corneal-thinnest-point-location</t>
+  </si>
+  <si>
+    <t>FHIR4Eyes Code System#corneal-volume</t>
+  </si>
+  <si>
     <t>ct-posterior-surface</t>
   </si>
   <si>
     <t>Corneal Tomography - Posterior Surface</t>
   </si>
   <si>
+    <t>FHIR4Eyes Code System#corneal-tomography-posterior-surface</t>
+  </si>
+  <si>
+    <t>FHIR4Eyes Code System#posterior-keratometry-k1</t>
+  </si>
+  <si>
+    <t>FHIR4Eyes Code System#posterior-keratometry-k2</t>
+  </si>
+  <si>
+    <t>FHIR4Eyes Code System#posterior-keratometry-km</t>
+  </si>
+  <si>
+    <t>FHIR4Eyes Code System#corneal-astigmatism-posterior</t>
+  </si>
+  <si>
+    <t>FHIR4Eyes Code System#corneal-asphericity-q-posterior</t>
+  </si>
+  <si>
+    <t>FHIR4Eyes Code System#elevation-posterior</t>
+  </si>
+  <si>
+    <t>FHIR4Eyes Code System#best-fit-sphere-radius-posterior</t>
+  </si>
+  <si>
     <t>gaze-position-measurement</t>
   </si>
   <si>
     <t>Gaze Position Measurement</t>
   </si>
   <si>
+    <t>FHIR4Eyes Code System#gaze-position-measurement</t>
+  </si>
+  <si>
+    <t>FHIR4Eyes Code System#gaze-position</t>
+  </si>
+  <si>
+    <t>FHIR4Eyes Code System#fixating-eye</t>
+  </si>
+  <si>
+    <t>FHIR4Eyes Code System#horizontal-deviation</t>
+  </si>
+  <si>
+    <t>FHIR4Eyes Code System#horizontal-deviation-direction</t>
+  </si>
+  <si>
+    <t>FHIR4Eyes Code System#vertical-deviation</t>
+  </si>
+  <si>
+    <t>FHIR4Eyes Code System#vertical-deviation-direction</t>
+  </si>
+  <si>
+    <t>FHIR4Eyes Code System#gaze-position-finding</t>
+  </si>
+  <si>
     <t>hirschberg-test</t>
   </si>
   <si>
     <t>Hirschberg Test</t>
   </si>
   <si>
+    <t>FHIR4Eyes Code System#hirschberg-test</t>
+  </si>
+  <si>
     <t>intraocular-pressure</t>
   </si>
   <si>
@@ -167,18 +512,48 @@
     <t>IOL Formula Result</t>
   </si>
   <si>
+    <t>FHIR4Eyes Code System#iol-formula-result</t>
+  </si>
+  <si>
+    <t>FHIR4Eyes Code System#iol-formula</t>
+  </si>
+  <si>
+    <t>FHIR4Eyes Code System#iol-lens-constant-type</t>
+  </si>
+  <si>
+    <t>FHIR4Eyes Code System#iol-lens-constant-value</t>
+  </si>
+  <si>
+    <t>FHIR4Eyes Code System#iol-model</t>
+  </si>
+  <si>
+    <t>FHIR4Eyes Code System#iol-power</t>
+  </si>
+  <si>
+    <t>FHIR4Eyes Code System#iol-expected-refraction</t>
+  </si>
+  <si>
+    <t>FHIR4Eyes Code System#iol-power-table</t>
+  </si>
+  <si>
     <t>krimsky-test</t>
   </si>
   <si>
     <t>Krimsky Test</t>
   </si>
   <si>
+    <t>FHIR4Eyes Code System#krimsky-test</t>
+  </si>
+  <si>
     <t>near-point-of-convergence</t>
   </si>
   <si>
     <t>Near Point of Convergence</t>
   </si>
   <si>
+    <t>FHIR4Eyes Code System#near-point-of-convergence</t>
+  </si>
+  <si>
     <t>Quantityĵ, CodeableConceptĵ</t>
   </si>
   <si>
@@ -188,12 +563,93 @@
     <t>Ocular Motility</t>
   </si>
   <si>
+    <t>FHIR4Eyes Code System#ocular-motility</t>
+  </si>
+  <si>
+    <t>FHIR4Eyes Code System#extraocular-muscle</t>
+  </si>
+  <si>
+    <t>FHIR4Eyes Code System#extraocular-muscle-function</t>
+  </si>
+  <si>
     <t>ophthalmic-humphrey-visual-field</t>
   </si>
   <si>
     <t>Ophthalmic Humphrey Visual Field</t>
   </si>
   <si>
+    <t>FHIR4Eyes Code System#visual-field-static-perimetry</t>
+  </si>
+  <si>
+    <t>FHIR4Eyes Code System#visual-field-test-pattern</t>
+  </si>
+  <si>
+    <t>FHIR4Eyes Code System#visual-field-mean-deviation</t>
+  </si>
+  <si>
+    <t>FHIR4Eyes Code System#visual-field-pattern-standard-deviation</t>
+  </si>
+  <si>
+    <t>FHIR4Eyes Code System#visual-field-index</t>
+  </si>
+  <si>
+    <t>FHIR4Eyes Code System#glaucoma-hemifield-test</t>
+  </si>
+  <si>
+    <t>FHIR4Eyes Code System#fixation-losses</t>
+  </si>
+  <si>
+    <t>Ratio</t>
+  </si>
+  <si>
+    <t>FHIR4Eyes Code System#false-positive-errors</t>
+  </si>
+  <si>
+    <t>FHIR4Eyes Code System#false-negative-errors</t>
+  </si>
+  <si>
+    <t>FHIR4Eyes Code System#visual-field-screening-mode</t>
+  </si>
+  <si>
+    <t>FHIR4Eyes Code System#visual-field-fixation-strategy</t>
+  </si>
+  <si>
+    <t>FHIR4Eyes Code System#perimetry-stimulus-size</t>
+  </si>
+  <si>
+    <t>FHIR4Eyes Code System#perimetry-stimulus-color</t>
+  </si>
+  <si>
+    <t>FHIR4Eyes Code System#perimetry-background-luminance</t>
+  </si>
+  <si>
+    <t>FHIR4Eyes Code System#perimetry-max-stimulus-luminance</t>
+  </si>
+  <si>
+    <t>FHIR4Eyes Code System#perimetry-stimulus-duration</t>
+  </si>
+  <si>
+    <t>FHIR4Eyes Code System#visual-field-horizontal-extent</t>
+  </si>
+  <si>
+    <t>FHIR4Eyes Code System#visual-field-vertical-extent</t>
+  </si>
+  <si>
+    <t>FHIR4Eyes Code System#visual-field-shape</t>
+  </si>
+  <si>
+    <t>FHIR4Eyes Code System#foveal-sensitivity</t>
+  </si>
+  <si>
+    <t>FHIR4Eyes Code System#visual-field-test-duration</t>
+  </si>
+  <si>
+    <t>FHIR4Eyes Code System#visual-field-test-point-count</t>
+  </si>
+  <si>
+    <t>FHIR4Eyes Code System#correction-lens-power</t>
+  </si>
+  <si>
     <t>ophthalmic-oct-macula</t>
   </si>
   <si>
@@ -209,6 +665,12 @@
     <t>LOINC#57108-3</t>
   </si>
   <si>
+    <t>FHIR4Eyes Code System#central-subfield-thickness-min</t>
+  </si>
+  <si>
+    <t>FHIR4Eyes Code System#central-subfield-thickness-max</t>
+  </si>
+  <si>
     <t>LOINC#57110-9</t>
   </si>
   <si>
@@ -236,6 +698,30 @@
     <t>LOINC#57118-2</t>
   </si>
   <si>
+    <t>FHIR4Eyes Code System#macular-subfield-volume</t>
+  </si>
+  <si>
+    <t>FHIR4Eyes Code System#etdrs-grid-diameters</t>
+  </si>
+  <si>
+    <t>FHIR4Eyes Code System#retinal-thickness-definition</t>
+  </si>
+  <si>
+    <t>FHIR4Eyes Code System#normative-deviation-category</t>
+  </si>
+  <si>
+    <t>FHIR4Eyes Code System#anatomic-reference-point</t>
+  </si>
+  <si>
+    <t>FHIR4Eyes Code System#pupil-dilated</t>
+  </si>
+  <si>
+    <t>FHIR4Eyes Code System#mydriatic-agent</t>
+  </si>
+  <si>
+    <t>FHIR4Eyes Code System#pupil-dilation-degree</t>
+  </si>
+  <si>
     <t>ophthalmic-oct-rnfl</t>
   </si>
   <si>
@@ -245,49 +731,172 @@
     <t>LOINC#86291-2</t>
   </si>
   <si>
+    <t>FHIR4Eyes Code System#optic-cup-area</t>
+  </si>
+  <si>
+    <t>FHIR4Eyes Code System#optic-cup-volume</t>
+  </si>
+  <si>
+    <t>FHIR4Eyes Code System#neuroretinal-rim-volume</t>
+  </si>
+  <si>
+    <t>FHIR4Eyes Code System#cup-disc-ratio-horizontal</t>
+  </si>
+  <si>
+    <t>FHIR4Eyes Code System#cup-disc-ratio-vertical</t>
+  </si>
+  <si>
+    <t>FHIR4Eyes Code System#optic-disc-diameter-horizontal</t>
+  </si>
+  <si>
+    <t>FHIR4Eyes Code System#optic-disc-diameter-vertical</t>
+  </si>
+  <si>
+    <t>FHIR4Eyes Code System#optic-disc-diameter-mean</t>
+  </si>
+  <si>
+    <t>FHIR4Eyes Code System#optic-cup-diameter-horizontal</t>
+  </si>
+  <si>
+    <t>FHIR4Eyes Code System#optic-cup-diameter-vertical</t>
+  </si>
+  <si>
+    <t>FHIR4Eyes Code System#optic-cup-diameter-mean</t>
+  </si>
+  <si>
+    <t>FHIR4Eyes Code System#optic-cup-depth-mean</t>
+  </si>
+  <si>
+    <t>FHIR4Eyes Code System#optic-cup-depth-max</t>
+  </si>
+  <si>
+    <t>FHIR4Eyes Code System#optic-disc-vertical-horizontal-ratio</t>
+  </si>
+  <si>
+    <t>FHIR4Eyes Code System#optic-cup-vertical-horizontal-ratio</t>
+  </si>
+  <si>
+    <t>FHIR4Eyes Code System#rim-disc-area-ratio</t>
+  </si>
+  <si>
+    <t>FHIR4Eyes Code System#neuroretinal-rim-absence-extent</t>
+  </si>
+  <si>
+    <t>FHIR4Eyes Code System#disc-damage-likelihood-scale</t>
+  </si>
+  <si>
     <t>integer</t>
   </si>
   <si>
+    <t>FHIR4Eyes Code System#rnfl-symmetry</t>
+  </si>
+  <si>
+    <t>FHIR4Eyes Code System#rnfl-thickness-mean-tsnit</t>
+  </si>
+  <si>
+    <t>FHIR4Eyes Code System#rnfl-thickness-tsnit-sd</t>
+  </si>
+  <si>
+    <t>FHIR4Eyes Code System#rnfl-thickness-superior</t>
+  </si>
+  <si>
+    <t>FHIR4Eyes Code System#rnfl-thickness-inferior</t>
+  </si>
+  <si>
+    <t>FHIR4Eyes Code System#rnfl-thickness-nasal</t>
+  </si>
+  <si>
+    <t>FHIR4Eyes Code System#rnfl-thickness-temporal</t>
+  </si>
+  <si>
     <t>ophthalmic-ocular-biometry</t>
   </si>
   <si>
     <t>Ophthalmic Ocular Biometry</t>
   </si>
   <si>
+    <t>FHIR4Eyes Code System#ocular-biometry</t>
+  </si>
+  <si>
+    <t>FHIR4Eyes Code System#axial-length</t>
+  </si>
+  <si>
+    <t>FHIR4Eyes Code System#axial-length-measurement-type</t>
+  </si>
+  <si>
+    <t>FHIR4Eyes Code System#axial-length-snr</t>
+  </si>
+  <si>
+    <t>FHIR4Eyes Code System#axial-length-selection-method</t>
+  </si>
+  <si>
+    <t>FHIR4Eyes Code System#anterior-chamber-depth-definition</t>
+  </si>
+  <si>
+    <t>FHIR4Eyes Code System#lens-status</t>
+  </si>
+  <si>
+    <t>FHIR4Eyes Code System#vitreous-status</t>
+  </si>
+  <si>
+    <t>FHIR4Eyes Code System#keratometry-mean-radius</t>
+  </si>
+  <si>
+    <t>FHIR4Eyes Code System#white-to-white</t>
+  </si>
+  <si>
+    <t>FHIR4Eyes Code System#refractive-surgery-history</t>
+  </si>
+  <si>
+    <t>FHIR4Eyes Code System#target-refraction</t>
+  </si>
+  <si>
+    <t>FHIR4Eyes Code System#refractive-error-type</t>
+  </si>
+  <si>
+    <t>FHIR4Eyes Code System#measurement-data-source</t>
+  </si>
+  <si>
+    <t>FHIR4Eyes Code System#vertex-distance</t>
+  </si>
+  <si>
     <t>ophthalmic-specular-microscopy</t>
   </si>
   <si>
     <t>Ophthalmic Specular Microscopy</t>
   </si>
   <si>
-    <t>LOINC#100086-8</t>
-  </si>
-  <si>
-    <t>LOINC#100070-2</t>
-  </si>
-  <si>
-    <t>LOINC#100076-9</t>
-  </si>
-  <si>
-    <t>LOINC#100072-8</t>
-  </si>
-  <si>
-    <t>LOINC#100074-4</t>
-  </si>
-  <si>
-    <t>LOINC#79825-6</t>
-  </si>
-  <si>
-    <t>LOINC#100078-5</t>
-  </si>
-  <si>
-    <t>LOINC#100080-1</t>
-  </si>
-  <si>
-    <t>LOINC#100082-7</t>
-  </si>
-  <si>
-    <t>LOINC#100084-3</t>
+    <t>FHIR4Eyes Code System#specular-microscopy-panel</t>
+  </si>
+  <si>
+    <t>FHIR4Eyes Code System#specular-capture-position</t>
+  </si>
+  <si>
+    <t>FHIR4Eyes Code System#specular-analysis-method</t>
+  </si>
+  <si>
+    <t>FHIR4Eyes Code System#endothelial-cell-density</t>
+  </si>
+  <si>
+    <t>FHIR4Eyes Code System#endothelial-cells-counted</t>
+  </si>
+  <si>
+    <t>FHIR4Eyes Code System#endothelial-cell-area-cv</t>
+  </si>
+  <si>
+    <t>FHIR4Eyes Code System#endothelial-hexagonality</t>
+  </si>
+  <si>
+    <t>FHIR4Eyes Code System#endothelial-cell-area-min</t>
+  </si>
+  <si>
+    <t>FHIR4Eyes Code System#endothelial-cell-area-max</t>
+  </si>
+  <si>
+    <t>FHIR4Eyes Code System#endothelial-cell-area-mean</t>
+  </si>
+  <si>
+    <t>FHIR4Eyes Code System#endothelial-cell-area-sd</t>
   </si>
   <si>
     <t>ophthalmic-visual-acuity</t>
@@ -296,15 +905,24 @@
     <t>Ophthalmic Visual Acuity</t>
   </si>
   <si>
-    <t>LOINC#98497-1</t>
+    <t>SNOMED CT#363983007</t>
   </si>
   <si>
     <t>Quantityĵ, CodeableConceptĵ, Ratioĵ</t>
   </si>
   <si>
+    <t>FHIR4Eyes Code System#test-distance</t>
+  </si>
+  <si>
     <t>LOINC#79908-0</t>
   </si>
   <si>
+    <t>FHIR4Eyes Code System#visual-acuity-scale</t>
+  </si>
+  <si>
+    <t>FHIR4Eyes Code System#pinhole-used</t>
+  </si>
+  <si>
     <t>boolean</t>
   </si>
   <si>
@@ -320,30 +938,48 @@
     <t>Prism Cover Test</t>
   </si>
   <si>
+    <t>FHIR4Eyes Code System#prism-cover-test</t>
+  </si>
+  <si>
     <t>red-filter-light-test</t>
   </si>
   <si>
     <t>Red Filter Light Test</t>
   </si>
   <si>
+    <t>FHIR4Eyes Code System#red-filter-light-test</t>
+  </si>
+  <si>
     <t>stereopsis-test</t>
   </si>
   <si>
     <t>Stereopsis Test</t>
   </si>
   <si>
+    <t>FHIR4Eyes Code System#stereopsis-test</t>
+  </si>
+  <si>
+    <t>FHIR4Eyes Code System#stereopsis-test-type</t>
+  </si>
+  <si>
     <t>strabismus-exam</t>
   </si>
   <si>
     <t>Strabismus Exam</t>
   </si>
   <si>
+    <t>FHIR4Eyes Code System#strabismus-exam</t>
+  </si>
+  <si>
     <t>tension-curve</t>
   </si>
   <si>
     <t>Tension Curve</t>
   </si>
   <si>
+    <t>FHIR4Eyes Code System#tension-curve</t>
+  </si>
+  <si>
     <t>Periodĵ</t>
   </si>
   <si>
@@ -351,6 +987,9 @@
   </si>
   <si>
     <t>Worth 4 Dot Test</t>
+  </si>
+  <si>
+    <t>FHIR4Eyes Code System#worth-4-dot-test</t>
   </si>
 </sst>
 </file>
@@ -484,7 +1123,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <dimension ref="A1:K258"/>
+  <dimension ref="A1:K272"/>
   <sheetFormatPr defaultRowHeight="15.0"/>
   <sheetData>
     <row r="1">
@@ -536,10 +1175,10 @@
         <v>14</v>
       </c>
       <c r="E2" t="s" s="2">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="F2" t="s" s="2">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="G2" t="s" s="2">
         <v>16</v>
@@ -571,16 +1210,16 @@
         <v>14</v>
       </c>
       <c r="E3" t="s" s="2">
-        <v>14</v>
+        <v>21</v>
       </c>
       <c r="F3" t="s" s="2">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="G3" t="s" s="2">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="H3" t="s" s="2">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="I3" t="s" s="2">
         <v>18</v>
@@ -594,10 +1233,10 @@
     </row>
     <row r="4">
       <c r="A4" t="s" s="2">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="B4" t="s" s="2">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="C4" t="s" s="2">
         <v>13</v>
@@ -606,16 +1245,16 @@
         <v>14</v>
       </c>
       <c r="E4" t="s" s="2">
-        <v>14</v>
+        <v>26</v>
       </c>
       <c r="F4" t="s" s="2">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="G4" t="s" s="2">
         <v>16</v>
       </c>
       <c r="H4" t="s" s="2">
-        <v>25</v>
+        <v>27</v>
       </c>
       <c r="I4" t="s" s="2">
         <v>18</v>
@@ -632,7 +1271,7 @@
         <v>14</v>
       </c>
       <c r="B5" t="s" s="2">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="C5" t="s" s="2">
         <v>14</v>
@@ -641,7 +1280,7 @@
         <v>14</v>
       </c>
       <c r="E5" t="s" s="2">
-        <v>14</v>
+        <v>28</v>
       </c>
       <c r="F5" t="s" s="2">
         <v>14</v>
@@ -650,7 +1289,7 @@
         <v>14</v>
       </c>
       <c r="H5" t="s" s="2">
-        <v>26</v>
+        <v>29</v>
       </c>
       <c r="I5" t="s" s="2">
         <v>18</v>
@@ -667,7 +1306,7 @@
         <v>14</v>
       </c>
       <c r="B6" t="s" s="2">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="C6" t="s" s="2">
         <v>14</v>
@@ -676,7 +1315,7 @@
         <v>14</v>
       </c>
       <c r="E6" t="s" s="2">
-        <v>14</v>
+        <v>30</v>
       </c>
       <c r="F6" t="s" s="2">
         <v>14</v>
@@ -685,7 +1324,7 @@
         <v>14</v>
       </c>
       <c r="H6" t="s" s="2">
-        <v>26</v>
+        <v>29</v>
       </c>
       <c r="I6" t="s" s="2">
         <v>18</v>
@@ -699,10 +1338,10 @@
     </row>
     <row r="7">
       <c r="A7" t="s" s="2">
-        <v>27</v>
+        <v>31</v>
       </c>
       <c r="B7" t="s" s="2">
-        <v>28</v>
+        <v>32</v>
       </c>
       <c r="C7" t="s" s="2">
         <v>13</v>
@@ -711,16 +1350,16 @@
         <v>14</v>
       </c>
       <c r="E7" t="s" s="2">
-        <v>14</v>
+        <v>33</v>
       </c>
       <c r="F7" t="s" s="2">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="G7" t="s" s="2">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="H7" t="s" s="2">
-        <v>29</v>
+        <v>34</v>
       </c>
       <c r="I7" t="s" s="2">
         <v>18</v>
@@ -737,7 +1376,7 @@
         <v>14</v>
       </c>
       <c r="B8" t="s" s="2">
-        <v>28</v>
+        <v>32</v>
       </c>
       <c r="C8" t="s" s="2">
         <v>14</v>
@@ -746,7 +1385,7 @@
         <v>14</v>
       </c>
       <c r="E8" t="s" s="2">
-        <v>14</v>
+        <v>35</v>
       </c>
       <c r="F8" t="s" s="2">
         <v>14</v>
@@ -755,7 +1394,7 @@
         <v>14</v>
       </c>
       <c r="H8" t="s" s="2">
-        <v>30</v>
+        <v>36</v>
       </c>
       <c r="I8" t="s" s="2">
         <v>18</v>
@@ -772,7 +1411,7 @@
         <v>14</v>
       </c>
       <c r="B9" t="s" s="2">
-        <v>28</v>
+        <v>32</v>
       </c>
       <c r="C9" t="s" s="2">
         <v>14</v>
@@ -781,7 +1420,7 @@
         <v>14</v>
       </c>
       <c r="E9" t="s" s="2">
-        <v>14</v>
+        <v>37</v>
       </c>
       <c r="F9" t="s" s="2">
         <v>14</v>
@@ -790,7 +1429,7 @@
         <v>14</v>
       </c>
       <c r="H9" t="s" s="2">
-        <v>30</v>
+        <v>36</v>
       </c>
       <c r="I9" t="s" s="2">
         <v>18</v>
@@ -807,7 +1446,7 @@
         <v>14</v>
       </c>
       <c r="B10" t="s" s="2">
-        <v>28</v>
+        <v>32</v>
       </c>
       <c r="C10" t="s" s="2">
         <v>14</v>
@@ -816,7 +1455,7 @@
         <v>14</v>
       </c>
       <c r="E10" t="s" s="2">
-        <v>14</v>
+        <v>38</v>
       </c>
       <c r="F10" t="s" s="2">
         <v>14</v>
@@ -825,7 +1464,7 @@
         <v>14</v>
       </c>
       <c r="H10" t="s" s="2">
-        <v>30</v>
+        <v>36</v>
       </c>
       <c r="I10" t="s" s="2">
         <v>18</v>
@@ -842,7 +1481,7 @@
         <v>14</v>
       </c>
       <c r="B11" t="s" s="2">
-        <v>28</v>
+        <v>32</v>
       </c>
       <c r="C11" t="s" s="2">
         <v>14</v>
@@ -851,7 +1490,7 @@
         <v>14</v>
       </c>
       <c r="E11" t="s" s="2">
-        <v>14</v>
+        <v>39</v>
       </c>
       <c r="F11" t="s" s="2">
         <v>14</v>
@@ -860,7 +1499,7 @@
         <v>14</v>
       </c>
       <c r="H11" t="s" s="2">
-        <v>30</v>
+        <v>36</v>
       </c>
       <c r="I11" t="s" s="2">
         <v>18</v>
@@ -877,7 +1516,7 @@
         <v>14</v>
       </c>
       <c r="B12" t="s" s="2">
-        <v>28</v>
+        <v>32</v>
       </c>
       <c r="C12" t="s" s="2">
         <v>14</v>
@@ -886,7 +1525,7 @@
         <v>14</v>
       </c>
       <c r="E12" t="s" s="2">
-        <v>14</v>
+        <v>40</v>
       </c>
       <c r="F12" t="s" s="2">
         <v>14</v>
@@ -895,7 +1534,7 @@
         <v>14</v>
       </c>
       <c r="H12" t="s" s="2">
-        <v>30</v>
+        <v>36</v>
       </c>
       <c r="I12" t="s" s="2">
         <v>18</v>
@@ -909,10 +1548,10 @@
     </row>
     <row r="13">
       <c r="A13" t="s" s="2">
-        <v>31</v>
+        <v>41</v>
       </c>
       <c r="B13" t="s" s="2">
-        <v>32</v>
+        <v>42</v>
       </c>
       <c r="C13" t="s" s="2">
         <v>13</v>
@@ -921,16 +1560,16 @@
         <v>14</v>
       </c>
       <c r="E13" t="s" s="2">
-        <v>14</v>
+        <v>43</v>
       </c>
       <c r="F13" t="s" s="2">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="G13" t="s" s="2">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="H13" t="s" s="2">
-        <v>29</v>
+        <v>34</v>
       </c>
       <c r="I13" t="s" s="2">
         <v>18</v>
@@ -947,7 +1586,7 @@
         <v>14</v>
       </c>
       <c r="B14" t="s" s="2">
-        <v>32</v>
+        <v>42</v>
       </c>
       <c r="C14" t="s" s="2">
         <v>14</v>
@@ -956,7 +1595,7 @@
         <v>14</v>
       </c>
       <c r="E14" t="s" s="2">
-        <v>14</v>
+        <v>44</v>
       </c>
       <c r="F14" t="s" s="2">
         <v>14</v>
@@ -965,7 +1604,7 @@
         <v>14</v>
       </c>
       <c r="H14" t="s" s="2">
-        <v>30</v>
+        <v>36</v>
       </c>
       <c r="I14" t="s" s="2">
         <v>18</v>
@@ -982,7 +1621,7 @@
         <v>14</v>
       </c>
       <c r="B15" t="s" s="2">
-        <v>32</v>
+        <v>42</v>
       </c>
       <c r="C15" t="s" s="2">
         <v>14</v>
@@ -991,7 +1630,7 @@
         <v>14</v>
       </c>
       <c r="E15" t="s" s="2">
-        <v>14</v>
+        <v>45</v>
       </c>
       <c r="F15" t="s" s="2">
         <v>14</v>
@@ -1000,7 +1639,7 @@
         <v>14</v>
       </c>
       <c r="H15" t="s" s="2">
-        <v>30</v>
+        <v>36</v>
       </c>
       <c r="I15" t="s" s="2">
         <v>18</v>
@@ -1017,7 +1656,7 @@
         <v>14</v>
       </c>
       <c r="B16" t="s" s="2">
-        <v>32</v>
+        <v>42</v>
       </c>
       <c r="C16" t="s" s="2">
         <v>14</v>
@@ -1026,7 +1665,7 @@
         <v>14</v>
       </c>
       <c r="E16" t="s" s="2">
-        <v>14</v>
+        <v>46</v>
       </c>
       <c r="F16" t="s" s="2">
         <v>14</v>
@@ -1035,7 +1674,7 @@
         <v>14</v>
       </c>
       <c r="H16" t="s" s="2">
-        <v>30</v>
+        <v>36</v>
       </c>
       <c r="I16" t="s" s="2">
         <v>18</v>
@@ -1052,7 +1691,7 @@
         <v>14</v>
       </c>
       <c r="B17" t="s" s="2">
-        <v>32</v>
+        <v>42</v>
       </c>
       <c r="C17" t="s" s="2">
         <v>14</v>
@@ -1061,7 +1700,7 @@
         <v>14</v>
       </c>
       <c r="E17" t="s" s="2">
-        <v>14</v>
+        <v>47</v>
       </c>
       <c r="F17" t="s" s="2">
         <v>14</v>
@@ -1070,7 +1709,7 @@
         <v>14</v>
       </c>
       <c r="H17" t="s" s="2">
-        <v>30</v>
+        <v>36</v>
       </c>
       <c r="I17" t="s" s="2">
         <v>18</v>
@@ -1087,7 +1726,7 @@
         <v>14</v>
       </c>
       <c r="B18" t="s" s="2">
-        <v>32</v>
+        <v>42</v>
       </c>
       <c r="C18" t="s" s="2">
         <v>14</v>
@@ -1096,7 +1735,7 @@
         <v>14</v>
       </c>
       <c r="E18" t="s" s="2">
-        <v>14</v>
+        <v>48</v>
       </c>
       <c r="F18" t="s" s="2">
         <v>14</v>
@@ -1105,7 +1744,7 @@
         <v>14</v>
       </c>
       <c r="H18" t="s" s="2">
-        <v>30</v>
+        <v>36</v>
       </c>
       <c r="I18" t="s" s="2">
         <v>18</v>
@@ -1122,7 +1761,7 @@
         <v>14</v>
       </c>
       <c r="B19" t="s" s="2">
-        <v>32</v>
+        <v>42</v>
       </c>
       <c r="C19" t="s" s="2">
         <v>14</v>
@@ -1131,7 +1770,7 @@
         <v>14</v>
       </c>
       <c r="E19" t="s" s="2">
-        <v>14</v>
+        <v>49</v>
       </c>
       <c r="F19" t="s" s="2">
         <v>14</v>
@@ -1140,7 +1779,7 @@
         <v>14</v>
       </c>
       <c r="H19" t="s" s="2">
-        <v>30</v>
+        <v>36</v>
       </c>
       <c r="I19" t="s" s="2">
         <v>18</v>
@@ -1157,7 +1796,7 @@
         <v>14</v>
       </c>
       <c r="B20" t="s" s="2">
-        <v>32</v>
+        <v>42</v>
       </c>
       <c r="C20" t="s" s="2">
         <v>14</v>
@@ -1166,7 +1805,7 @@
         <v>14</v>
       </c>
       <c r="E20" t="s" s="2">
-        <v>14</v>
+        <v>50</v>
       </c>
       <c r="F20" t="s" s="2">
         <v>14</v>
@@ -1175,7 +1814,7 @@
         <v>14</v>
       </c>
       <c r="H20" t="s" s="2">
-        <v>30</v>
+        <v>36</v>
       </c>
       <c r="I20" t="s" s="2">
         <v>18</v>
@@ -1192,7 +1831,7 @@
         <v>14</v>
       </c>
       <c r="B21" t="s" s="2">
-        <v>32</v>
+        <v>42</v>
       </c>
       <c r="C21" t="s" s="2">
         <v>14</v>
@@ -1201,7 +1840,7 @@
         <v>14</v>
       </c>
       <c r="E21" t="s" s="2">
-        <v>14</v>
+        <v>51</v>
       </c>
       <c r="F21" t="s" s="2">
         <v>14</v>
@@ -1210,7 +1849,7 @@
         <v>14</v>
       </c>
       <c r="H21" t="s" s="2">
-        <v>30</v>
+        <v>36</v>
       </c>
       <c r="I21" t="s" s="2">
         <v>18</v>
@@ -1227,7 +1866,7 @@
         <v>14</v>
       </c>
       <c r="B22" t="s" s="2">
-        <v>32</v>
+        <v>42</v>
       </c>
       <c r="C22" t="s" s="2">
         <v>14</v>
@@ -1236,7 +1875,7 @@
         <v>14</v>
       </c>
       <c r="E22" t="s" s="2">
-        <v>14</v>
+        <v>52</v>
       </c>
       <c r="F22" t="s" s="2">
         <v>14</v>
@@ -1245,7 +1884,7 @@
         <v>14</v>
       </c>
       <c r="H22" t="s" s="2">
-        <v>30</v>
+        <v>36</v>
       </c>
       <c r="I22" t="s" s="2">
         <v>18</v>
@@ -1262,7 +1901,7 @@
         <v>14</v>
       </c>
       <c r="B23" t="s" s="2">
-        <v>32</v>
+        <v>42</v>
       </c>
       <c r="C23" t="s" s="2">
         <v>14</v>
@@ -1271,7 +1910,7 @@
         <v>14</v>
       </c>
       <c r="E23" t="s" s="2">
-        <v>14</v>
+        <v>53</v>
       </c>
       <c r="F23" t="s" s="2">
         <v>14</v>
@@ -1280,7 +1919,7 @@
         <v>14</v>
       </c>
       <c r="H23" t="s" s="2">
-        <v>30</v>
+        <v>36</v>
       </c>
       <c r="I23" t="s" s="2">
         <v>18</v>
@@ -1297,7 +1936,7 @@
         <v>14</v>
       </c>
       <c r="B24" t="s" s="2">
-        <v>32</v>
+        <v>42</v>
       </c>
       <c r="C24" t="s" s="2">
         <v>14</v>
@@ -1306,7 +1945,7 @@
         <v>14</v>
       </c>
       <c r="E24" t="s" s="2">
-        <v>14</v>
+        <v>54</v>
       </c>
       <c r="F24" t="s" s="2">
         <v>14</v>
@@ -1315,7 +1954,7 @@
         <v>14</v>
       </c>
       <c r="H24" t="s" s="2">
-        <v>30</v>
+        <v>36</v>
       </c>
       <c r="I24" t="s" s="2">
         <v>18</v>
@@ -1332,7 +1971,7 @@
         <v>14</v>
       </c>
       <c r="B25" t="s" s="2">
-        <v>32</v>
+        <v>42</v>
       </c>
       <c r="C25" t="s" s="2">
         <v>14</v>
@@ -1341,7 +1980,7 @@
         <v>14</v>
       </c>
       <c r="E25" t="s" s="2">
-        <v>14</v>
+        <v>55</v>
       </c>
       <c r="F25" t="s" s="2">
         <v>14</v>
@@ -1350,7 +1989,7 @@
         <v>14</v>
       </c>
       <c r="H25" t="s" s="2">
-        <v>30</v>
+        <v>36</v>
       </c>
       <c r="I25" t="s" s="2">
         <v>18</v>
@@ -1367,7 +2006,7 @@
         <v>14</v>
       </c>
       <c r="B26" t="s" s="2">
-        <v>32</v>
+        <v>42</v>
       </c>
       <c r="C26" t="s" s="2">
         <v>14</v>
@@ -1376,7 +2015,7 @@
         <v>14</v>
       </c>
       <c r="E26" t="s" s="2">
-        <v>14</v>
+        <v>56</v>
       </c>
       <c r="F26" t="s" s="2">
         <v>14</v>
@@ -1385,7 +2024,7 @@
         <v>14</v>
       </c>
       <c r="H26" t="s" s="2">
-        <v>30</v>
+        <v>36</v>
       </c>
       <c r="I26" t="s" s="2">
         <v>18</v>
@@ -1402,7 +2041,7 @@
         <v>14</v>
       </c>
       <c r="B27" t="s" s="2">
-        <v>32</v>
+        <v>42</v>
       </c>
       <c r="C27" t="s" s="2">
         <v>14</v>
@@ -1411,7 +2050,7 @@
         <v>14</v>
       </c>
       <c r="E27" t="s" s="2">
-        <v>14</v>
+        <v>57</v>
       </c>
       <c r="F27" t="s" s="2">
         <v>14</v>
@@ -1420,7 +2059,7 @@
         <v>14</v>
       </c>
       <c r="H27" t="s" s="2">
-        <v>30</v>
+        <v>36</v>
       </c>
       <c r="I27" t="s" s="2">
         <v>18</v>
@@ -1437,7 +2076,7 @@
         <v>14</v>
       </c>
       <c r="B28" t="s" s="2">
-        <v>32</v>
+        <v>42</v>
       </c>
       <c r="C28" t="s" s="2">
         <v>14</v>
@@ -1446,7 +2085,7 @@
         <v>14</v>
       </c>
       <c r="E28" t="s" s="2">
-        <v>14</v>
+        <v>58</v>
       </c>
       <c r="F28" t="s" s="2">
         <v>14</v>
@@ -1455,7 +2094,7 @@
         <v>14</v>
       </c>
       <c r="H28" t="s" s="2">
-        <v>30</v>
+        <v>36</v>
       </c>
       <c r="I28" t="s" s="2">
         <v>18</v>
@@ -1472,7 +2111,7 @@
         <v>14</v>
       </c>
       <c r="B29" t="s" s="2">
-        <v>32</v>
+        <v>42</v>
       </c>
       <c r="C29" t="s" s="2">
         <v>14</v>
@@ -1481,7 +2120,7 @@
         <v>14</v>
       </c>
       <c r="E29" t="s" s="2">
-        <v>14</v>
+        <v>59</v>
       </c>
       <c r="F29" t="s" s="2">
         <v>14</v>
@@ -1490,7 +2129,7 @@
         <v>14</v>
       </c>
       <c r="H29" t="s" s="2">
-        <v>30</v>
+        <v>36</v>
       </c>
       <c r="I29" t="s" s="2">
         <v>18</v>
@@ -1507,7 +2146,7 @@
         <v>14</v>
       </c>
       <c r="B30" t="s" s="2">
-        <v>32</v>
+        <v>42</v>
       </c>
       <c r="C30" t="s" s="2">
         <v>14</v>
@@ -1516,7 +2155,7 @@
         <v>14</v>
       </c>
       <c r="E30" t="s" s="2">
-        <v>14</v>
+        <v>60</v>
       </c>
       <c r="F30" t="s" s="2">
         <v>14</v>
@@ -1525,7 +2164,7 @@
         <v>14</v>
       </c>
       <c r="H30" t="s" s="2">
-        <v>30</v>
+        <v>36</v>
       </c>
       <c r="I30" t="s" s="2">
         <v>18</v>
@@ -1542,7 +2181,7 @@
         <v>14</v>
       </c>
       <c r="B31" t="s" s="2">
-        <v>32</v>
+        <v>42</v>
       </c>
       <c r="C31" t="s" s="2">
         <v>14</v>
@@ -1551,7 +2190,7 @@
         <v>14</v>
       </c>
       <c r="E31" t="s" s="2">
-        <v>14</v>
+        <v>61</v>
       </c>
       <c r="F31" t="s" s="2">
         <v>14</v>
@@ -1560,7 +2199,7 @@
         <v>14</v>
       </c>
       <c r="H31" t="s" s="2">
-        <v>30</v>
+        <v>36</v>
       </c>
       <c r="I31" t="s" s="2">
         <v>18</v>
@@ -1577,7 +2216,7 @@
         <v>14</v>
       </c>
       <c r="B32" t="s" s="2">
-        <v>32</v>
+        <v>42</v>
       </c>
       <c r="C32" t="s" s="2">
         <v>14</v>
@@ -1586,7 +2225,7 @@
         <v>14</v>
       </c>
       <c r="E32" t="s" s="2">
-        <v>14</v>
+        <v>62</v>
       </c>
       <c r="F32" t="s" s="2">
         <v>14</v>
@@ -1595,7 +2234,7 @@
         <v>14</v>
       </c>
       <c r="H32" t="s" s="2">
-        <v>30</v>
+        <v>36</v>
       </c>
       <c r="I32" t="s" s="2">
         <v>18</v>
@@ -1612,7 +2251,7 @@
         <v>14</v>
       </c>
       <c r="B33" t="s" s="2">
-        <v>32</v>
+        <v>42</v>
       </c>
       <c r="C33" t="s" s="2">
         <v>14</v>
@@ -1621,7 +2260,7 @@
         <v>14</v>
       </c>
       <c r="E33" t="s" s="2">
-        <v>14</v>
+        <v>63</v>
       </c>
       <c r="F33" t="s" s="2">
         <v>14</v>
@@ -1630,7 +2269,7 @@
         <v>14</v>
       </c>
       <c r="H33" t="s" s="2">
-        <v>30</v>
+        <v>36</v>
       </c>
       <c r="I33" t="s" s="2">
         <v>18</v>
@@ -1647,7 +2286,7 @@
         <v>14</v>
       </c>
       <c r="B34" t="s" s="2">
-        <v>32</v>
+        <v>42</v>
       </c>
       <c r="C34" t="s" s="2">
         <v>14</v>
@@ -1656,7 +2295,7 @@
         <v>14</v>
       </c>
       <c r="E34" t="s" s="2">
-        <v>14</v>
+        <v>64</v>
       </c>
       <c r="F34" t="s" s="2">
         <v>14</v>
@@ -1665,7 +2304,7 @@
         <v>14</v>
       </c>
       <c r="H34" t="s" s="2">
-        <v>30</v>
+        <v>36</v>
       </c>
       <c r="I34" t="s" s="2">
         <v>18</v>
@@ -1682,7 +2321,7 @@
         <v>14</v>
       </c>
       <c r="B35" t="s" s="2">
-        <v>32</v>
+        <v>42</v>
       </c>
       <c r="C35" t="s" s="2">
         <v>14</v>
@@ -1691,7 +2330,7 @@
         <v>14</v>
       </c>
       <c r="E35" t="s" s="2">
-        <v>14</v>
+        <v>65</v>
       </c>
       <c r="F35" t="s" s="2">
         <v>14</v>
@@ -1700,7 +2339,7 @@
         <v>14</v>
       </c>
       <c r="H35" t="s" s="2">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="I35" t="s" s="2">
         <v>18</v>
@@ -1717,7 +2356,7 @@
         <v>14</v>
       </c>
       <c r="B36" t="s" s="2">
-        <v>32</v>
+        <v>42</v>
       </c>
       <c r="C36" t="s" s="2">
         <v>14</v>
@@ -1726,7 +2365,7 @@
         <v>14</v>
       </c>
       <c r="E36" t="s" s="2">
-        <v>14</v>
+        <v>66</v>
       </c>
       <c r="F36" t="s" s="2">
         <v>14</v>
@@ -1735,7 +2374,7 @@
         <v>14</v>
       </c>
       <c r="H36" t="s" s="2">
-        <v>26</v>
+        <v>36</v>
       </c>
       <c r="I36" t="s" s="2">
         <v>18</v>
@@ -1752,7 +2391,7 @@
         <v>14</v>
       </c>
       <c r="B37" t="s" s="2">
-        <v>32</v>
+        <v>42</v>
       </c>
       <c r="C37" t="s" s="2">
         <v>14</v>
@@ -1761,7 +2400,7 @@
         <v>14</v>
       </c>
       <c r="E37" t="s" s="2">
-        <v>14</v>
+        <v>67</v>
       </c>
       <c r="F37" t="s" s="2">
         <v>14</v>
@@ -1770,7 +2409,7 @@
         <v>14</v>
       </c>
       <c r="H37" t="s" s="2">
-        <v>30</v>
+        <v>36</v>
       </c>
       <c r="I37" t="s" s="2">
         <v>18</v>
@@ -1787,7 +2426,7 @@
         <v>14</v>
       </c>
       <c r="B38" t="s" s="2">
-        <v>32</v>
+        <v>42</v>
       </c>
       <c r="C38" t="s" s="2">
         <v>14</v>
@@ -1796,7 +2435,7 @@
         <v>14</v>
       </c>
       <c r="E38" t="s" s="2">
-        <v>14</v>
+        <v>68</v>
       </c>
       <c r="F38" t="s" s="2">
         <v>14</v>
@@ -1805,7 +2444,7 @@
         <v>14</v>
       </c>
       <c r="H38" t="s" s="2">
-        <v>30</v>
+        <v>36</v>
       </c>
       <c r="I38" t="s" s="2">
         <v>18</v>
@@ -1822,7 +2461,7 @@
         <v>14</v>
       </c>
       <c r="B39" t="s" s="2">
-        <v>32</v>
+        <v>42</v>
       </c>
       <c r="C39" t="s" s="2">
         <v>14</v>
@@ -1831,7 +2470,7 @@
         <v>14</v>
       </c>
       <c r="E39" t="s" s="2">
-        <v>14</v>
+        <v>69</v>
       </c>
       <c r="F39" t="s" s="2">
         <v>14</v>
@@ -1840,7 +2479,7 @@
         <v>14</v>
       </c>
       <c r="H39" t="s" s="2">
-        <v>30</v>
+        <v>36</v>
       </c>
       <c r="I39" t="s" s="2">
         <v>18</v>
@@ -1857,7 +2496,7 @@
         <v>14</v>
       </c>
       <c r="B40" t="s" s="2">
-        <v>32</v>
+        <v>42</v>
       </c>
       <c r="C40" t="s" s="2">
         <v>14</v>
@@ -1866,7 +2505,7 @@
         <v>14</v>
       </c>
       <c r="E40" t="s" s="2">
-        <v>14</v>
+        <v>70</v>
       </c>
       <c r="F40" t="s" s="2">
         <v>14</v>
@@ -1875,7 +2514,7 @@
         <v>14</v>
       </c>
       <c r="H40" t="s" s="2">
-        <v>30</v>
+        <v>36</v>
       </c>
       <c r="I40" t="s" s="2">
         <v>18</v>
@@ -1892,7 +2531,7 @@
         <v>14</v>
       </c>
       <c r="B41" t="s" s="2">
-        <v>32</v>
+        <v>42</v>
       </c>
       <c r="C41" t="s" s="2">
         <v>14</v>
@@ -1901,7 +2540,7 @@
         <v>14</v>
       </c>
       <c r="E41" t="s" s="2">
-        <v>14</v>
+        <v>71</v>
       </c>
       <c r="F41" t="s" s="2">
         <v>14</v>
@@ -1910,7 +2549,7 @@
         <v>14</v>
       </c>
       <c r="H41" t="s" s="2">
-        <v>30</v>
+        <v>36</v>
       </c>
       <c r="I41" t="s" s="2">
         <v>18</v>
@@ -1927,7 +2566,7 @@
         <v>14</v>
       </c>
       <c r="B42" t="s" s="2">
-        <v>32</v>
+        <v>42</v>
       </c>
       <c r="C42" t="s" s="2">
         <v>14</v>
@@ -1936,7 +2575,7 @@
         <v>14</v>
       </c>
       <c r="E42" t="s" s="2">
-        <v>14</v>
+        <v>72</v>
       </c>
       <c r="F42" t="s" s="2">
         <v>14</v>
@@ -1945,7 +2584,7 @@
         <v>14</v>
       </c>
       <c r="H42" t="s" s="2">
-        <v>30</v>
+        <v>36</v>
       </c>
       <c r="I42" t="s" s="2">
         <v>18</v>
@@ -1962,7 +2601,7 @@
         <v>14</v>
       </c>
       <c r="B43" t="s" s="2">
-        <v>32</v>
+        <v>42</v>
       </c>
       <c r="C43" t="s" s="2">
         <v>14</v>
@@ -1971,7 +2610,7 @@
         <v>14</v>
       </c>
       <c r="E43" t="s" s="2">
-        <v>14</v>
+        <v>73</v>
       </c>
       <c r="F43" t="s" s="2">
         <v>14</v>
@@ -1980,7 +2619,7 @@
         <v>14</v>
       </c>
       <c r="H43" t="s" s="2">
-        <v>30</v>
+        <v>36</v>
       </c>
       <c r="I43" t="s" s="2">
         <v>18</v>
@@ -1997,7 +2636,7 @@
         <v>14</v>
       </c>
       <c r="B44" t="s" s="2">
-        <v>32</v>
+        <v>42</v>
       </c>
       <c r="C44" t="s" s="2">
         <v>14</v>
@@ -2006,7 +2645,7 @@
         <v>14</v>
       </c>
       <c r="E44" t="s" s="2">
-        <v>14</v>
+        <v>74</v>
       </c>
       <c r="F44" t="s" s="2">
         <v>14</v>
@@ -2015,7 +2654,7 @@
         <v>14</v>
       </c>
       <c r="H44" t="s" s="2">
-        <v>30</v>
+        <v>36</v>
       </c>
       <c r="I44" t="s" s="2">
         <v>18</v>
@@ -2032,7 +2671,7 @@
         <v>14</v>
       </c>
       <c r="B45" t="s" s="2">
-        <v>32</v>
+        <v>42</v>
       </c>
       <c r="C45" t="s" s="2">
         <v>14</v>
@@ -2041,7 +2680,7 @@
         <v>14</v>
       </c>
       <c r="E45" t="s" s="2">
-        <v>14</v>
+        <v>75</v>
       </c>
       <c r="F45" t="s" s="2">
         <v>14</v>
@@ -2050,7 +2689,7 @@
         <v>14</v>
       </c>
       <c r="H45" t="s" s="2">
-        <v>30</v>
+        <v>36</v>
       </c>
       <c r="I45" t="s" s="2">
         <v>18</v>
@@ -2067,7 +2706,7 @@
         <v>14</v>
       </c>
       <c r="B46" t="s" s="2">
-        <v>32</v>
+        <v>42</v>
       </c>
       <c r="C46" t="s" s="2">
         <v>14</v>
@@ -2076,7 +2715,7 @@
         <v>14</v>
       </c>
       <c r="E46" t="s" s="2">
-        <v>14</v>
+        <v>76</v>
       </c>
       <c r="F46" t="s" s="2">
         <v>14</v>
@@ -2085,7 +2724,7 @@
         <v>14</v>
       </c>
       <c r="H46" t="s" s="2">
-        <v>30</v>
+        <v>36</v>
       </c>
       <c r="I46" t="s" s="2">
         <v>18</v>
@@ -2102,7 +2741,7 @@
         <v>14</v>
       </c>
       <c r="B47" t="s" s="2">
-        <v>32</v>
+        <v>42</v>
       </c>
       <c r="C47" t="s" s="2">
         <v>14</v>
@@ -2111,7 +2750,7 @@
         <v>14</v>
       </c>
       <c r="E47" t="s" s="2">
-        <v>14</v>
+        <v>77</v>
       </c>
       <c r="F47" t="s" s="2">
         <v>14</v>
@@ -2120,7 +2759,7 @@
         <v>14</v>
       </c>
       <c r="H47" t="s" s="2">
-        <v>30</v>
+        <v>36</v>
       </c>
       <c r="I47" t="s" s="2">
         <v>18</v>
@@ -2137,7 +2776,7 @@
         <v>14</v>
       </c>
       <c r="B48" t="s" s="2">
-        <v>32</v>
+        <v>42</v>
       </c>
       <c r="C48" t="s" s="2">
         <v>14</v>
@@ -2146,7 +2785,7 @@
         <v>14</v>
       </c>
       <c r="E48" t="s" s="2">
-        <v>14</v>
+        <v>78</v>
       </c>
       <c r="F48" t="s" s="2">
         <v>14</v>
@@ -2155,7 +2794,7 @@
         <v>14</v>
       </c>
       <c r="H48" t="s" s="2">
-        <v>30</v>
+        <v>36</v>
       </c>
       <c r="I48" t="s" s="2">
         <v>18</v>
@@ -2172,7 +2811,7 @@
         <v>14</v>
       </c>
       <c r="B49" t="s" s="2">
-        <v>32</v>
+        <v>42</v>
       </c>
       <c r="C49" t="s" s="2">
         <v>14</v>
@@ -2181,7 +2820,7 @@
         <v>14</v>
       </c>
       <c r="E49" t="s" s="2">
-        <v>14</v>
+        <v>79</v>
       </c>
       <c r="F49" t="s" s="2">
         <v>14</v>
@@ -2190,7 +2829,7 @@
         <v>14</v>
       </c>
       <c r="H49" t="s" s="2">
-        <v>30</v>
+        <v>36</v>
       </c>
       <c r="I49" t="s" s="2">
         <v>18</v>
@@ -2207,7 +2846,7 @@
         <v>14</v>
       </c>
       <c r="B50" t="s" s="2">
-        <v>32</v>
+        <v>42</v>
       </c>
       <c r="C50" t="s" s="2">
         <v>14</v>
@@ -2216,7 +2855,7 @@
         <v>14</v>
       </c>
       <c r="E50" t="s" s="2">
-        <v>14</v>
+        <v>80</v>
       </c>
       <c r="F50" t="s" s="2">
         <v>14</v>
@@ -2225,7 +2864,7 @@
         <v>14</v>
       </c>
       <c r="H50" t="s" s="2">
-        <v>30</v>
+        <v>36</v>
       </c>
       <c r="I50" t="s" s="2">
         <v>18</v>
@@ -2242,7 +2881,7 @@
         <v>14</v>
       </c>
       <c r="B51" t="s" s="2">
-        <v>32</v>
+        <v>42</v>
       </c>
       <c r="C51" t="s" s="2">
         <v>14</v>
@@ -2251,7 +2890,7 @@
         <v>14</v>
       </c>
       <c r="E51" t="s" s="2">
-        <v>14</v>
+        <v>81</v>
       </c>
       <c r="F51" t="s" s="2">
         <v>14</v>
@@ -2260,7 +2899,7 @@
         <v>14</v>
       </c>
       <c r="H51" t="s" s="2">
-        <v>30</v>
+        <v>36</v>
       </c>
       <c r="I51" t="s" s="2">
         <v>18</v>
@@ -2277,7 +2916,7 @@
         <v>14</v>
       </c>
       <c r="B52" t="s" s="2">
-        <v>32</v>
+        <v>42</v>
       </c>
       <c r="C52" t="s" s="2">
         <v>14</v>
@@ -2286,7 +2925,7 @@
         <v>14</v>
       </c>
       <c r="E52" t="s" s="2">
-        <v>14</v>
+        <v>82</v>
       </c>
       <c r="F52" t="s" s="2">
         <v>14</v>
@@ -2295,7 +2934,7 @@
         <v>14</v>
       </c>
       <c r="H52" t="s" s="2">
-        <v>30</v>
+        <v>36</v>
       </c>
       <c r="I52" t="s" s="2">
         <v>18</v>
@@ -2312,7 +2951,7 @@
         <v>14</v>
       </c>
       <c r="B53" t="s" s="2">
-        <v>32</v>
+        <v>42</v>
       </c>
       <c r="C53" t="s" s="2">
         <v>14</v>
@@ -2321,7 +2960,7 @@
         <v>14</v>
       </c>
       <c r="E53" t="s" s="2">
-        <v>14</v>
+        <v>83</v>
       </c>
       <c r="F53" t="s" s="2">
         <v>14</v>
@@ -2330,7 +2969,7 @@
         <v>14</v>
       </c>
       <c r="H53" t="s" s="2">
-        <v>30</v>
+        <v>84</v>
       </c>
       <c r="I53" t="s" s="2">
         <v>18</v>
@@ -2347,7 +2986,7 @@
         <v>14</v>
       </c>
       <c r="B54" t="s" s="2">
-        <v>32</v>
+        <v>42</v>
       </c>
       <c r="C54" t="s" s="2">
         <v>14</v>
@@ -2356,7 +2995,7 @@
         <v>14</v>
       </c>
       <c r="E54" t="s" s="2">
-        <v>14</v>
+        <v>85</v>
       </c>
       <c r="F54" t="s" s="2">
         <v>14</v>
@@ -2365,7 +3004,7 @@
         <v>14</v>
       </c>
       <c r="H54" t="s" s="2">
-        <v>33</v>
+        <v>36</v>
       </c>
       <c r="I54" t="s" s="2">
         <v>18</v>
@@ -2382,7 +3021,7 @@
         <v>14</v>
       </c>
       <c r="B55" t="s" s="2">
-        <v>32</v>
+        <v>42</v>
       </c>
       <c r="C55" t="s" s="2">
         <v>14</v>
@@ -2391,7 +3030,7 @@
         <v>14</v>
       </c>
       <c r="E55" t="s" s="2">
-        <v>14</v>
+        <v>86</v>
       </c>
       <c r="F55" t="s" s="2">
         <v>14</v>
@@ -2400,7 +3039,7 @@
         <v>14</v>
       </c>
       <c r="H55" t="s" s="2">
-        <v>30</v>
+        <v>36</v>
       </c>
       <c r="I55" t="s" s="2">
         <v>18</v>
@@ -2417,7 +3056,7 @@
         <v>14</v>
       </c>
       <c r="B56" t="s" s="2">
-        <v>32</v>
+        <v>42</v>
       </c>
       <c r="C56" t="s" s="2">
         <v>14</v>
@@ -2426,7 +3065,7 @@
         <v>14</v>
       </c>
       <c r="E56" t="s" s="2">
-        <v>14</v>
+        <v>87</v>
       </c>
       <c r="F56" t="s" s="2">
         <v>14</v>
@@ -2435,7 +3074,7 @@
         <v>14</v>
       </c>
       <c r="H56" t="s" s="2">
-        <v>30</v>
+        <v>36</v>
       </c>
       <c r="I56" t="s" s="2">
         <v>18</v>
@@ -2452,7 +3091,7 @@
         <v>14</v>
       </c>
       <c r="B57" t="s" s="2">
-        <v>32</v>
+        <v>42</v>
       </c>
       <c r="C57" t="s" s="2">
         <v>14</v>
@@ -2461,7 +3100,7 @@
         <v>14</v>
       </c>
       <c r="E57" t="s" s="2">
-        <v>14</v>
+        <v>88</v>
       </c>
       <c r="F57" t="s" s="2">
         <v>14</v>
@@ -2470,7 +3109,7 @@
         <v>14</v>
       </c>
       <c r="H57" t="s" s="2">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="I57" t="s" s="2">
         <v>18</v>
@@ -2487,7 +3126,7 @@
         <v>14</v>
       </c>
       <c r="B58" t="s" s="2">
-        <v>32</v>
+        <v>42</v>
       </c>
       <c r="C58" t="s" s="2">
         <v>14</v>
@@ -2496,7 +3135,7 @@
         <v>14</v>
       </c>
       <c r="E58" t="s" s="2">
-        <v>14</v>
+        <v>89</v>
       </c>
       <c r="F58" t="s" s="2">
         <v>14</v>
@@ -2505,7 +3144,7 @@
         <v>14</v>
       </c>
       <c r="H58" t="s" s="2">
-        <v>26</v>
+        <v>84</v>
       </c>
       <c r="I58" t="s" s="2">
         <v>18</v>
@@ -2522,7 +3161,7 @@
         <v>14</v>
       </c>
       <c r="B59" t="s" s="2">
-        <v>32</v>
+        <v>42</v>
       </c>
       <c r="C59" t="s" s="2">
         <v>14</v>
@@ -2531,7 +3170,7 @@
         <v>14</v>
       </c>
       <c r="E59" t="s" s="2">
-        <v>14</v>
+        <v>90</v>
       </c>
       <c r="F59" t="s" s="2">
         <v>14</v>
@@ -2540,7 +3179,7 @@
         <v>14</v>
       </c>
       <c r="H59" t="s" s="2">
-        <v>33</v>
+        <v>36</v>
       </c>
       <c r="I59" t="s" s="2">
         <v>18</v>
@@ -2557,7 +3196,7 @@
         <v>14</v>
       </c>
       <c r="B60" t="s" s="2">
-        <v>32</v>
+        <v>42</v>
       </c>
       <c r="C60" t="s" s="2">
         <v>14</v>
@@ -2566,7 +3205,7 @@
         <v>14</v>
       </c>
       <c r="E60" t="s" s="2">
-        <v>14</v>
+        <v>91</v>
       </c>
       <c r="F60" t="s" s="2">
         <v>14</v>
@@ -2575,7 +3214,7 @@
         <v>14</v>
       </c>
       <c r="H60" t="s" s="2">
-        <v>30</v>
+        <v>36</v>
       </c>
       <c r="I60" t="s" s="2">
         <v>18</v>
@@ -2592,7 +3231,7 @@
         <v>14</v>
       </c>
       <c r="B61" t="s" s="2">
-        <v>32</v>
+        <v>42</v>
       </c>
       <c r="C61" t="s" s="2">
         <v>14</v>
@@ -2601,7 +3240,7 @@
         <v>14</v>
       </c>
       <c r="E61" t="s" s="2">
-        <v>14</v>
+        <v>92</v>
       </c>
       <c r="F61" t="s" s="2">
         <v>14</v>
@@ -2610,7 +3249,7 @@
         <v>14</v>
       </c>
       <c r="H61" t="s" s="2">
-        <v>30</v>
+        <v>36</v>
       </c>
       <c r="I61" t="s" s="2">
         <v>18</v>
@@ -2627,7 +3266,7 @@
         <v>14</v>
       </c>
       <c r="B62" t="s" s="2">
-        <v>32</v>
+        <v>42</v>
       </c>
       <c r="C62" t="s" s="2">
         <v>14</v>
@@ -2636,7 +3275,7 @@
         <v>14</v>
       </c>
       <c r="E62" t="s" s="2">
-        <v>14</v>
+        <v>93</v>
       </c>
       <c r="F62" t="s" s="2">
         <v>14</v>
@@ -2645,7 +3284,7 @@
         <v>14</v>
       </c>
       <c r="H62" t="s" s="2">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="I62" t="s" s="2">
         <v>18</v>
@@ -2662,7 +3301,7 @@
         <v>14</v>
       </c>
       <c r="B63" t="s" s="2">
-        <v>32</v>
+        <v>42</v>
       </c>
       <c r="C63" t="s" s="2">
         <v>14</v>
@@ -2671,7 +3310,7 @@
         <v>14</v>
       </c>
       <c r="E63" t="s" s="2">
-        <v>14</v>
+        <v>94</v>
       </c>
       <c r="F63" t="s" s="2">
         <v>14</v>
@@ -2680,7 +3319,7 @@
         <v>14</v>
       </c>
       <c r="H63" t="s" s="2">
-        <v>26</v>
+        <v>36</v>
       </c>
       <c r="I63" t="s" s="2">
         <v>18</v>
@@ -2697,7 +3336,7 @@
         <v>14</v>
       </c>
       <c r="B64" t="s" s="2">
-        <v>32</v>
+        <v>42</v>
       </c>
       <c r="C64" t="s" s="2">
         <v>14</v>
@@ -2706,7 +3345,7 @@
         <v>14</v>
       </c>
       <c r="E64" t="s" s="2">
-        <v>14</v>
+        <v>95</v>
       </c>
       <c r="F64" t="s" s="2">
         <v>14</v>
@@ -2715,7 +3354,7 @@
         <v>14</v>
       </c>
       <c r="H64" t="s" s="2">
-        <v>30</v>
+        <v>36</v>
       </c>
       <c r="I64" t="s" s="2">
         <v>18</v>
@@ -2732,7 +3371,7 @@
         <v>14</v>
       </c>
       <c r="B65" t="s" s="2">
-        <v>32</v>
+        <v>42</v>
       </c>
       <c r="C65" t="s" s="2">
         <v>14</v>
@@ -2741,7 +3380,7 @@
         <v>14</v>
       </c>
       <c r="E65" t="s" s="2">
-        <v>14</v>
+        <v>96</v>
       </c>
       <c r="F65" t="s" s="2">
         <v>14</v>
@@ -2750,7 +3389,7 @@
         <v>14</v>
       </c>
       <c r="H65" t="s" s="2">
-        <v>30</v>
+        <v>36</v>
       </c>
       <c r="I65" t="s" s="2">
         <v>18</v>
@@ -2767,7 +3406,7 @@
         <v>14</v>
       </c>
       <c r="B66" t="s" s="2">
-        <v>32</v>
+        <v>42</v>
       </c>
       <c r="C66" t="s" s="2">
         <v>14</v>
@@ -2776,7 +3415,7 @@
         <v>14</v>
       </c>
       <c r="E66" t="s" s="2">
-        <v>14</v>
+        <v>97</v>
       </c>
       <c r="F66" t="s" s="2">
         <v>14</v>
@@ -2785,7 +3424,7 @@
         <v>14</v>
       </c>
       <c r="H66" t="s" s="2">
-        <v>30</v>
+        <v>36</v>
       </c>
       <c r="I66" t="s" s="2">
         <v>18</v>
@@ -2799,28 +3438,28 @@
     </row>
     <row r="67">
       <c r="A67" t="s" s="2">
-        <v>14</v>
+        <v>98</v>
       </c>
       <c r="B67" t="s" s="2">
-        <v>32</v>
+        <v>99</v>
       </c>
       <c r="C67" t="s" s="2">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="D67" t="s" s="2">
         <v>14</v>
       </c>
       <c r="E67" t="s" s="2">
-        <v>14</v>
+        <v>100</v>
       </c>
       <c r="F67" t="s" s="2">
         <v>14</v>
       </c>
       <c r="G67" t="s" s="2">
-        <v>14</v>
+        <v>22</v>
       </c>
       <c r="H67" t="s" s="2">
-        <v>30</v>
+        <v>34</v>
       </c>
       <c r="I67" t="s" s="2">
         <v>18</v>
@@ -2834,28 +3473,28 @@
     </row>
     <row r="68">
       <c r="A68" t="s" s="2">
-        <v>34</v>
+        <v>14</v>
       </c>
       <c r="B68" t="s" s="2">
-        <v>35</v>
+        <v>99</v>
       </c>
       <c r="C68" t="s" s="2">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="D68" t="s" s="2">
         <v>14</v>
       </c>
       <c r="E68" t="s" s="2">
-        <v>14</v>
+        <v>101</v>
       </c>
       <c r="F68" t="s" s="2">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="G68" t="s" s="2">
-        <v>21</v>
+        <v>14</v>
       </c>
       <c r="H68" t="s" s="2">
-        <v>29</v>
+        <v>36</v>
       </c>
       <c r="I68" t="s" s="2">
         <v>18</v>
@@ -2872,7 +3511,7 @@
         <v>14</v>
       </c>
       <c r="B69" t="s" s="2">
-        <v>35</v>
+        <v>99</v>
       </c>
       <c r="C69" t="s" s="2">
         <v>14</v>
@@ -2881,7 +3520,7 @@
         <v>14</v>
       </c>
       <c r="E69" t="s" s="2">
-        <v>14</v>
+        <v>102</v>
       </c>
       <c r="F69" t="s" s="2">
         <v>14</v>
@@ -2890,7 +3529,7 @@
         <v>14</v>
       </c>
       <c r="H69" t="s" s="2">
-        <v>30</v>
+        <v>36</v>
       </c>
       <c r="I69" t="s" s="2">
         <v>18</v>
@@ -2907,7 +3546,7 @@
         <v>14</v>
       </c>
       <c r="B70" t="s" s="2">
-        <v>35</v>
+        <v>99</v>
       </c>
       <c r="C70" t="s" s="2">
         <v>14</v>
@@ -2916,7 +3555,7 @@
         <v>14</v>
       </c>
       <c r="E70" t="s" s="2">
-        <v>14</v>
+        <v>103</v>
       </c>
       <c r="F70" t="s" s="2">
         <v>14</v>
@@ -2925,7 +3564,7 @@
         <v>14</v>
       </c>
       <c r="H70" t="s" s="2">
-        <v>30</v>
+        <v>36</v>
       </c>
       <c r="I70" t="s" s="2">
         <v>18</v>
@@ -2942,7 +3581,7 @@
         <v>14</v>
       </c>
       <c r="B71" t="s" s="2">
-        <v>35</v>
+        <v>99</v>
       </c>
       <c r="C71" t="s" s="2">
         <v>14</v>
@@ -2951,7 +3590,7 @@
         <v>14</v>
       </c>
       <c r="E71" t="s" s="2">
-        <v>14</v>
+        <v>104</v>
       </c>
       <c r="F71" t="s" s="2">
         <v>14</v>
@@ -2960,7 +3599,7 @@
         <v>14</v>
       </c>
       <c r="H71" t="s" s="2">
-        <v>30</v>
+        <v>36</v>
       </c>
       <c r="I71" t="s" s="2">
         <v>18</v>
@@ -2977,7 +3616,7 @@
         <v>14</v>
       </c>
       <c r="B72" t="s" s="2">
-        <v>35</v>
+        <v>99</v>
       </c>
       <c r="C72" t="s" s="2">
         <v>14</v>
@@ -2986,7 +3625,7 @@
         <v>14</v>
       </c>
       <c r="E72" t="s" s="2">
-        <v>14</v>
+        <v>105</v>
       </c>
       <c r="F72" t="s" s="2">
         <v>14</v>
@@ -2995,7 +3634,7 @@
         <v>14</v>
       </c>
       <c r="H72" t="s" s="2">
-        <v>30</v>
+        <v>36</v>
       </c>
       <c r="I72" t="s" s="2">
         <v>18</v>
@@ -3012,7 +3651,7 @@
         <v>14</v>
       </c>
       <c r="B73" t="s" s="2">
-        <v>35</v>
+        <v>99</v>
       </c>
       <c r="C73" t="s" s="2">
         <v>14</v>
@@ -3021,7 +3660,7 @@
         <v>14</v>
       </c>
       <c r="E73" t="s" s="2">
-        <v>14</v>
+        <v>106</v>
       </c>
       <c r="F73" t="s" s="2">
         <v>14</v>
@@ -3030,7 +3669,7 @@
         <v>14</v>
       </c>
       <c r="H73" t="s" s="2">
-        <v>30</v>
+        <v>36</v>
       </c>
       <c r="I73" t="s" s="2">
         <v>18</v>
@@ -3047,7 +3686,7 @@
         <v>14</v>
       </c>
       <c r="B74" t="s" s="2">
-        <v>35</v>
+        <v>99</v>
       </c>
       <c r="C74" t="s" s="2">
         <v>14</v>
@@ -3056,7 +3695,7 @@
         <v>14</v>
       </c>
       <c r="E74" t="s" s="2">
-        <v>14</v>
+        <v>107</v>
       </c>
       <c r="F74" t="s" s="2">
         <v>14</v>
@@ -3065,7 +3704,7 @@
         <v>14</v>
       </c>
       <c r="H74" t="s" s="2">
-        <v>30</v>
+        <v>36</v>
       </c>
       <c r="I74" t="s" s="2">
         <v>18</v>
@@ -3079,28 +3718,28 @@
     </row>
     <row r="75">
       <c r="A75" t="s" s="2">
-        <v>14</v>
+        <v>108</v>
       </c>
       <c r="B75" t="s" s="2">
-        <v>35</v>
+        <v>109</v>
       </c>
       <c r="C75" t="s" s="2">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="D75" t="s" s="2">
         <v>14</v>
       </c>
       <c r="E75" t="s" s="2">
-        <v>14</v>
+        <v>110</v>
       </c>
       <c r="F75" t="s" s="2">
         <v>14</v>
       </c>
       <c r="G75" t="s" s="2">
-        <v>14</v>
+        <v>22</v>
       </c>
       <c r="H75" t="s" s="2">
-        <v>30</v>
+        <v>34</v>
       </c>
       <c r="I75" t="s" s="2">
         <v>18</v>
@@ -3114,28 +3753,28 @@
     </row>
     <row r="76">
       <c r="A76" t="s" s="2">
-        <v>36</v>
+        <v>14</v>
       </c>
       <c r="B76" t="s" s="2">
-        <v>37</v>
+        <v>109</v>
       </c>
       <c r="C76" t="s" s="2">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="D76" t="s" s="2">
         <v>14</v>
       </c>
       <c r="E76" t="s" s="2">
-        <v>14</v>
+        <v>111</v>
       </c>
       <c r="F76" t="s" s="2">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="G76" t="s" s="2">
-        <v>21</v>
+        <v>14</v>
       </c>
       <c r="H76" t="s" s="2">
-        <v>29</v>
+        <v>36</v>
       </c>
       <c r="I76" t="s" s="2">
         <v>18</v>
@@ -3152,7 +3791,7 @@
         <v>14</v>
       </c>
       <c r="B77" t="s" s="2">
-        <v>37</v>
+        <v>109</v>
       </c>
       <c r="C77" t="s" s="2">
         <v>14</v>
@@ -3161,7 +3800,7 @@
         <v>14</v>
       </c>
       <c r="E77" t="s" s="2">
-        <v>14</v>
+        <v>112</v>
       </c>
       <c r="F77" t="s" s="2">
         <v>14</v>
@@ -3170,7 +3809,7 @@
         <v>14</v>
       </c>
       <c r="H77" t="s" s="2">
-        <v>30</v>
+        <v>36</v>
       </c>
       <c r="I77" t="s" s="2">
         <v>18</v>
@@ -3187,7 +3826,7 @@
         <v>14</v>
       </c>
       <c r="B78" t="s" s="2">
-        <v>37</v>
+        <v>109</v>
       </c>
       <c r="C78" t="s" s="2">
         <v>14</v>
@@ -3196,7 +3835,7 @@
         <v>14</v>
       </c>
       <c r="E78" t="s" s="2">
-        <v>14</v>
+        <v>113</v>
       </c>
       <c r="F78" t="s" s="2">
         <v>14</v>
@@ -3205,7 +3844,7 @@
         <v>14</v>
       </c>
       <c r="H78" t="s" s="2">
-        <v>30</v>
+        <v>36</v>
       </c>
       <c r="I78" t="s" s="2">
         <v>18</v>
@@ -3222,7 +3861,7 @@
         <v>14</v>
       </c>
       <c r="B79" t="s" s="2">
-        <v>37</v>
+        <v>109</v>
       </c>
       <c r="C79" t="s" s="2">
         <v>14</v>
@@ -3231,7 +3870,7 @@
         <v>14</v>
       </c>
       <c r="E79" t="s" s="2">
-        <v>14</v>
+        <v>114</v>
       </c>
       <c r="F79" t="s" s="2">
         <v>14</v>
@@ -3240,7 +3879,7 @@
         <v>14</v>
       </c>
       <c r="H79" t="s" s="2">
-        <v>30</v>
+        <v>36</v>
       </c>
       <c r="I79" t="s" s="2">
         <v>18</v>
@@ -3257,7 +3896,7 @@
         <v>14</v>
       </c>
       <c r="B80" t="s" s="2">
-        <v>37</v>
+        <v>109</v>
       </c>
       <c r="C80" t="s" s="2">
         <v>14</v>
@@ -3266,7 +3905,7 @@
         <v>14</v>
       </c>
       <c r="E80" t="s" s="2">
-        <v>14</v>
+        <v>115</v>
       </c>
       <c r="F80" t="s" s="2">
         <v>14</v>
@@ -3275,7 +3914,7 @@
         <v>14</v>
       </c>
       <c r="H80" t="s" s="2">
-        <v>30</v>
+        <v>36</v>
       </c>
       <c r="I80" t="s" s="2">
         <v>18</v>
@@ -3292,7 +3931,7 @@
         <v>14</v>
       </c>
       <c r="B81" t="s" s="2">
-        <v>37</v>
+        <v>109</v>
       </c>
       <c r="C81" t="s" s="2">
         <v>14</v>
@@ -3301,7 +3940,7 @@
         <v>14</v>
       </c>
       <c r="E81" t="s" s="2">
-        <v>14</v>
+        <v>116</v>
       </c>
       <c r="F81" t="s" s="2">
         <v>14</v>
@@ -3310,7 +3949,7 @@
         <v>14</v>
       </c>
       <c r="H81" t="s" s="2">
-        <v>30</v>
+        <v>36</v>
       </c>
       <c r="I81" t="s" s="2">
         <v>18</v>
@@ -3327,7 +3966,7 @@
         <v>14</v>
       </c>
       <c r="B82" t="s" s="2">
-        <v>37</v>
+        <v>109</v>
       </c>
       <c r="C82" t="s" s="2">
         <v>14</v>
@@ -3336,7 +3975,7 @@
         <v>14</v>
       </c>
       <c r="E82" t="s" s="2">
-        <v>14</v>
+        <v>117</v>
       </c>
       <c r="F82" t="s" s="2">
         <v>14</v>
@@ -3345,7 +3984,7 @@
         <v>14</v>
       </c>
       <c r="H82" t="s" s="2">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="I82" t="s" s="2">
         <v>18</v>
@@ -3362,7 +4001,7 @@
         <v>14</v>
       </c>
       <c r="B83" t="s" s="2">
-        <v>37</v>
+        <v>109</v>
       </c>
       <c r="C83" t="s" s="2">
         <v>14</v>
@@ -3371,7 +4010,7 @@
         <v>14</v>
       </c>
       <c r="E83" t="s" s="2">
-        <v>14</v>
+        <v>118</v>
       </c>
       <c r="F83" t="s" s="2">
         <v>14</v>
@@ -3380,7 +4019,7 @@
         <v>14</v>
       </c>
       <c r="H83" t="s" s="2">
-        <v>26</v>
+        <v>36</v>
       </c>
       <c r="I83" t="s" s="2">
         <v>18</v>
@@ -3397,7 +4036,7 @@
         <v>14</v>
       </c>
       <c r="B84" t="s" s="2">
-        <v>37</v>
+        <v>109</v>
       </c>
       <c r="C84" t="s" s="2">
         <v>14</v>
@@ -3406,7 +4045,7 @@
         <v>14</v>
       </c>
       <c r="E84" t="s" s="2">
-        <v>14</v>
+        <v>119</v>
       </c>
       <c r="F84" t="s" s="2">
         <v>14</v>
@@ -3415,7 +4054,7 @@
         <v>14</v>
       </c>
       <c r="H84" t="s" s="2">
-        <v>30</v>
+        <v>36</v>
       </c>
       <c r="I84" t="s" s="2">
         <v>18</v>
@@ -3432,7 +4071,7 @@
         <v>14</v>
       </c>
       <c r="B85" t="s" s="2">
-        <v>37</v>
+        <v>109</v>
       </c>
       <c r="C85" t="s" s="2">
         <v>14</v>
@@ -3441,7 +4080,7 @@
         <v>14</v>
       </c>
       <c r="E85" t="s" s="2">
-        <v>14</v>
+        <v>120</v>
       </c>
       <c r="F85" t="s" s="2">
         <v>14</v>
@@ -3450,7 +4089,7 @@
         <v>14</v>
       </c>
       <c r="H85" t="s" s="2">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="I85" t="s" s="2">
         <v>18</v>
@@ -3467,7 +4106,7 @@
         <v>14</v>
       </c>
       <c r="B86" t="s" s="2">
-        <v>37</v>
+        <v>109</v>
       </c>
       <c r="C86" t="s" s="2">
         <v>14</v>
@@ -3476,7 +4115,7 @@
         <v>14</v>
       </c>
       <c r="E86" t="s" s="2">
-        <v>14</v>
+        <v>121</v>
       </c>
       <c r="F86" t="s" s="2">
         <v>14</v>
@@ -3485,7 +4124,7 @@
         <v>14</v>
       </c>
       <c r="H86" t="s" s="2">
-        <v>26</v>
+        <v>84</v>
       </c>
       <c r="I86" t="s" s="2">
         <v>18</v>
@@ -3502,7 +4141,7 @@
         <v>14</v>
       </c>
       <c r="B87" t="s" s="2">
-        <v>37</v>
+        <v>109</v>
       </c>
       <c r="C87" t="s" s="2">
         <v>14</v>
@@ -3511,7 +4150,7 @@
         <v>14</v>
       </c>
       <c r="E87" t="s" s="2">
-        <v>14</v>
+        <v>122</v>
       </c>
       <c r="F87" t="s" s="2">
         <v>14</v>
@@ -3520,7 +4159,7 @@
         <v>14</v>
       </c>
       <c r="H87" t="s" s="2">
-        <v>33</v>
+        <v>36</v>
       </c>
       <c r="I87" t="s" s="2">
         <v>18</v>
@@ -3537,7 +4176,7 @@
         <v>14</v>
       </c>
       <c r="B88" t="s" s="2">
-        <v>37</v>
+        <v>109</v>
       </c>
       <c r="C88" t="s" s="2">
         <v>14</v>
@@ -3546,7 +4185,7 @@
         <v>14</v>
       </c>
       <c r="E88" t="s" s="2">
-        <v>14</v>
+        <v>123</v>
       </c>
       <c r="F88" t="s" s="2">
         <v>14</v>
@@ -3555,7 +4194,7 @@
         <v>14</v>
       </c>
       <c r="H88" t="s" s="2">
-        <v>30</v>
+        <v>36</v>
       </c>
       <c r="I88" t="s" s="2">
         <v>18</v>
@@ -3572,7 +4211,7 @@
         <v>14</v>
       </c>
       <c r="B89" t="s" s="2">
-        <v>37</v>
+        <v>109</v>
       </c>
       <c r="C89" t="s" s="2">
         <v>14</v>
@@ -3581,7 +4220,7 @@
         <v>14</v>
       </c>
       <c r="E89" t="s" s="2">
-        <v>14</v>
+        <v>124</v>
       </c>
       <c r="F89" t="s" s="2">
         <v>14</v>
@@ -3590,7 +4229,7 @@
         <v>14</v>
       </c>
       <c r="H89" t="s" s="2">
-        <v>30</v>
+        <v>36</v>
       </c>
       <c r="I89" t="s" s="2">
         <v>18</v>
@@ -3607,7 +4246,7 @@
         <v>14</v>
       </c>
       <c r="B90" t="s" s="2">
-        <v>37</v>
+        <v>109</v>
       </c>
       <c r="C90" t="s" s="2">
         <v>14</v>
@@ -3616,7 +4255,7 @@
         <v>14</v>
       </c>
       <c r="E90" t="s" s="2">
-        <v>14</v>
+        <v>125</v>
       </c>
       <c r="F90" t="s" s="2">
         <v>14</v>
@@ -3625,7 +4264,7 @@
         <v>14</v>
       </c>
       <c r="H90" t="s" s="2">
-        <v>30</v>
+        <v>36</v>
       </c>
       <c r="I90" t="s" s="2">
         <v>18</v>
@@ -3642,7 +4281,7 @@
         <v>14</v>
       </c>
       <c r="B91" t="s" s="2">
-        <v>37</v>
+        <v>109</v>
       </c>
       <c r="C91" t="s" s="2">
         <v>14</v>
@@ -3651,7 +4290,7 @@
         <v>14</v>
       </c>
       <c r="E91" t="s" s="2">
-        <v>14</v>
+        <v>126</v>
       </c>
       <c r="F91" t="s" s="2">
         <v>14</v>
@@ -3660,7 +4299,7 @@
         <v>14</v>
       </c>
       <c r="H91" t="s" s="2">
-        <v>30</v>
+        <v>36</v>
       </c>
       <c r="I91" t="s" s="2">
         <v>18</v>
@@ -3677,7 +4316,7 @@
         <v>14</v>
       </c>
       <c r="B92" t="s" s="2">
-        <v>37</v>
+        <v>109</v>
       </c>
       <c r="C92" t="s" s="2">
         <v>14</v>
@@ -3686,7 +4325,7 @@
         <v>14</v>
       </c>
       <c r="E92" t="s" s="2">
-        <v>14</v>
+        <v>127</v>
       </c>
       <c r="F92" t="s" s="2">
         <v>14</v>
@@ -3695,7 +4334,7 @@
         <v>14</v>
       </c>
       <c r="H92" t="s" s="2">
-        <v>30</v>
+        <v>36</v>
       </c>
       <c r="I92" t="s" s="2">
         <v>18</v>
@@ -3712,7 +4351,7 @@
         <v>14</v>
       </c>
       <c r="B93" t="s" s="2">
-        <v>37</v>
+        <v>109</v>
       </c>
       <c r="C93" t="s" s="2">
         <v>14</v>
@@ -3721,7 +4360,7 @@
         <v>14</v>
       </c>
       <c r="E93" t="s" s="2">
-        <v>14</v>
+        <v>128</v>
       </c>
       <c r="F93" t="s" s="2">
         <v>14</v>
@@ -3730,7 +4369,7 @@
         <v>14</v>
       </c>
       <c r="H93" t="s" s="2">
-        <v>30</v>
+        <v>36</v>
       </c>
       <c r="I93" t="s" s="2">
         <v>18</v>
@@ -3747,7 +4386,7 @@
         <v>14</v>
       </c>
       <c r="B94" t="s" s="2">
-        <v>37</v>
+        <v>109</v>
       </c>
       <c r="C94" t="s" s="2">
         <v>14</v>
@@ -3756,7 +4395,7 @@
         <v>14</v>
       </c>
       <c r="E94" t="s" s="2">
-        <v>14</v>
+        <v>129</v>
       </c>
       <c r="F94" t="s" s="2">
         <v>14</v>
@@ -3765,7 +4404,7 @@
         <v>14</v>
       </c>
       <c r="H94" t="s" s="2">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="I94" t="s" s="2">
         <v>18</v>
@@ -3779,28 +4418,28 @@
     </row>
     <row r="95">
       <c r="A95" t="s" s="2">
-        <v>14</v>
+        <v>130</v>
       </c>
       <c r="B95" t="s" s="2">
-        <v>37</v>
+        <v>131</v>
       </c>
       <c r="C95" t="s" s="2">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="D95" t="s" s="2">
         <v>14</v>
       </c>
       <c r="E95" t="s" s="2">
-        <v>14</v>
+        <v>132</v>
       </c>
       <c r="F95" t="s" s="2">
         <v>14</v>
       </c>
       <c r="G95" t="s" s="2">
-        <v>14</v>
+        <v>22</v>
       </c>
       <c r="H95" t="s" s="2">
-        <v>26</v>
+        <v>34</v>
       </c>
       <c r="I95" t="s" s="2">
         <v>18</v>
@@ -3814,28 +4453,28 @@
     </row>
     <row r="96">
       <c r="A96" t="s" s="2">
-        <v>38</v>
+        <v>14</v>
       </c>
       <c r="B96" t="s" s="2">
-        <v>39</v>
+        <v>131</v>
       </c>
       <c r="C96" t="s" s="2">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="D96" t="s" s="2">
         <v>14</v>
       </c>
       <c r="E96" t="s" s="2">
-        <v>14</v>
+        <v>133</v>
       </c>
       <c r="F96" t="s" s="2">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="G96" t="s" s="2">
-        <v>21</v>
+        <v>14</v>
       </c>
       <c r="H96" t="s" s="2">
-        <v>29</v>
+        <v>36</v>
       </c>
       <c r="I96" t="s" s="2">
         <v>18</v>
@@ -3852,7 +4491,7 @@
         <v>14</v>
       </c>
       <c r="B97" t="s" s="2">
-        <v>39</v>
+        <v>131</v>
       </c>
       <c r="C97" t="s" s="2">
         <v>14</v>
@@ -3861,7 +4500,7 @@
         <v>14</v>
       </c>
       <c r="E97" t="s" s="2">
-        <v>14</v>
+        <v>134</v>
       </c>
       <c r="F97" t="s" s="2">
         <v>14</v>
@@ -3870,7 +4509,7 @@
         <v>14</v>
       </c>
       <c r="H97" t="s" s="2">
-        <v>30</v>
+        <v>36</v>
       </c>
       <c r="I97" t="s" s="2">
         <v>18</v>
@@ -3887,7 +4526,7 @@
         <v>14</v>
       </c>
       <c r="B98" t="s" s="2">
-        <v>39</v>
+        <v>131</v>
       </c>
       <c r="C98" t="s" s="2">
         <v>14</v>
@@ -3896,7 +4535,7 @@
         <v>14</v>
       </c>
       <c r="E98" t="s" s="2">
-        <v>14</v>
+        <v>135</v>
       </c>
       <c r="F98" t="s" s="2">
         <v>14</v>
@@ -3905,7 +4544,7 @@
         <v>14</v>
       </c>
       <c r="H98" t="s" s="2">
-        <v>30</v>
+        <v>36</v>
       </c>
       <c r="I98" t="s" s="2">
         <v>18</v>
@@ -3922,7 +4561,7 @@
         <v>14</v>
       </c>
       <c r="B99" t="s" s="2">
-        <v>39</v>
+        <v>131</v>
       </c>
       <c r="C99" t="s" s="2">
         <v>14</v>
@@ -3931,7 +4570,7 @@
         <v>14</v>
       </c>
       <c r="E99" t="s" s="2">
-        <v>14</v>
+        <v>136</v>
       </c>
       <c r="F99" t="s" s="2">
         <v>14</v>
@@ -3940,7 +4579,7 @@
         <v>14</v>
       </c>
       <c r="H99" t="s" s="2">
-        <v>30</v>
+        <v>84</v>
       </c>
       <c r="I99" t="s" s="2">
         <v>18</v>
@@ -3957,7 +4596,7 @@
         <v>14</v>
       </c>
       <c r="B100" t="s" s="2">
-        <v>39</v>
+        <v>131</v>
       </c>
       <c r="C100" t="s" s="2">
         <v>14</v>
@@ -3966,7 +4605,7 @@
         <v>14</v>
       </c>
       <c r="E100" t="s" s="2">
-        <v>14</v>
+        <v>137</v>
       </c>
       <c r="F100" t="s" s="2">
         <v>14</v>
@@ -3975,7 +4614,7 @@
         <v>14</v>
       </c>
       <c r="H100" t="s" s="2">
-        <v>33</v>
+        <v>36</v>
       </c>
       <c r="I100" t="s" s="2">
         <v>18</v>
@@ -3992,7 +4631,7 @@
         <v>14</v>
       </c>
       <c r="B101" t="s" s="2">
-        <v>39</v>
+        <v>131</v>
       </c>
       <c r="C101" t="s" s="2">
         <v>14</v>
@@ -4001,7 +4640,7 @@
         <v>14</v>
       </c>
       <c r="E101" t="s" s="2">
-        <v>14</v>
+        <v>114</v>
       </c>
       <c r="F101" t="s" s="2">
         <v>14</v>
@@ -4010,7 +4649,7 @@
         <v>14</v>
       </c>
       <c r="H101" t="s" s="2">
-        <v>30</v>
+        <v>36</v>
       </c>
       <c r="I101" t="s" s="2">
         <v>18</v>
@@ -4024,28 +4663,28 @@
     </row>
     <row r="102">
       <c r="A102" t="s" s="2">
-        <v>14</v>
+        <v>138</v>
       </c>
       <c r="B102" t="s" s="2">
-        <v>39</v>
+        <v>139</v>
       </c>
       <c r="C102" t="s" s="2">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="D102" t="s" s="2">
         <v>14</v>
       </c>
       <c r="E102" t="s" s="2">
-        <v>14</v>
+        <v>140</v>
       </c>
       <c r="F102" t="s" s="2">
         <v>14</v>
       </c>
       <c r="G102" t="s" s="2">
-        <v>14</v>
+        <v>22</v>
       </c>
       <c r="H102" t="s" s="2">
-        <v>30</v>
+        <v>34</v>
       </c>
       <c r="I102" t="s" s="2">
         <v>18</v>
@@ -4059,28 +4698,28 @@
     </row>
     <row r="103">
       <c r="A103" t="s" s="2">
-        <v>40</v>
+        <v>14</v>
       </c>
       <c r="B103" t="s" s="2">
-        <v>41</v>
+        <v>139</v>
       </c>
       <c r="C103" t="s" s="2">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="D103" t="s" s="2">
         <v>14</v>
       </c>
       <c r="E103" t="s" s="2">
-        <v>14</v>
+        <v>141</v>
       </c>
       <c r="F103" t="s" s="2">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="G103" t="s" s="2">
-        <v>21</v>
+        <v>14</v>
       </c>
       <c r="H103" t="s" s="2">
-        <v>29</v>
+        <v>36</v>
       </c>
       <c r="I103" t="s" s="2">
         <v>18</v>
@@ -4097,7 +4736,7 @@
         <v>14</v>
       </c>
       <c r="B104" t="s" s="2">
-        <v>41</v>
+        <v>139</v>
       </c>
       <c r="C104" t="s" s="2">
         <v>14</v>
@@ -4106,7 +4745,7 @@
         <v>14</v>
       </c>
       <c r="E104" t="s" s="2">
-        <v>14</v>
+        <v>142</v>
       </c>
       <c r="F104" t="s" s="2">
         <v>14</v>
@@ -4115,7 +4754,7 @@
         <v>14</v>
       </c>
       <c r="H104" t="s" s="2">
-        <v>30</v>
+        <v>36</v>
       </c>
       <c r="I104" t="s" s="2">
         <v>18</v>
@@ -4132,7 +4771,7 @@
         <v>14</v>
       </c>
       <c r="B105" t="s" s="2">
-        <v>41</v>
+        <v>139</v>
       </c>
       <c r="C105" t="s" s="2">
         <v>14</v>
@@ -4141,7 +4780,7 @@
         <v>14</v>
       </c>
       <c r="E105" t="s" s="2">
-        <v>14</v>
+        <v>143</v>
       </c>
       <c r="F105" t="s" s="2">
         <v>14</v>
@@ -4150,7 +4789,7 @@
         <v>14</v>
       </c>
       <c r="H105" t="s" s="2">
-        <v>30</v>
+        <v>36</v>
       </c>
       <c r="I105" t="s" s="2">
         <v>18</v>
@@ -4167,7 +4806,7 @@
         <v>14</v>
       </c>
       <c r="B106" t="s" s="2">
-        <v>41</v>
+        <v>139</v>
       </c>
       <c r="C106" t="s" s="2">
         <v>14</v>
@@ -4176,7 +4815,7 @@
         <v>14</v>
       </c>
       <c r="E106" t="s" s="2">
-        <v>14</v>
+        <v>144</v>
       </c>
       <c r="F106" t="s" s="2">
         <v>14</v>
@@ -4185,7 +4824,7 @@
         <v>14</v>
       </c>
       <c r="H106" t="s" s="2">
-        <v>30</v>
+        <v>36</v>
       </c>
       <c r="I106" t="s" s="2">
         <v>18</v>
@@ -4202,7 +4841,7 @@
         <v>14</v>
       </c>
       <c r="B107" t="s" s="2">
-        <v>41</v>
+        <v>139</v>
       </c>
       <c r="C107" t="s" s="2">
         <v>14</v>
@@ -4211,7 +4850,7 @@
         <v>14</v>
       </c>
       <c r="E107" t="s" s="2">
-        <v>14</v>
+        <v>145</v>
       </c>
       <c r="F107" t="s" s="2">
         <v>14</v>
@@ -4220,7 +4859,7 @@
         <v>14</v>
       </c>
       <c r="H107" t="s" s="2">
-        <v>30</v>
+        <v>36</v>
       </c>
       <c r="I107" t="s" s="2">
         <v>18</v>
@@ -4237,7 +4876,7 @@
         <v>14</v>
       </c>
       <c r="B108" t="s" s="2">
-        <v>41</v>
+        <v>139</v>
       </c>
       <c r="C108" t="s" s="2">
         <v>14</v>
@@ -4246,7 +4885,7 @@
         <v>14</v>
       </c>
       <c r="E108" t="s" s="2">
-        <v>14</v>
+        <v>146</v>
       </c>
       <c r="F108" t="s" s="2">
         <v>14</v>
@@ -4255,7 +4894,7 @@
         <v>14</v>
       </c>
       <c r="H108" t="s" s="2">
-        <v>30</v>
+        <v>36</v>
       </c>
       <c r="I108" t="s" s="2">
         <v>18</v>
@@ -4272,7 +4911,7 @@
         <v>14</v>
       </c>
       <c r="B109" t="s" s="2">
-        <v>41</v>
+        <v>139</v>
       </c>
       <c r="C109" t="s" s="2">
         <v>14</v>
@@ -4281,7 +4920,7 @@
         <v>14</v>
       </c>
       <c r="E109" t="s" s="2">
-        <v>14</v>
+        <v>147</v>
       </c>
       <c r="F109" t="s" s="2">
         <v>14</v>
@@ -4290,7 +4929,7 @@
         <v>14</v>
       </c>
       <c r="H109" t="s" s="2">
-        <v>30</v>
+        <v>36</v>
       </c>
       <c r="I109" t="s" s="2">
         <v>18</v>
@@ -4304,28 +4943,28 @@
     </row>
     <row r="110">
       <c r="A110" t="s" s="2">
-        <v>14</v>
+        <v>148</v>
       </c>
       <c r="B110" t="s" s="2">
-        <v>41</v>
+        <v>149</v>
       </c>
       <c r="C110" t="s" s="2">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="D110" t="s" s="2">
         <v>14</v>
       </c>
       <c r="E110" t="s" s="2">
-        <v>14</v>
+        <v>150</v>
       </c>
       <c r="F110" t="s" s="2">
         <v>14</v>
       </c>
       <c r="G110" t="s" s="2">
-        <v>14</v>
+        <v>16</v>
       </c>
       <c r="H110" t="s" s="2">
-        <v>30</v>
+        <v>14</v>
       </c>
       <c r="I110" t="s" s="2">
         <v>18</v>
@@ -4339,28 +4978,28 @@
     </row>
     <row r="111">
       <c r="A111" t="s" s="2">
-        <v>42</v>
+        <v>14</v>
       </c>
       <c r="B111" t="s" s="2">
-        <v>43</v>
+        <v>149</v>
       </c>
       <c r="C111" t="s" s="2">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="D111" t="s" s="2">
         <v>14</v>
       </c>
       <c r="E111" t="s" s="2">
-        <v>14</v>
+        <v>151</v>
       </c>
       <c r="F111" t="s" s="2">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="G111" t="s" s="2">
-        <v>16</v>
+        <v>14</v>
       </c>
       <c r="H111" t="s" s="2">
-        <v>14</v>
+        <v>29</v>
       </c>
       <c r="I111" t="s" s="2">
         <v>18</v>
@@ -4377,7 +5016,7 @@
         <v>14</v>
       </c>
       <c r="B112" t="s" s="2">
-        <v>43</v>
+        <v>149</v>
       </c>
       <c r="C112" t="s" s="2">
         <v>14</v>
@@ -4386,7 +5025,7 @@
         <v>14</v>
       </c>
       <c r="E112" t="s" s="2">
-        <v>14</v>
+        <v>152</v>
       </c>
       <c r="F112" t="s" s="2">
         <v>14</v>
@@ -4395,7 +5034,7 @@
         <v>14</v>
       </c>
       <c r="H112" t="s" s="2">
-        <v>26</v>
+        <v>29</v>
       </c>
       <c r="I112" t="s" s="2">
         <v>18</v>
@@ -4412,7 +5051,7 @@
         <v>14</v>
       </c>
       <c r="B113" t="s" s="2">
-        <v>43</v>
+        <v>149</v>
       </c>
       <c r="C113" t="s" s="2">
         <v>14</v>
@@ -4421,7 +5060,7 @@
         <v>14</v>
       </c>
       <c r="E113" t="s" s="2">
-        <v>14</v>
+        <v>153</v>
       </c>
       <c r="F113" t="s" s="2">
         <v>14</v>
@@ -4430,7 +5069,7 @@
         <v>14</v>
       </c>
       <c r="H113" t="s" s="2">
-        <v>30</v>
+        <v>36</v>
       </c>
       <c r="I113" t="s" s="2">
         <v>18</v>
@@ -4447,7 +5086,7 @@
         <v>14</v>
       </c>
       <c r="B114" t="s" s="2">
-        <v>43</v>
+        <v>149</v>
       </c>
       <c r="C114" t="s" s="2">
         <v>14</v>
@@ -4456,7 +5095,7 @@
         <v>14</v>
       </c>
       <c r="E114" t="s" s="2">
-        <v>14</v>
+        <v>154</v>
       </c>
       <c r="F114" t="s" s="2">
         <v>14</v>
@@ -4465,7 +5104,7 @@
         <v>14</v>
       </c>
       <c r="H114" t="s" s="2">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="I114" t="s" s="2">
         <v>18</v>
@@ -4482,7 +5121,7 @@
         <v>14</v>
       </c>
       <c r="B115" t="s" s="2">
-        <v>43</v>
+        <v>149</v>
       </c>
       <c r="C115" t="s" s="2">
         <v>14</v>
@@ -4491,7 +5130,7 @@
         <v>14</v>
       </c>
       <c r="E115" t="s" s="2">
-        <v>14</v>
+        <v>155</v>
       </c>
       <c r="F115" t="s" s="2">
         <v>14</v>
@@ -4500,7 +5139,7 @@
         <v>14</v>
       </c>
       <c r="H115" t="s" s="2">
-        <v>26</v>
+        <v>36</v>
       </c>
       <c r="I115" t="s" s="2">
         <v>18</v>
@@ -4514,28 +5153,28 @@
     </row>
     <row r="116">
       <c r="A116" t="s" s="2">
-        <v>44</v>
+        <v>14</v>
       </c>
       <c r="B116" t="s" s="2">
-        <v>45</v>
+        <v>149</v>
       </c>
       <c r="C116" t="s" s="2">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="D116" t="s" s="2">
         <v>14</v>
       </c>
       <c r="E116" t="s" s="2">
-        <v>14</v>
+        <v>156</v>
       </c>
       <c r="F116" t="s" s="2">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="G116" t="s" s="2">
-        <v>16</v>
+        <v>14</v>
       </c>
       <c r="H116" t="s" s="2">
-        <v>14</v>
+        <v>29</v>
       </c>
       <c r="I116" t="s" s="2">
         <v>18</v>
@@ -4549,28 +5188,28 @@
     </row>
     <row r="117">
       <c r="A117" t="s" s="2">
-        <v>46</v>
+        <v>14</v>
       </c>
       <c r="B117" t="s" s="2">
-        <v>47</v>
+        <v>149</v>
       </c>
       <c r="C117" t="s" s="2">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="D117" t="s" s="2">
         <v>14</v>
       </c>
       <c r="E117" t="s" s="2">
-        <v>48</v>
+        <v>157</v>
       </c>
       <c r="F117" t="s" s="2">
         <v>14</v>
       </c>
       <c r="G117" t="s" s="2">
-        <v>21</v>
+        <v>14</v>
       </c>
       <c r="H117" t="s" s="2">
-        <v>22</v>
+        <v>29</v>
       </c>
       <c r="I117" t="s" s="2">
         <v>18</v>
@@ -4584,10 +5223,10 @@
     </row>
     <row r="118">
       <c r="A118" t="s" s="2">
-        <v>49</v>
+        <v>158</v>
       </c>
       <c r="B118" t="s" s="2">
-        <v>50</v>
+        <v>159</v>
       </c>
       <c r="C118" t="s" s="2">
         <v>13</v>
@@ -4596,16 +5235,16 @@
         <v>14</v>
       </c>
       <c r="E118" t="s" s="2">
-        <v>14</v>
+        <v>160</v>
       </c>
       <c r="F118" t="s" s="2">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="G118" t="s" s="2">
-        <v>21</v>
+        <v>16</v>
       </c>
       <c r="H118" t="s" s="2">
-        <v>29</v>
+        <v>14</v>
       </c>
       <c r="I118" t="s" s="2">
         <v>18</v>
@@ -4619,28 +5258,28 @@
     </row>
     <row r="119">
       <c r="A119" t="s" s="2">
-        <v>14</v>
+        <v>161</v>
       </c>
       <c r="B119" t="s" s="2">
-        <v>50</v>
+        <v>162</v>
       </c>
       <c r="C119" t="s" s="2">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="D119" t="s" s="2">
         <v>14</v>
       </c>
       <c r="E119" t="s" s="2">
-        <v>14</v>
+        <v>163</v>
       </c>
       <c r="F119" t="s" s="2">
         <v>14</v>
       </c>
       <c r="G119" t="s" s="2">
-        <v>14</v>
+        <v>22</v>
       </c>
       <c r="H119" t="s" s="2">
-        <v>26</v>
+        <v>23</v>
       </c>
       <c r="I119" t="s" s="2">
         <v>18</v>
@@ -4654,28 +5293,28 @@
     </row>
     <row r="120">
       <c r="A120" t="s" s="2">
-        <v>14</v>
+        <v>164</v>
       </c>
       <c r="B120" t="s" s="2">
-        <v>50</v>
+        <v>165</v>
       </c>
       <c r="C120" t="s" s="2">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="D120" t="s" s="2">
         <v>14</v>
       </c>
       <c r="E120" t="s" s="2">
-        <v>14</v>
+        <v>166</v>
       </c>
       <c r="F120" t="s" s="2">
         <v>14</v>
       </c>
       <c r="G120" t="s" s="2">
-        <v>14</v>
+        <v>22</v>
       </c>
       <c r="H120" t="s" s="2">
-        <v>26</v>
+        <v>34</v>
       </c>
       <c r="I120" t="s" s="2">
         <v>18</v>
@@ -4692,7 +5331,7 @@
         <v>14</v>
       </c>
       <c r="B121" t="s" s="2">
-        <v>50</v>
+        <v>165</v>
       </c>
       <c r="C121" t="s" s="2">
         <v>14</v>
@@ -4701,7 +5340,7 @@
         <v>14</v>
       </c>
       <c r="E121" t="s" s="2">
-        <v>14</v>
+        <v>167</v>
       </c>
       <c r="F121" t="s" s="2">
         <v>14</v>
@@ -4710,7 +5349,7 @@
         <v>14</v>
       </c>
       <c r="H121" t="s" s="2">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="I121" t="s" s="2">
         <v>18</v>
@@ -4727,7 +5366,7 @@
         <v>14</v>
       </c>
       <c r="B122" t="s" s="2">
-        <v>50</v>
+        <v>165</v>
       </c>
       <c r="C122" t="s" s="2">
         <v>14</v>
@@ -4736,7 +5375,7 @@
         <v>14</v>
       </c>
       <c r="E122" t="s" s="2">
-        <v>14</v>
+        <v>168</v>
       </c>
       <c r="F122" t="s" s="2">
         <v>14</v>
@@ -4745,7 +5384,7 @@
         <v>14</v>
       </c>
       <c r="H122" t="s" s="2">
-        <v>33</v>
+        <v>29</v>
       </c>
       <c r="I122" t="s" s="2">
         <v>18</v>
@@ -4762,7 +5401,7 @@
         <v>14</v>
       </c>
       <c r="B123" t="s" s="2">
-        <v>50</v>
+        <v>165</v>
       </c>
       <c r="C123" t="s" s="2">
         <v>14</v>
@@ -4771,7 +5410,7 @@
         <v>14</v>
       </c>
       <c r="E123" t="s" s="2">
-        <v>14</v>
+        <v>169</v>
       </c>
       <c r="F123" t="s" s="2">
         <v>14</v>
@@ -4780,7 +5419,7 @@
         <v>14</v>
       </c>
       <c r="H123" t="s" s="2">
-        <v>30</v>
+        <v>36</v>
       </c>
       <c r="I123" t="s" s="2">
         <v>18</v>
@@ -4797,7 +5436,7 @@
         <v>14</v>
       </c>
       <c r="B124" t="s" s="2">
-        <v>50</v>
+        <v>165</v>
       </c>
       <c r="C124" t="s" s="2">
         <v>14</v>
@@ -4806,7 +5445,7 @@
         <v>14</v>
       </c>
       <c r="E124" t="s" s="2">
-        <v>14</v>
+        <v>170</v>
       </c>
       <c r="F124" t="s" s="2">
         <v>14</v>
@@ -4815,7 +5454,7 @@
         <v>14</v>
       </c>
       <c r="H124" t="s" s="2">
-        <v>30</v>
+        <v>84</v>
       </c>
       <c r="I124" t="s" s="2">
         <v>18</v>
@@ -4832,7 +5471,7 @@
         <v>14</v>
       </c>
       <c r="B125" t="s" s="2">
-        <v>50</v>
+        <v>165</v>
       </c>
       <c r="C125" t="s" s="2">
         <v>14</v>
@@ -4841,7 +5480,7 @@
         <v>14</v>
       </c>
       <c r="E125" t="s" s="2">
-        <v>14</v>
+        <v>171</v>
       </c>
       <c r="F125" t="s" s="2">
         <v>14</v>
@@ -4850,7 +5489,7 @@
         <v>14</v>
       </c>
       <c r="H125" t="s" s="2">
-        <v>33</v>
+        <v>36</v>
       </c>
       <c r="I125" t="s" s="2">
         <v>18</v>
@@ -4864,28 +5503,28 @@
     </row>
     <row r="126">
       <c r="A126" t="s" s="2">
-        <v>51</v>
+        <v>14</v>
       </c>
       <c r="B126" t="s" s="2">
-        <v>52</v>
+        <v>165</v>
       </c>
       <c r="C126" t="s" s="2">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="D126" t="s" s="2">
         <v>14</v>
       </c>
       <c r="E126" t="s" s="2">
-        <v>14</v>
+        <v>172</v>
       </c>
       <c r="F126" t="s" s="2">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="G126" t="s" s="2">
-        <v>16</v>
+        <v>14</v>
       </c>
       <c r="H126" t="s" s="2">
-        <v>14</v>
+        <v>36</v>
       </c>
       <c r="I126" t="s" s="2">
         <v>18</v>
@@ -4902,7 +5541,7 @@
         <v>14</v>
       </c>
       <c r="B127" t="s" s="2">
-        <v>52</v>
+        <v>165</v>
       </c>
       <c r="C127" t="s" s="2">
         <v>14</v>
@@ -4911,7 +5550,7 @@
         <v>14</v>
       </c>
       <c r="E127" t="s" s="2">
-        <v>14</v>
+        <v>173</v>
       </c>
       <c r="F127" t="s" s="2">
         <v>14</v>
@@ -4920,7 +5559,7 @@
         <v>14</v>
       </c>
       <c r="H127" t="s" s="2">
-        <v>26</v>
+        <v>84</v>
       </c>
       <c r="I127" t="s" s="2">
         <v>18</v>
@@ -4934,28 +5573,28 @@
     </row>
     <row r="128">
       <c r="A128" t="s" s="2">
-        <v>14</v>
+        <v>174</v>
       </c>
       <c r="B128" t="s" s="2">
-        <v>52</v>
+        <v>175</v>
       </c>
       <c r="C128" t="s" s="2">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="D128" t="s" s="2">
         <v>14</v>
       </c>
       <c r="E128" t="s" s="2">
-        <v>14</v>
+        <v>176</v>
       </c>
       <c r="F128" t="s" s="2">
         <v>14</v>
       </c>
       <c r="G128" t="s" s="2">
-        <v>14</v>
+        <v>16</v>
       </c>
       <c r="H128" t="s" s="2">
-        <v>26</v>
+        <v>14</v>
       </c>
       <c r="I128" t="s" s="2">
         <v>18</v>
@@ -4969,28 +5608,28 @@
     </row>
     <row r="129">
       <c r="A129" t="s" s="2">
-        <v>53</v>
+        <v>14</v>
       </c>
       <c r="B129" t="s" s="2">
-        <v>54</v>
+        <v>175</v>
       </c>
       <c r="C129" t="s" s="2">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="D129" t="s" s="2">
         <v>14</v>
       </c>
       <c r="E129" t="s" s="2">
-        <v>14</v>
+        <v>30</v>
       </c>
       <c r="F129" t="s" s="2">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="G129" t="s" s="2">
-        <v>16</v>
+        <v>14</v>
       </c>
       <c r="H129" t="s" s="2">
-        <v>55</v>
+        <v>29</v>
       </c>
       <c r="I129" t="s" s="2">
         <v>18</v>
@@ -5004,25 +5643,25 @@
     </row>
     <row r="130">
       <c r="A130" t="s" s="2">
-        <v>56</v>
+        <v>14</v>
       </c>
       <c r="B130" t="s" s="2">
-        <v>57</v>
+        <v>175</v>
       </c>
       <c r="C130" t="s" s="2">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="D130" t="s" s="2">
         <v>14</v>
       </c>
       <c r="E130" t="s" s="2">
-        <v>14</v>
+        <v>28</v>
       </c>
       <c r="F130" t="s" s="2">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="G130" t="s" s="2">
-        <v>16</v>
+        <v>14</v>
       </c>
       <c r="H130" t="s" s="2">
         <v>29</v>
@@ -5039,28 +5678,28 @@
     </row>
     <row r="131">
       <c r="A131" t="s" s="2">
-        <v>14</v>
+        <v>177</v>
       </c>
       <c r="B131" t="s" s="2">
-        <v>57</v>
+        <v>178</v>
       </c>
       <c r="C131" t="s" s="2">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="D131" t="s" s="2">
         <v>14</v>
       </c>
       <c r="E131" t="s" s="2">
-        <v>14</v>
+        <v>179</v>
       </c>
       <c r="F131" t="s" s="2">
         <v>14</v>
       </c>
       <c r="G131" t="s" s="2">
-        <v>14</v>
+        <v>16</v>
       </c>
       <c r="H131" t="s" s="2">
-        <v>26</v>
+        <v>180</v>
       </c>
       <c r="I131" t="s" s="2">
         <v>18</v>
@@ -5074,28 +5713,28 @@
     </row>
     <row r="132">
       <c r="A132" t="s" s="2">
-        <v>14</v>
+        <v>181</v>
       </c>
       <c r="B132" t="s" s="2">
-        <v>57</v>
+        <v>182</v>
       </c>
       <c r="C132" t="s" s="2">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="D132" t="s" s="2">
         <v>14</v>
       </c>
       <c r="E132" t="s" s="2">
-        <v>14</v>
+        <v>183</v>
       </c>
       <c r="F132" t="s" s="2">
         <v>14</v>
       </c>
       <c r="G132" t="s" s="2">
-        <v>14</v>
+        <v>16</v>
       </c>
       <c r="H132" t="s" s="2">
-        <v>26</v>
+        <v>34</v>
       </c>
       <c r="I132" t="s" s="2">
         <v>18</v>
@@ -5109,25 +5748,25 @@
     </row>
     <row r="133">
       <c r="A133" t="s" s="2">
-        <v>58</v>
+        <v>14</v>
       </c>
       <c r="B133" t="s" s="2">
-        <v>59</v>
+        <v>182</v>
       </c>
       <c r="C133" t="s" s="2">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="D133" t="s" s="2">
         <v>14</v>
       </c>
       <c r="E133" t="s" s="2">
-        <v>14</v>
+        <v>184</v>
       </c>
       <c r="F133" t="s" s="2">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="G133" t="s" s="2">
-        <v>21</v>
+        <v>14</v>
       </c>
       <c r="H133" t="s" s="2">
         <v>29</v>
@@ -5147,7 +5786,7 @@
         <v>14</v>
       </c>
       <c r="B134" t="s" s="2">
-        <v>59</v>
+        <v>182</v>
       </c>
       <c r="C134" t="s" s="2">
         <v>14</v>
@@ -5156,7 +5795,7 @@
         <v>14</v>
       </c>
       <c r="E134" t="s" s="2">
-        <v>14</v>
+        <v>185</v>
       </c>
       <c r="F134" t="s" s="2">
         <v>14</v>
@@ -5165,7 +5804,7 @@
         <v>14</v>
       </c>
       <c r="H134" t="s" s="2">
-        <v>33</v>
+        <v>29</v>
       </c>
       <c r="I134" t="s" s="2">
         <v>18</v>
@@ -5179,28 +5818,28 @@
     </row>
     <row r="135">
       <c r="A135" t="s" s="2">
-        <v>14</v>
+        <v>186</v>
       </c>
       <c r="B135" t="s" s="2">
-        <v>59</v>
+        <v>187</v>
       </c>
       <c r="C135" t="s" s="2">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="D135" t="s" s="2">
         <v>14</v>
       </c>
       <c r="E135" t="s" s="2">
-        <v>14</v>
+        <v>188</v>
       </c>
       <c r="F135" t="s" s="2">
         <v>14</v>
       </c>
       <c r="G135" t="s" s="2">
-        <v>14</v>
+        <v>22</v>
       </c>
       <c r="H135" t="s" s="2">
-        <v>30</v>
+        <v>34</v>
       </c>
       <c r="I135" t="s" s="2">
         <v>18</v>
@@ -5217,7 +5856,7 @@
         <v>14</v>
       </c>
       <c r="B136" t="s" s="2">
-        <v>59</v>
+        <v>187</v>
       </c>
       <c r="C136" t="s" s="2">
         <v>14</v>
@@ -5226,7 +5865,7 @@
         <v>14</v>
       </c>
       <c r="E136" t="s" s="2">
-        <v>14</v>
+        <v>189</v>
       </c>
       <c r="F136" t="s" s="2">
         <v>14</v>
@@ -5235,7 +5874,7 @@
         <v>14</v>
       </c>
       <c r="H136" t="s" s="2">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="I136" t="s" s="2">
         <v>18</v>
@@ -5252,7 +5891,7 @@
         <v>14</v>
       </c>
       <c r="B137" t="s" s="2">
-        <v>59</v>
+        <v>187</v>
       </c>
       <c r="C137" t="s" s="2">
         <v>14</v>
@@ -5261,7 +5900,7 @@
         <v>14</v>
       </c>
       <c r="E137" t="s" s="2">
-        <v>14</v>
+        <v>190</v>
       </c>
       <c r="F137" t="s" s="2">
         <v>14</v>
@@ -5270,7 +5909,7 @@
         <v>14</v>
       </c>
       <c r="H137" t="s" s="2">
-        <v>30</v>
+        <v>36</v>
       </c>
       <c r="I137" t="s" s="2">
         <v>18</v>
@@ -5287,7 +5926,7 @@
         <v>14</v>
       </c>
       <c r="B138" t="s" s="2">
-        <v>59</v>
+        <v>187</v>
       </c>
       <c r="C138" t="s" s="2">
         <v>14</v>
@@ -5296,7 +5935,7 @@
         <v>14</v>
       </c>
       <c r="E138" t="s" s="2">
-        <v>14</v>
+        <v>191</v>
       </c>
       <c r="F138" t="s" s="2">
         <v>14</v>
@@ -5305,7 +5944,7 @@
         <v>14</v>
       </c>
       <c r="H138" t="s" s="2">
-        <v>26</v>
+        <v>36</v>
       </c>
       <c r="I138" t="s" s="2">
         <v>18</v>
@@ -5322,7 +5961,7 @@
         <v>14</v>
       </c>
       <c r="B139" t="s" s="2">
-        <v>59</v>
+        <v>187</v>
       </c>
       <c r="C139" t="s" s="2">
         <v>14</v>
@@ -5331,7 +5970,7 @@
         <v>14</v>
       </c>
       <c r="E139" t="s" s="2">
-        <v>14</v>
+        <v>192</v>
       </c>
       <c r="F139" t="s" s="2">
         <v>14</v>
@@ -5340,7 +5979,7 @@
         <v>14</v>
       </c>
       <c r="H139" t="s" s="2">
-        <v>26</v>
+        <v>36</v>
       </c>
       <c r="I139" t="s" s="2">
         <v>18</v>
@@ -5357,7 +5996,7 @@
         <v>14</v>
       </c>
       <c r="B140" t="s" s="2">
-        <v>59</v>
+        <v>187</v>
       </c>
       <c r="C140" t="s" s="2">
         <v>14</v>
@@ -5366,7 +6005,7 @@
         <v>14</v>
       </c>
       <c r="E140" t="s" s="2">
-        <v>14</v>
+        <v>193</v>
       </c>
       <c r="F140" t="s" s="2">
         <v>14</v>
@@ -5375,7 +6014,7 @@
         <v>14</v>
       </c>
       <c r="H140" t="s" s="2">
-        <v>26</v>
+        <v>29</v>
       </c>
       <c r="I140" t="s" s="2">
         <v>18</v>
@@ -5392,7 +6031,7 @@
         <v>14</v>
       </c>
       <c r="B141" t="s" s="2">
-        <v>59</v>
+        <v>187</v>
       </c>
       <c r="C141" t="s" s="2">
         <v>14</v>
@@ -5401,7 +6040,7 @@
         <v>14</v>
       </c>
       <c r="E141" t="s" s="2">
-        <v>14</v>
+        <v>194</v>
       </c>
       <c r="F141" t="s" s="2">
         <v>14</v>
@@ -5410,7 +6049,7 @@
         <v>14</v>
       </c>
       <c r="H141" t="s" s="2">
-        <v>26</v>
+        <v>195</v>
       </c>
       <c r="I141" t="s" s="2">
         <v>18</v>
@@ -5427,7 +6066,7 @@
         <v>14</v>
       </c>
       <c r="B142" t="s" s="2">
-        <v>59</v>
+        <v>187</v>
       </c>
       <c r="C142" t="s" s="2">
         <v>14</v>
@@ -5436,7 +6075,7 @@
         <v>14</v>
       </c>
       <c r="E142" t="s" s="2">
-        <v>14</v>
+        <v>196</v>
       </c>
       <c r="F142" t="s" s="2">
         <v>14</v>
@@ -5445,7 +6084,7 @@
         <v>14</v>
       </c>
       <c r="H142" t="s" s="2">
-        <v>30</v>
+        <v>36</v>
       </c>
       <c r="I142" t="s" s="2">
         <v>18</v>
@@ -5462,7 +6101,7 @@
         <v>14</v>
       </c>
       <c r="B143" t="s" s="2">
-        <v>59</v>
+        <v>187</v>
       </c>
       <c r="C143" t="s" s="2">
         <v>14</v>
@@ -5471,7 +6110,7 @@
         <v>14</v>
       </c>
       <c r="E143" t="s" s="2">
-        <v>14</v>
+        <v>197</v>
       </c>
       <c r="F143" t="s" s="2">
         <v>14</v>
@@ -5480,7 +6119,7 @@
         <v>14</v>
       </c>
       <c r="H143" t="s" s="2">
-        <v>30</v>
+        <v>36</v>
       </c>
       <c r="I143" t="s" s="2">
         <v>18</v>
@@ -5497,7 +6136,7 @@
         <v>14</v>
       </c>
       <c r="B144" t="s" s="2">
-        <v>59</v>
+        <v>187</v>
       </c>
       <c r="C144" t="s" s="2">
         <v>14</v>
@@ -5506,7 +6145,7 @@
         <v>14</v>
       </c>
       <c r="E144" t="s" s="2">
-        <v>14</v>
+        <v>198</v>
       </c>
       <c r="F144" t="s" s="2">
         <v>14</v>
@@ -5515,7 +6154,7 @@
         <v>14</v>
       </c>
       <c r="H144" t="s" s="2">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="I144" t="s" s="2">
         <v>18</v>
@@ -5532,7 +6171,7 @@
         <v>14</v>
       </c>
       <c r="B145" t="s" s="2">
-        <v>59</v>
+        <v>187</v>
       </c>
       <c r="C145" t="s" s="2">
         <v>14</v>
@@ -5541,7 +6180,7 @@
         <v>14</v>
       </c>
       <c r="E145" t="s" s="2">
-        <v>14</v>
+        <v>199</v>
       </c>
       <c r="F145" t="s" s="2">
         <v>14</v>
@@ -5550,7 +6189,7 @@
         <v>14</v>
       </c>
       <c r="H145" t="s" s="2">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="I145" t="s" s="2">
         <v>18</v>
@@ -5567,7 +6206,7 @@
         <v>14</v>
       </c>
       <c r="B146" t="s" s="2">
-        <v>59</v>
+        <v>187</v>
       </c>
       <c r="C146" t="s" s="2">
         <v>14</v>
@@ -5576,7 +6215,7 @@
         <v>14</v>
       </c>
       <c r="E146" t="s" s="2">
-        <v>14</v>
+        <v>200</v>
       </c>
       <c r="F146" t="s" s="2">
         <v>14</v>
@@ -5585,7 +6224,7 @@
         <v>14</v>
       </c>
       <c r="H146" t="s" s="2">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="I146" t="s" s="2">
         <v>18</v>
@@ -5602,7 +6241,7 @@
         <v>14</v>
       </c>
       <c r="B147" t="s" s="2">
-        <v>59</v>
+        <v>187</v>
       </c>
       <c r="C147" t="s" s="2">
         <v>14</v>
@@ -5611,7 +6250,7 @@
         <v>14</v>
       </c>
       <c r="E147" t="s" s="2">
-        <v>14</v>
+        <v>201</v>
       </c>
       <c r="F147" t="s" s="2">
         <v>14</v>
@@ -5620,7 +6259,7 @@
         <v>14</v>
       </c>
       <c r="H147" t="s" s="2">
-        <v>26</v>
+        <v>29</v>
       </c>
       <c r="I147" t="s" s="2">
         <v>18</v>
@@ -5637,7 +6276,7 @@
         <v>14</v>
       </c>
       <c r="B148" t="s" s="2">
-        <v>59</v>
+        <v>187</v>
       </c>
       <c r="C148" t="s" s="2">
         <v>14</v>
@@ -5646,7 +6285,7 @@
         <v>14</v>
       </c>
       <c r="E148" t="s" s="2">
-        <v>14</v>
+        <v>202</v>
       </c>
       <c r="F148" t="s" s="2">
         <v>14</v>
@@ -5655,7 +6294,7 @@
         <v>14</v>
       </c>
       <c r="H148" t="s" s="2">
-        <v>30</v>
+        <v>36</v>
       </c>
       <c r="I148" t="s" s="2">
         <v>18</v>
@@ -5672,7 +6311,7 @@
         <v>14</v>
       </c>
       <c r="B149" t="s" s="2">
-        <v>59</v>
+        <v>187</v>
       </c>
       <c r="C149" t="s" s="2">
         <v>14</v>
@@ -5681,7 +6320,7 @@
         <v>14</v>
       </c>
       <c r="E149" t="s" s="2">
-        <v>14</v>
+        <v>203</v>
       </c>
       <c r="F149" t="s" s="2">
         <v>14</v>
@@ -5690,7 +6329,7 @@
         <v>14</v>
       </c>
       <c r="H149" t="s" s="2">
-        <v>30</v>
+        <v>36</v>
       </c>
       <c r="I149" t="s" s="2">
         <v>18</v>
@@ -5707,7 +6346,7 @@
         <v>14</v>
       </c>
       <c r="B150" t="s" s="2">
-        <v>59</v>
+        <v>187</v>
       </c>
       <c r="C150" t="s" s="2">
         <v>14</v>
@@ -5716,7 +6355,7 @@
         <v>14</v>
       </c>
       <c r="E150" t="s" s="2">
-        <v>14</v>
+        <v>204</v>
       </c>
       <c r="F150" t="s" s="2">
         <v>14</v>
@@ -5725,7 +6364,7 @@
         <v>14</v>
       </c>
       <c r="H150" t="s" s="2">
-        <v>30</v>
+        <v>36</v>
       </c>
       <c r="I150" t="s" s="2">
         <v>18</v>
@@ -5742,7 +6381,7 @@
         <v>14</v>
       </c>
       <c r="B151" t="s" s="2">
-        <v>59</v>
+        <v>187</v>
       </c>
       <c r="C151" t="s" s="2">
         <v>14</v>
@@ -5751,7 +6390,7 @@
         <v>14</v>
       </c>
       <c r="E151" t="s" s="2">
-        <v>14</v>
+        <v>205</v>
       </c>
       <c r="F151" t="s" s="2">
         <v>14</v>
@@ -5760,7 +6399,7 @@
         <v>14</v>
       </c>
       <c r="H151" t="s" s="2">
-        <v>26</v>
+        <v>36</v>
       </c>
       <c r="I151" t="s" s="2">
         <v>18</v>
@@ -5777,7 +6416,7 @@
         <v>14</v>
       </c>
       <c r="B152" t="s" s="2">
-        <v>59</v>
+        <v>187</v>
       </c>
       <c r="C152" t="s" s="2">
         <v>14</v>
@@ -5786,7 +6425,7 @@
         <v>14</v>
       </c>
       <c r="E152" t="s" s="2">
-        <v>14</v>
+        <v>206</v>
       </c>
       <c r="F152" t="s" s="2">
         <v>14</v>
@@ -5795,7 +6434,7 @@
         <v>14</v>
       </c>
       <c r="H152" t="s" s="2">
-        <v>30</v>
+        <v>36</v>
       </c>
       <c r="I152" t="s" s="2">
         <v>18</v>
@@ -5809,25 +6448,25 @@
     </row>
     <row r="153">
       <c r="A153" t="s" s="2">
-        <v>60</v>
+        <v>14</v>
       </c>
       <c r="B153" t="s" s="2">
-        <v>61</v>
+        <v>187</v>
       </c>
       <c r="C153" t="s" s="2">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="D153" t="s" s="2">
         <v>14</v>
       </c>
       <c r="E153" t="s" s="2">
-        <v>62</v>
+        <v>207</v>
       </c>
       <c r="F153" t="s" s="2">
         <v>14</v>
       </c>
       <c r="G153" t="s" s="2">
-        <v>21</v>
+        <v>14</v>
       </c>
       <c r="H153" t="s" s="2">
         <v>29</v>
@@ -5847,7 +6486,7 @@
         <v>14</v>
       </c>
       <c r="B154" t="s" s="2">
-        <v>61</v>
+        <v>187</v>
       </c>
       <c r="C154" t="s" s="2">
         <v>14</v>
@@ -5856,7 +6495,7 @@
         <v>14</v>
       </c>
       <c r="E154" t="s" s="2">
-        <v>63</v>
+        <v>208</v>
       </c>
       <c r="F154" t="s" s="2">
         <v>14</v>
@@ -5865,7 +6504,7 @@
         <v>14</v>
       </c>
       <c r="H154" t="s" s="2">
-        <v>30</v>
+        <v>36</v>
       </c>
       <c r="I154" t="s" s="2">
         <v>18</v>
@@ -5882,7 +6521,7 @@
         <v>14</v>
       </c>
       <c r="B155" t="s" s="2">
-        <v>61</v>
+        <v>187</v>
       </c>
       <c r="C155" t="s" s="2">
         <v>14</v>
@@ -5891,7 +6530,7 @@
         <v>14</v>
       </c>
       <c r="E155" t="s" s="2">
-        <v>64</v>
+        <v>209</v>
       </c>
       <c r="F155" t="s" s="2">
         <v>14</v>
@@ -5900,7 +6539,7 @@
         <v>14</v>
       </c>
       <c r="H155" t="s" s="2">
-        <v>30</v>
+        <v>36</v>
       </c>
       <c r="I155" t="s" s="2">
         <v>18</v>
@@ -5917,7 +6556,7 @@
         <v>14</v>
       </c>
       <c r="B156" t="s" s="2">
-        <v>61</v>
+        <v>187</v>
       </c>
       <c r="C156" t="s" s="2">
         <v>14</v>
@@ -5926,7 +6565,7 @@
         <v>14</v>
       </c>
       <c r="E156" t="s" s="2">
-        <v>14</v>
+        <v>210</v>
       </c>
       <c r="F156" t="s" s="2">
         <v>14</v>
@@ -5935,7 +6574,7 @@
         <v>14</v>
       </c>
       <c r="H156" t="s" s="2">
-        <v>30</v>
+        <v>36</v>
       </c>
       <c r="I156" t="s" s="2">
         <v>18</v>
@@ -5952,7 +6591,7 @@
         <v>14</v>
       </c>
       <c r="B157" t="s" s="2">
-        <v>61</v>
+        <v>187</v>
       </c>
       <c r="C157" t="s" s="2">
         <v>14</v>
@@ -5961,7 +6600,7 @@
         <v>14</v>
       </c>
       <c r="E157" t="s" s="2">
-        <v>14</v>
+        <v>28</v>
       </c>
       <c r="F157" t="s" s="2">
         <v>14</v>
@@ -5970,7 +6609,7 @@
         <v>14</v>
       </c>
       <c r="H157" t="s" s="2">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="I157" t="s" s="2">
         <v>18</v>
@@ -5987,7 +6626,7 @@
         <v>14</v>
       </c>
       <c r="B158" t="s" s="2">
-        <v>61</v>
+        <v>187</v>
       </c>
       <c r="C158" t="s" s="2">
         <v>14</v>
@@ -5996,7 +6635,7 @@
         <v>14</v>
       </c>
       <c r="E158" t="s" s="2">
-        <v>65</v>
+        <v>211</v>
       </c>
       <c r="F158" t="s" s="2">
         <v>14</v>
@@ -6005,7 +6644,7 @@
         <v>14</v>
       </c>
       <c r="H158" t="s" s="2">
-        <v>30</v>
+        <v>36</v>
       </c>
       <c r="I158" t="s" s="2">
         <v>18</v>
@@ -6019,28 +6658,28 @@
     </row>
     <row r="159">
       <c r="A159" t="s" s="2">
-        <v>14</v>
+        <v>212</v>
       </c>
       <c r="B159" t="s" s="2">
-        <v>61</v>
+        <v>213</v>
       </c>
       <c r="C159" t="s" s="2">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="D159" t="s" s="2">
         <v>14</v>
       </c>
       <c r="E159" t="s" s="2">
-        <v>66</v>
+        <v>214</v>
       </c>
       <c r="F159" t="s" s="2">
         <v>14</v>
       </c>
       <c r="G159" t="s" s="2">
-        <v>14</v>
+        <v>22</v>
       </c>
       <c r="H159" t="s" s="2">
-        <v>30</v>
+        <v>34</v>
       </c>
       <c r="I159" t="s" s="2">
         <v>18</v>
@@ -6057,7 +6696,7 @@
         <v>14</v>
       </c>
       <c r="B160" t="s" s="2">
-        <v>61</v>
+        <v>213</v>
       </c>
       <c r="C160" t="s" s="2">
         <v>14</v>
@@ -6066,7 +6705,7 @@
         <v>14</v>
       </c>
       <c r="E160" t="s" s="2">
-        <v>67</v>
+        <v>215</v>
       </c>
       <c r="F160" t="s" s="2">
         <v>14</v>
@@ -6075,7 +6714,7 @@
         <v>14</v>
       </c>
       <c r="H160" t="s" s="2">
-        <v>30</v>
+        <v>36</v>
       </c>
       <c r="I160" t="s" s="2">
         <v>18</v>
@@ -6092,7 +6731,7 @@
         <v>14</v>
       </c>
       <c r="B161" t="s" s="2">
-        <v>61</v>
+        <v>213</v>
       </c>
       <c r="C161" t="s" s="2">
         <v>14</v>
@@ -6101,7 +6740,7 @@
         <v>14</v>
       </c>
       <c r="E161" t="s" s="2">
-        <v>68</v>
+        <v>216</v>
       </c>
       <c r="F161" t="s" s="2">
         <v>14</v>
@@ -6110,7 +6749,7 @@
         <v>14</v>
       </c>
       <c r="H161" t="s" s="2">
-        <v>30</v>
+        <v>36</v>
       </c>
       <c r="I161" t="s" s="2">
         <v>18</v>
@@ -6127,7 +6766,7 @@
         <v>14</v>
       </c>
       <c r="B162" t="s" s="2">
-        <v>61</v>
+        <v>213</v>
       </c>
       <c r="C162" t="s" s="2">
         <v>14</v>
@@ -6136,7 +6775,7 @@
         <v>14</v>
       </c>
       <c r="E162" t="s" s="2">
-        <v>69</v>
+        <v>217</v>
       </c>
       <c r="F162" t="s" s="2">
         <v>14</v>
@@ -6145,7 +6784,7 @@
         <v>14</v>
       </c>
       <c r="H162" t="s" s="2">
-        <v>30</v>
+        <v>36</v>
       </c>
       <c r="I162" t="s" s="2">
         <v>18</v>
@@ -6162,7 +6801,7 @@
         <v>14</v>
       </c>
       <c r="B163" t="s" s="2">
-        <v>61</v>
+        <v>213</v>
       </c>
       <c r="C163" t="s" s="2">
         <v>14</v>
@@ -6171,7 +6810,7 @@
         <v>14</v>
       </c>
       <c r="E163" t="s" s="2">
-        <v>70</v>
+        <v>218</v>
       </c>
       <c r="F163" t="s" s="2">
         <v>14</v>
@@ -6180,7 +6819,7 @@
         <v>14</v>
       </c>
       <c r="H163" t="s" s="2">
-        <v>30</v>
+        <v>36</v>
       </c>
       <c r="I163" t="s" s="2">
         <v>18</v>
@@ -6197,7 +6836,7 @@
         <v>14</v>
       </c>
       <c r="B164" t="s" s="2">
-        <v>61</v>
+        <v>213</v>
       </c>
       <c r="C164" t="s" s="2">
         <v>14</v>
@@ -6206,7 +6845,7 @@
         <v>14</v>
       </c>
       <c r="E164" t="s" s="2">
-        <v>71</v>
+        <v>219</v>
       </c>
       <c r="F164" t="s" s="2">
         <v>14</v>
@@ -6215,7 +6854,7 @@
         <v>14</v>
       </c>
       <c r="H164" t="s" s="2">
-        <v>30</v>
+        <v>36</v>
       </c>
       <c r="I164" t="s" s="2">
         <v>18</v>
@@ -6232,7 +6871,7 @@
         <v>14</v>
       </c>
       <c r="B165" t="s" s="2">
-        <v>61</v>
+        <v>213</v>
       </c>
       <c r="C165" t="s" s="2">
         <v>14</v>
@@ -6241,7 +6880,7 @@
         <v>14</v>
       </c>
       <c r="E165" t="s" s="2">
-        <v>72</v>
+        <v>220</v>
       </c>
       <c r="F165" t="s" s="2">
         <v>14</v>
@@ -6250,7 +6889,7 @@
         <v>14</v>
       </c>
       <c r="H165" t="s" s="2">
-        <v>30</v>
+        <v>36</v>
       </c>
       <c r="I165" t="s" s="2">
         <v>18</v>
@@ -6267,7 +6906,7 @@
         <v>14</v>
       </c>
       <c r="B166" t="s" s="2">
-        <v>61</v>
+        <v>213</v>
       </c>
       <c r="C166" t="s" s="2">
         <v>14</v>
@@ -6276,7 +6915,7 @@
         <v>14</v>
       </c>
       <c r="E166" t="s" s="2">
-        <v>73</v>
+        <v>221</v>
       </c>
       <c r="F166" t="s" s="2">
         <v>14</v>
@@ -6285,7 +6924,7 @@
         <v>14</v>
       </c>
       <c r="H166" t="s" s="2">
-        <v>30</v>
+        <v>36</v>
       </c>
       <c r="I166" t="s" s="2">
         <v>18</v>
@@ -6302,7 +6941,7 @@
         <v>14</v>
       </c>
       <c r="B167" t="s" s="2">
-        <v>61</v>
+        <v>213</v>
       </c>
       <c r="C167" t="s" s="2">
         <v>14</v>
@@ -6311,7 +6950,7 @@
         <v>14</v>
       </c>
       <c r="E167" t="s" s="2">
-        <v>14</v>
+        <v>222</v>
       </c>
       <c r="F167" t="s" s="2">
         <v>14</v>
@@ -6320,7 +6959,7 @@
         <v>14</v>
       </c>
       <c r="H167" t="s" s="2">
-        <v>30</v>
+        <v>36</v>
       </c>
       <c r="I167" t="s" s="2">
         <v>18</v>
@@ -6337,7 +6976,7 @@
         <v>14</v>
       </c>
       <c r="B168" t="s" s="2">
-        <v>61</v>
+        <v>213</v>
       </c>
       <c r="C168" t="s" s="2">
         <v>14</v>
@@ -6346,7 +6985,7 @@
         <v>14</v>
       </c>
       <c r="E168" t="s" s="2">
-        <v>14</v>
+        <v>223</v>
       </c>
       <c r="F168" t="s" s="2">
         <v>14</v>
@@ -6355,7 +6994,7 @@
         <v>14</v>
       </c>
       <c r="H168" t="s" s="2">
-        <v>33</v>
+        <v>36</v>
       </c>
       <c r="I168" t="s" s="2">
         <v>18</v>
@@ -6372,7 +7011,7 @@
         <v>14</v>
       </c>
       <c r="B169" t="s" s="2">
-        <v>61</v>
+        <v>213</v>
       </c>
       <c r="C169" t="s" s="2">
         <v>14</v>
@@ -6381,7 +7020,7 @@
         <v>14</v>
       </c>
       <c r="E169" t="s" s="2">
-        <v>14</v>
+        <v>224</v>
       </c>
       <c r="F169" t="s" s="2">
         <v>14</v>
@@ -6390,7 +7029,7 @@
         <v>14</v>
       </c>
       <c r="H169" t="s" s="2">
-        <v>26</v>
+        <v>36</v>
       </c>
       <c r="I169" t="s" s="2">
         <v>18</v>
@@ -6407,7 +7046,7 @@
         <v>14</v>
       </c>
       <c r="B170" t="s" s="2">
-        <v>61</v>
+        <v>213</v>
       </c>
       <c r="C170" t="s" s="2">
         <v>14</v>
@@ -6416,7 +7055,7 @@
         <v>14</v>
       </c>
       <c r="E170" t="s" s="2">
-        <v>14</v>
+        <v>225</v>
       </c>
       <c r="F170" t="s" s="2">
         <v>14</v>
@@ -6425,7 +7064,7 @@
         <v>14</v>
       </c>
       <c r="H170" t="s" s="2">
-        <v>26</v>
+        <v>36</v>
       </c>
       <c r="I170" t="s" s="2">
         <v>18</v>
@@ -6442,7 +7081,7 @@
         <v>14</v>
       </c>
       <c r="B171" t="s" s="2">
-        <v>61</v>
+        <v>213</v>
       </c>
       <c r="C171" t="s" s="2">
         <v>14</v>
@@ -6451,7 +7090,7 @@
         <v>14</v>
       </c>
       <c r="E171" t="s" s="2">
-        <v>14</v>
+        <v>226</v>
       </c>
       <c r="F171" t="s" s="2">
         <v>14</v>
@@ -6460,7 +7099,7 @@
         <v>14</v>
       </c>
       <c r="H171" t="s" s="2">
-        <v>26</v>
+        <v>36</v>
       </c>
       <c r="I171" t="s" s="2">
         <v>18</v>
@@ -6477,7 +7116,7 @@
         <v>14</v>
       </c>
       <c r="B172" t="s" s="2">
-        <v>61</v>
+        <v>213</v>
       </c>
       <c r="C172" t="s" s="2">
         <v>14</v>
@@ -6486,7 +7125,7 @@
         <v>14</v>
       </c>
       <c r="E172" t="s" s="2">
-        <v>14</v>
+        <v>227</v>
       </c>
       <c r="F172" t="s" s="2">
         <v>14</v>
@@ -6495,7 +7134,7 @@
         <v>14</v>
       </c>
       <c r="H172" t="s" s="2">
-        <v>26</v>
+        <v>36</v>
       </c>
       <c r="I172" t="s" s="2">
         <v>18</v>
@@ -6512,7 +7151,7 @@
         <v>14</v>
       </c>
       <c r="B173" t="s" s="2">
-        <v>61</v>
+        <v>213</v>
       </c>
       <c r="C173" t="s" s="2">
         <v>14</v>
@@ -6521,7 +7160,7 @@
         <v>14</v>
       </c>
       <c r="E173" t="s" s="2">
-        <v>14</v>
+        <v>228</v>
       </c>
       <c r="F173" t="s" s="2">
         <v>14</v>
@@ -6530,7 +7169,7 @@
         <v>14</v>
       </c>
       <c r="H173" t="s" s="2">
-        <v>26</v>
+        <v>36</v>
       </c>
       <c r="I173" t="s" s="2">
         <v>18</v>
@@ -6547,7 +7186,7 @@
         <v>14</v>
       </c>
       <c r="B174" t="s" s="2">
-        <v>61</v>
+        <v>213</v>
       </c>
       <c r="C174" t="s" s="2">
         <v>14</v>
@@ -6556,7 +7195,7 @@
         <v>14</v>
       </c>
       <c r="E174" t="s" s="2">
-        <v>14</v>
+        <v>229</v>
       </c>
       <c r="F174" t="s" s="2">
         <v>14</v>
@@ -6565,7 +7204,7 @@
         <v>14</v>
       </c>
       <c r="H174" t="s" s="2">
-        <v>30</v>
+        <v>84</v>
       </c>
       <c r="I174" t="s" s="2">
         <v>18</v>
@@ -6582,7 +7221,7 @@
         <v>14</v>
       </c>
       <c r="B175" t="s" s="2">
-        <v>61</v>
+        <v>213</v>
       </c>
       <c r="C175" t="s" s="2">
         <v>14</v>
@@ -6591,7 +7230,7 @@
         <v>14</v>
       </c>
       <c r="E175" t="s" s="2">
-        <v>14</v>
+        <v>230</v>
       </c>
       <c r="F175" t="s" s="2">
         <v>14</v>
@@ -6600,7 +7239,7 @@
         <v>14</v>
       </c>
       <c r="H175" t="s" s="2">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="I175" t="s" s="2">
         <v>18</v>
@@ -6614,25 +7253,25 @@
     </row>
     <row r="176">
       <c r="A176" t="s" s="2">
-        <v>74</v>
+        <v>14</v>
       </c>
       <c r="B176" t="s" s="2">
-        <v>75</v>
+        <v>213</v>
       </c>
       <c r="C176" t="s" s="2">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="D176" t="s" s="2">
         <v>14</v>
       </c>
       <c r="E176" t="s" s="2">
-        <v>76</v>
+        <v>231</v>
       </c>
       <c r="F176" t="s" s="2">
         <v>14</v>
       </c>
       <c r="G176" t="s" s="2">
-        <v>21</v>
+        <v>14</v>
       </c>
       <c r="H176" t="s" s="2">
         <v>29</v>
@@ -6652,7 +7291,7 @@
         <v>14</v>
       </c>
       <c r="B177" t="s" s="2">
-        <v>75</v>
+        <v>213</v>
       </c>
       <c r="C177" t="s" s="2">
         <v>14</v>
@@ -6661,7 +7300,7 @@
         <v>14</v>
       </c>
       <c r="E177" t="s" s="2">
-        <v>14</v>
+        <v>232</v>
       </c>
       <c r="F177" t="s" s="2">
         <v>14</v>
@@ -6670,7 +7309,7 @@
         <v>14</v>
       </c>
       <c r="H177" t="s" s="2">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="I177" t="s" s="2">
         <v>18</v>
@@ -6687,7 +7326,7 @@
         <v>14</v>
       </c>
       <c r="B178" t="s" s="2">
-        <v>75</v>
+        <v>213</v>
       </c>
       <c r="C178" t="s" s="2">
         <v>14</v>
@@ -6696,7 +7335,7 @@
         <v>14</v>
       </c>
       <c r="E178" t="s" s="2">
-        <v>14</v>
+        <v>233</v>
       </c>
       <c r="F178" t="s" s="2">
         <v>14</v>
@@ -6705,7 +7344,7 @@
         <v>14</v>
       </c>
       <c r="H178" t="s" s="2">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="I178" t="s" s="2">
         <v>18</v>
@@ -6722,7 +7361,7 @@
         <v>14</v>
       </c>
       <c r="B179" t="s" s="2">
-        <v>75</v>
+        <v>213</v>
       </c>
       <c r="C179" t="s" s="2">
         <v>14</v>
@@ -6731,7 +7370,7 @@
         <v>14</v>
       </c>
       <c r="E179" t="s" s="2">
-        <v>14</v>
+        <v>234</v>
       </c>
       <c r="F179" t="s" s="2">
         <v>14</v>
@@ -6740,7 +7379,7 @@
         <v>14</v>
       </c>
       <c r="H179" t="s" s="2">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="I179" t="s" s="2">
         <v>18</v>
@@ -6757,7 +7396,7 @@
         <v>14</v>
       </c>
       <c r="B180" t="s" s="2">
-        <v>75</v>
+        <v>213</v>
       </c>
       <c r="C180" t="s" s="2">
         <v>14</v>
@@ -6766,7 +7405,7 @@
         <v>14</v>
       </c>
       <c r="E180" t="s" s="2">
-        <v>14</v>
+        <v>235</v>
       </c>
       <c r="F180" t="s" s="2">
         <v>14</v>
@@ -6775,7 +7414,7 @@
         <v>14</v>
       </c>
       <c r="H180" t="s" s="2">
-        <v>30</v>
+        <v>36</v>
       </c>
       <c r="I180" t="s" s="2">
         <v>18</v>
@@ -6792,7 +7431,7 @@
         <v>14</v>
       </c>
       <c r="B181" t="s" s="2">
-        <v>75</v>
+        <v>213</v>
       </c>
       <c r="C181" t="s" s="2">
         <v>14</v>
@@ -6801,7 +7440,7 @@
         <v>14</v>
       </c>
       <c r="E181" t="s" s="2">
-        <v>14</v>
+        <v>88</v>
       </c>
       <c r="F181" t="s" s="2">
         <v>14</v>
@@ -6810,7 +7449,7 @@
         <v>14</v>
       </c>
       <c r="H181" t="s" s="2">
-        <v>30</v>
+        <v>36</v>
       </c>
       <c r="I181" t="s" s="2">
         <v>18</v>
@@ -6824,28 +7463,28 @@
     </row>
     <row r="182">
       <c r="A182" t="s" s="2">
-        <v>14</v>
+        <v>236</v>
       </c>
       <c r="B182" t="s" s="2">
-        <v>75</v>
+        <v>237</v>
       </c>
       <c r="C182" t="s" s="2">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="D182" t="s" s="2">
         <v>14</v>
       </c>
       <c r="E182" t="s" s="2">
-        <v>14</v>
+        <v>238</v>
       </c>
       <c r="F182" t="s" s="2">
         <v>14</v>
       </c>
       <c r="G182" t="s" s="2">
-        <v>14</v>
+        <v>22</v>
       </c>
       <c r="H182" t="s" s="2">
-        <v>30</v>
+        <v>34</v>
       </c>
       <c r="I182" t="s" s="2">
         <v>18</v>
@@ -6862,7 +7501,7 @@
         <v>14</v>
       </c>
       <c r="B183" t="s" s="2">
-        <v>75</v>
+        <v>237</v>
       </c>
       <c r="C183" t="s" s="2">
         <v>14</v>
@@ -6871,7 +7510,7 @@
         <v>14</v>
       </c>
       <c r="E183" t="s" s="2">
-        <v>14</v>
+        <v>239</v>
       </c>
       <c r="F183" t="s" s="2">
         <v>14</v>
@@ -6880,7 +7519,7 @@
         <v>14</v>
       </c>
       <c r="H183" t="s" s="2">
-        <v>30</v>
+        <v>36</v>
       </c>
       <c r="I183" t="s" s="2">
         <v>18</v>
@@ -6897,7 +7536,7 @@
         <v>14</v>
       </c>
       <c r="B184" t="s" s="2">
-        <v>75</v>
+        <v>237</v>
       </c>
       <c r="C184" t="s" s="2">
         <v>14</v>
@@ -6906,7 +7545,7 @@
         <v>14</v>
       </c>
       <c r="E184" t="s" s="2">
-        <v>14</v>
+        <v>240</v>
       </c>
       <c r="F184" t="s" s="2">
         <v>14</v>
@@ -6915,7 +7554,7 @@
         <v>14</v>
       </c>
       <c r="H184" t="s" s="2">
-        <v>30</v>
+        <v>36</v>
       </c>
       <c r="I184" t="s" s="2">
         <v>18</v>
@@ -6932,7 +7571,7 @@
         <v>14</v>
       </c>
       <c r="B185" t="s" s="2">
-        <v>75</v>
+        <v>237</v>
       </c>
       <c r="C185" t="s" s="2">
         <v>14</v>
@@ -6941,7 +7580,7 @@
         <v>14</v>
       </c>
       <c r="E185" t="s" s="2">
-        <v>14</v>
+        <v>241</v>
       </c>
       <c r="F185" t="s" s="2">
         <v>14</v>
@@ -6950,7 +7589,7 @@
         <v>14</v>
       </c>
       <c r="H185" t="s" s="2">
-        <v>30</v>
+        <v>36</v>
       </c>
       <c r="I185" t="s" s="2">
         <v>18</v>
@@ -6967,7 +7606,7 @@
         <v>14</v>
       </c>
       <c r="B186" t="s" s="2">
-        <v>75</v>
+        <v>237</v>
       </c>
       <c r="C186" t="s" s="2">
         <v>14</v>
@@ -6976,7 +7615,7 @@
         <v>14</v>
       </c>
       <c r="E186" t="s" s="2">
-        <v>14</v>
+        <v>242</v>
       </c>
       <c r="F186" t="s" s="2">
         <v>14</v>
@@ -6985,7 +7624,7 @@
         <v>14</v>
       </c>
       <c r="H186" t="s" s="2">
-        <v>30</v>
+        <v>36</v>
       </c>
       <c r="I186" t="s" s="2">
         <v>18</v>
@@ -7002,7 +7641,7 @@
         <v>14</v>
       </c>
       <c r="B187" t="s" s="2">
-        <v>75</v>
+        <v>237</v>
       </c>
       <c r="C187" t="s" s="2">
         <v>14</v>
@@ -7011,7 +7650,7 @@
         <v>14</v>
       </c>
       <c r="E187" t="s" s="2">
-        <v>14</v>
+        <v>243</v>
       </c>
       <c r="F187" t="s" s="2">
         <v>14</v>
@@ -7020,7 +7659,7 @@
         <v>14</v>
       </c>
       <c r="H187" t="s" s="2">
-        <v>30</v>
+        <v>36</v>
       </c>
       <c r="I187" t="s" s="2">
         <v>18</v>
@@ -7037,7 +7676,7 @@
         <v>14</v>
       </c>
       <c r="B188" t="s" s="2">
-        <v>75</v>
+        <v>237</v>
       </c>
       <c r="C188" t="s" s="2">
         <v>14</v>
@@ -7046,7 +7685,7 @@
         <v>14</v>
       </c>
       <c r="E188" t="s" s="2">
-        <v>14</v>
+        <v>244</v>
       </c>
       <c r="F188" t="s" s="2">
         <v>14</v>
@@ -7055,7 +7694,7 @@
         <v>14</v>
       </c>
       <c r="H188" t="s" s="2">
-        <v>30</v>
+        <v>36</v>
       </c>
       <c r="I188" t="s" s="2">
         <v>18</v>
@@ -7072,7 +7711,7 @@
         <v>14</v>
       </c>
       <c r="B189" t="s" s="2">
-        <v>75</v>
+        <v>237</v>
       </c>
       <c r="C189" t="s" s="2">
         <v>14</v>
@@ -7081,7 +7720,7 @@
         <v>14</v>
       </c>
       <c r="E189" t="s" s="2">
-        <v>14</v>
+        <v>245</v>
       </c>
       <c r="F189" t="s" s="2">
         <v>14</v>
@@ -7090,7 +7729,7 @@
         <v>14</v>
       </c>
       <c r="H189" t="s" s="2">
-        <v>30</v>
+        <v>36</v>
       </c>
       <c r="I189" t="s" s="2">
         <v>18</v>
@@ -7107,7 +7746,7 @@
         <v>14</v>
       </c>
       <c r="B190" t="s" s="2">
-        <v>75</v>
+        <v>237</v>
       </c>
       <c r="C190" t="s" s="2">
         <v>14</v>
@@ -7116,7 +7755,7 @@
         <v>14</v>
       </c>
       <c r="E190" t="s" s="2">
-        <v>14</v>
+        <v>246</v>
       </c>
       <c r="F190" t="s" s="2">
         <v>14</v>
@@ -7125,7 +7764,7 @@
         <v>14</v>
       </c>
       <c r="H190" t="s" s="2">
-        <v>30</v>
+        <v>36</v>
       </c>
       <c r="I190" t="s" s="2">
         <v>18</v>
@@ -7142,7 +7781,7 @@
         <v>14</v>
       </c>
       <c r="B191" t="s" s="2">
-        <v>75</v>
+        <v>237</v>
       </c>
       <c r="C191" t="s" s="2">
         <v>14</v>
@@ -7151,7 +7790,7 @@
         <v>14</v>
       </c>
       <c r="E191" t="s" s="2">
-        <v>14</v>
+        <v>247</v>
       </c>
       <c r="F191" t="s" s="2">
         <v>14</v>
@@ -7160,7 +7799,7 @@
         <v>14</v>
       </c>
       <c r="H191" t="s" s="2">
-        <v>30</v>
+        <v>36</v>
       </c>
       <c r="I191" t="s" s="2">
         <v>18</v>
@@ -7177,7 +7816,7 @@
         <v>14</v>
       </c>
       <c r="B192" t="s" s="2">
-        <v>75</v>
+        <v>237</v>
       </c>
       <c r="C192" t="s" s="2">
         <v>14</v>
@@ -7186,7 +7825,7 @@
         <v>14</v>
       </c>
       <c r="E192" t="s" s="2">
-        <v>14</v>
+        <v>248</v>
       </c>
       <c r="F192" t="s" s="2">
         <v>14</v>
@@ -7195,7 +7834,7 @@
         <v>14</v>
       </c>
       <c r="H192" t="s" s="2">
-        <v>30</v>
+        <v>36</v>
       </c>
       <c r="I192" t="s" s="2">
         <v>18</v>
@@ -7212,7 +7851,7 @@
         <v>14</v>
       </c>
       <c r="B193" t="s" s="2">
-        <v>75</v>
+        <v>237</v>
       </c>
       <c r="C193" t="s" s="2">
         <v>14</v>
@@ -7221,7 +7860,7 @@
         <v>14</v>
       </c>
       <c r="E193" t="s" s="2">
-        <v>14</v>
+        <v>249</v>
       </c>
       <c r="F193" t="s" s="2">
         <v>14</v>
@@ -7230,7 +7869,7 @@
         <v>14</v>
       </c>
       <c r="H193" t="s" s="2">
-        <v>30</v>
+        <v>36</v>
       </c>
       <c r="I193" t="s" s="2">
         <v>18</v>
@@ -7247,7 +7886,7 @@
         <v>14</v>
       </c>
       <c r="B194" t="s" s="2">
-        <v>75</v>
+        <v>237</v>
       </c>
       <c r="C194" t="s" s="2">
         <v>14</v>
@@ -7256,7 +7895,7 @@
         <v>14</v>
       </c>
       <c r="E194" t="s" s="2">
-        <v>14</v>
+        <v>250</v>
       </c>
       <c r="F194" t="s" s="2">
         <v>14</v>
@@ -7265,7 +7904,7 @@
         <v>14</v>
       </c>
       <c r="H194" t="s" s="2">
-        <v>77</v>
+        <v>36</v>
       </c>
       <c r="I194" t="s" s="2">
         <v>18</v>
@@ -7282,7 +7921,7 @@
         <v>14</v>
       </c>
       <c r="B195" t="s" s="2">
-        <v>75</v>
+        <v>237</v>
       </c>
       <c r="C195" t="s" s="2">
         <v>14</v>
@@ -7291,7 +7930,7 @@
         <v>14</v>
       </c>
       <c r="E195" t="s" s="2">
-        <v>14</v>
+        <v>251</v>
       </c>
       <c r="F195" t="s" s="2">
         <v>14</v>
@@ -7300,7 +7939,7 @@
         <v>14</v>
       </c>
       <c r="H195" t="s" s="2">
-        <v>30</v>
+        <v>36</v>
       </c>
       <c r="I195" t="s" s="2">
         <v>18</v>
@@ -7317,7 +7956,7 @@
         <v>14</v>
       </c>
       <c r="B196" t="s" s="2">
-        <v>75</v>
+        <v>237</v>
       </c>
       <c r="C196" t="s" s="2">
         <v>14</v>
@@ -7326,7 +7965,7 @@
         <v>14</v>
       </c>
       <c r="E196" t="s" s="2">
-        <v>14</v>
+        <v>252</v>
       </c>
       <c r="F196" t="s" s="2">
         <v>14</v>
@@ -7335,7 +7974,7 @@
         <v>14</v>
       </c>
       <c r="H196" t="s" s="2">
-        <v>30</v>
+        <v>36</v>
       </c>
       <c r="I196" t="s" s="2">
         <v>18</v>
@@ -7352,7 +7991,7 @@
         <v>14</v>
       </c>
       <c r="B197" t="s" s="2">
-        <v>75</v>
+        <v>237</v>
       </c>
       <c r="C197" t="s" s="2">
         <v>14</v>
@@ -7361,7 +8000,7 @@
         <v>14</v>
       </c>
       <c r="E197" t="s" s="2">
-        <v>14</v>
+        <v>253</v>
       </c>
       <c r="F197" t="s" s="2">
         <v>14</v>
@@ -7370,7 +8009,7 @@
         <v>14</v>
       </c>
       <c r="H197" t="s" s="2">
-        <v>30</v>
+        <v>36</v>
       </c>
       <c r="I197" t="s" s="2">
         <v>18</v>
@@ -7387,7 +8026,7 @@
         <v>14</v>
       </c>
       <c r="B198" t="s" s="2">
-        <v>75</v>
+        <v>237</v>
       </c>
       <c r="C198" t="s" s="2">
         <v>14</v>
@@ -7396,7 +8035,7 @@
         <v>14</v>
       </c>
       <c r="E198" t="s" s="2">
-        <v>14</v>
+        <v>254</v>
       </c>
       <c r="F198" t="s" s="2">
         <v>14</v>
@@ -7405,7 +8044,7 @@
         <v>14</v>
       </c>
       <c r="H198" t="s" s="2">
-        <v>30</v>
+        <v>36</v>
       </c>
       <c r="I198" t="s" s="2">
         <v>18</v>
@@ -7422,7 +8061,7 @@
         <v>14</v>
       </c>
       <c r="B199" t="s" s="2">
-        <v>75</v>
+        <v>237</v>
       </c>
       <c r="C199" t="s" s="2">
         <v>14</v>
@@ -7431,7 +8070,7 @@
         <v>14</v>
       </c>
       <c r="E199" t="s" s="2">
-        <v>14</v>
+        <v>255</v>
       </c>
       <c r="F199" t="s" s="2">
         <v>14</v>
@@ -7440,7 +8079,7 @@
         <v>14</v>
       </c>
       <c r="H199" t="s" s="2">
-        <v>26</v>
+        <v>36</v>
       </c>
       <c r="I199" t="s" s="2">
         <v>18</v>
@@ -7457,7 +8096,7 @@
         <v>14</v>
       </c>
       <c r="B200" t="s" s="2">
-        <v>75</v>
+        <v>237</v>
       </c>
       <c r="C200" t="s" s="2">
         <v>14</v>
@@ -7466,7 +8105,7 @@
         <v>14</v>
       </c>
       <c r="E200" t="s" s="2">
-        <v>14</v>
+        <v>256</v>
       </c>
       <c r="F200" t="s" s="2">
         <v>14</v>
@@ -7475,7 +8114,7 @@
         <v>14</v>
       </c>
       <c r="H200" t="s" s="2">
-        <v>26</v>
+        <v>257</v>
       </c>
       <c r="I200" t="s" s="2">
         <v>18</v>
@@ -7492,7 +8131,7 @@
         <v>14</v>
       </c>
       <c r="B201" t="s" s="2">
-        <v>75</v>
+        <v>237</v>
       </c>
       <c r="C201" t="s" s="2">
         <v>14</v>
@@ -7501,7 +8140,7 @@
         <v>14</v>
       </c>
       <c r="E201" t="s" s="2">
-        <v>14</v>
+        <v>258</v>
       </c>
       <c r="F201" t="s" s="2">
         <v>14</v>
@@ -7510,7 +8149,7 @@
         <v>14</v>
       </c>
       <c r="H201" t="s" s="2">
-        <v>26</v>
+        <v>36</v>
       </c>
       <c r="I201" t="s" s="2">
         <v>18</v>
@@ -7524,28 +8163,28 @@
     </row>
     <row r="202">
       <c r="A202" t="s" s="2">
-        <v>78</v>
+        <v>14</v>
       </c>
       <c r="B202" t="s" s="2">
-        <v>79</v>
+        <v>237</v>
       </c>
       <c r="C202" t="s" s="2">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="D202" t="s" s="2">
         <v>14</v>
       </c>
       <c r="E202" t="s" s="2">
-        <v>14</v>
+        <v>259</v>
       </c>
       <c r="F202" t="s" s="2">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="G202" t="s" s="2">
-        <v>21</v>
+        <v>14</v>
       </c>
       <c r="H202" t="s" s="2">
-        <v>29</v>
+        <v>36</v>
       </c>
       <c r="I202" t="s" s="2">
         <v>18</v>
@@ -7562,7 +8201,7 @@
         <v>14</v>
       </c>
       <c r="B203" t="s" s="2">
-        <v>79</v>
+        <v>237</v>
       </c>
       <c r="C203" t="s" s="2">
         <v>14</v>
@@ -7571,7 +8210,7 @@
         <v>14</v>
       </c>
       <c r="E203" t="s" s="2">
-        <v>14</v>
+        <v>260</v>
       </c>
       <c r="F203" t="s" s="2">
         <v>14</v>
@@ -7580,7 +8219,7 @@
         <v>14</v>
       </c>
       <c r="H203" t="s" s="2">
-        <v>30</v>
+        <v>36</v>
       </c>
       <c r="I203" t="s" s="2">
         <v>18</v>
@@ -7597,7 +8236,7 @@
         <v>14</v>
       </c>
       <c r="B204" t="s" s="2">
-        <v>79</v>
+        <v>237</v>
       </c>
       <c r="C204" t="s" s="2">
         <v>14</v>
@@ -7606,7 +8245,7 @@
         <v>14</v>
       </c>
       <c r="E204" t="s" s="2">
-        <v>14</v>
+        <v>261</v>
       </c>
       <c r="F204" t="s" s="2">
         <v>14</v>
@@ -7615,7 +8254,7 @@
         <v>14</v>
       </c>
       <c r="H204" t="s" s="2">
-        <v>26</v>
+        <v>36</v>
       </c>
       <c r="I204" t="s" s="2">
         <v>18</v>
@@ -7632,7 +8271,7 @@
         <v>14</v>
       </c>
       <c r="B205" t="s" s="2">
-        <v>79</v>
+        <v>237</v>
       </c>
       <c r="C205" t="s" s="2">
         <v>14</v>
@@ -7641,7 +8280,7 @@
         <v>14</v>
       </c>
       <c r="E205" t="s" s="2">
-        <v>14</v>
+        <v>262</v>
       </c>
       <c r="F205" t="s" s="2">
         <v>14</v>
@@ -7650,7 +8289,7 @@
         <v>14</v>
       </c>
       <c r="H205" t="s" s="2">
-        <v>30</v>
+        <v>36</v>
       </c>
       <c r="I205" t="s" s="2">
         <v>18</v>
@@ -7667,7 +8306,7 @@
         <v>14</v>
       </c>
       <c r="B206" t="s" s="2">
-        <v>79</v>
+        <v>237</v>
       </c>
       <c r="C206" t="s" s="2">
         <v>14</v>
@@ -7676,7 +8315,7 @@
         <v>14</v>
       </c>
       <c r="E206" t="s" s="2">
-        <v>14</v>
+        <v>263</v>
       </c>
       <c r="F206" t="s" s="2">
         <v>14</v>
@@ -7685,7 +8324,7 @@
         <v>14</v>
       </c>
       <c r="H206" t="s" s="2">
-        <v>26</v>
+        <v>36</v>
       </c>
       <c r="I206" t="s" s="2">
         <v>18</v>
@@ -7702,7 +8341,7 @@
         <v>14</v>
       </c>
       <c r="B207" t="s" s="2">
-        <v>79</v>
+        <v>237</v>
       </c>
       <c r="C207" t="s" s="2">
         <v>14</v>
@@ -7711,7 +8350,7 @@
         <v>14</v>
       </c>
       <c r="E207" t="s" s="2">
-        <v>14</v>
+        <v>264</v>
       </c>
       <c r="F207" t="s" s="2">
         <v>14</v>
@@ -7720,7 +8359,7 @@
         <v>14</v>
       </c>
       <c r="H207" t="s" s="2">
-        <v>30</v>
+        <v>36</v>
       </c>
       <c r="I207" t="s" s="2">
         <v>18</v>
@@ -7737,7 +8376,7 @@
         <v>14</v>
       </c>
       <c r="B208" t="s" s="2">
-        <v>79</v>
+        <v>237</v>
       </c>
       <c r="C208" t="s" s="2">
         <v>14</v>
@@ -7746,7 +8385,7 @@
         <v>14</v>
       </c>
       <c r="E208" t="s" s="2">
-        <v>14</v>
+        <v>88</v>
       </c>
       <c r="F208" t="s" s="2">
         <v>14</v>
@@ -7755,7 +8394,7 @@
         <v>14</v>
       </c>
       <c r="H208" t="s" s="2">
-        <v>26</v>
+        <v>36</v>
       </c>
       <c r="I208" t="s" s="2">
         <v>18</v>
@@ -7772,7 +8411,7 @@
         <v>14</v>
       </c>
       <c r="B209" t="s" s="2">
-        <v>79</v>
+        <v>237</v>
       </c>
       <c r="C209" t="s" s="2">
         <v>14</v>
@@ -7781,7 +8420,7 @@
         <v>14</v>
       </c>
       <c r="E209" t="s" s="2">
-        <v>14</v>
+        <v>230</v>
       </c>
       <c r="F209" t="s" s="2">
         <v>14</v>
@@ -7790,7 +8429,7 @@
         <v>14</v>
       </c>
       <c r="H209" t="s" s="2">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="I209" t="s" s="2">
         <v>18</v>
@@ -7807,7 +8446,7 @@
         <v>14</v>
       </c>
       <c r="B210" t="s" s="2">
-        <v>79</v>
+        <v>237</v>
       </c>
       <c r="C210" t="s" s="2">
         <v>14</v>
@@ -7816,7 +8455,7 @@
         <v>14</v>
       </c>
       <c r="E210" t="s" s="2">
-        <v>14</v>
+        <v>233</v>
       </c>
       <c r="F210" t="s" s="2">
         <v>14</v>
@@ -7825,7 +8464,7 @@
         <v>14</v>
       </c>
       <c r="H210" t="s" s="2">
-        <v>26</v>
+        <v>29</v>
       </c>
       <c r="I210" t="s" s="2">
         <v>18</v>
@@ -7842,7 +8481,7 @@
         <v>14</v>
       </c>
       <c r="B211" t="s" s="2">
-        <v>79</v>
+        <v>237</v>
       </c>
       <c r="C211" t="s" s="2">
         <v>14</v>
@@ -7851,7 +8490,7 @@
         <v>14</v>
       </c>
       <c r="E211" t="s" s="2">
-        <v>14</v>
+        <v>234</v>
       </c>
       <c r="F211" t="s" s="2">
         <v>14</v>
@@ -7860,7 +8499,7 @@
         <v>14</v>
       </c>
       <c r="H211" t="s" s="2">
-        <v>26</v>
+        <v>29</v>
       </c>
       <c r="I211" t="s" s="2">
         <v>18</v>
@@ -7874,28 +8513,28 @@
     </row>
     <row r="212">
       <c r="A212" t="s" s="2">
-        <v>14</v>
+        <v>265</v>
       </c>
       <c r="B212" t="s" s="2">
-        <v>79</v>
+        <v>266</v>
       </c>
       <c r="C212" t="s" s="2">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="D212" t="s" s="2">
         <v>14</v>
       </c>
       <c r="E212" t="s" s="2">
-        <v>14</v>
+        <v>267</v>
       </c>
       <c r="F212" t="s" s="2">
         <v>14</v>
       </c>
       <c r="G212" t="s" s="2">
-        <v>14</v>
+        <v>22</v>
       </c>
       <c r="H212" t="s" s="2">
-        <v>30</v>
+        <v>34</v>
       </c>
       <c r="I212" t="s" s="2">
         <v>18</v>
@@ -7912,7 +8551,7 @@
         <v>14</v>
       </c>
       <c r="B213" t="s" s="2">
-        <v>79</v>
+        <v>266</v>
       </c>
       <c r="C213" t="s" s="2">
         <v>14</v>
@@ -7921,7 +8560,7 @@
         <v>14</v>
       </c>
       <c r="E213" t="s" s="2">
-        <v>14</v>
+        <v>268</v>
       </c>
       <c r="F213" t="s" s="2">
         <v>14</v>
@@ -7930,7 +8569,7 @@
         <v>14</v>
       </c>
       <c r="H213" t="s" s="2">
-        <v>30</v>
+        <v>36</v>
       </c>
       <c r="I213" t="s" s="2">
         <v>18</v>
@@ -7947,7 +8586,7 @@
         <v>14</v>
       </c>
       <c r="B214" t="s" s="2">
-        <v>79</v>
+        <v>266</v>
       </c>
       <c r="C214" t="s" s="2">
         <v>14</v>
@@ -7956,7 +8595,7 @@
         <v>14</v>
       </c>
       <c r="E214" t="s" s="2">
-        <v>14</v>
+        <v>269</v>
       </c>
       <c r="F214" t="s" s="2">
         <v>14</v>
@@ -7965,7 +8604,7 @@
         <v>14</v>
       </c>
       <c r="H214" t="s" s="2">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="I214" t="s" s="2">
         <v>18</v>
@@ -7982,7 +8621,7 @@
         <v>14</v>
       </c>
       <c r="B215" t="s" s="2">
-        <v>79</v>
+        <v>266</v>
       </c>
       <c r="C215" t="s" s="2">
         <v>14</v>
@@ -7991,7 +8630,7 @@
         <v>14</v>
       </c>
       <c r="E215" t="s" s="2">
-        <v>14</v>
+        <v>270</v>
       </c>
       <c r="F215" t="s" s="2">
         <v>14</v>
@@ -8000,7 +8639,7 @@
         <v>14</v>
       </c>
       <c r="H215" t="s" s="2">
-        <v>30</v>
+        <v>36</v>
       </c>
       <c r="I215" t="s" s="2">
         <v>18</v>
@@ -8017,7 +8656,7 @@
         <v>14</v>
       </c>
       <c r="B216" t="s" s="2">
-        <v>79</v>
+        <v>266</v>
       </c>
       <c r="C216" t="s" s="2">
         <v>14</v>
@@ -8026,7 +8665,7 @@
         <v>14</v>
       </c>
       <c r="E216" t="s" s="2">
-        <v>14</v>
+        <v>271</v>
       </c>
       <c r="F216" t="s" s="2">
         <v>14</v>
@@ -8035,7 +8674,7 @@
         <v>14</v>
       </c>
       <c r="H216" t="s" s="2">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="I216" t="s" s="2">
         <v>18</v>
@@ -8052,7 +8691,7 @@
         <v>14</v>
       </c>
       <c r="B217" t="s" s="2">
-        <v>79</v>
+        <v>266</v>
       </c>
       <c r="C217" t="s" s="2">
         <v>14</v>
@@ -8061,7 +8700,7 @@
         <v>14</v>
       </c>
       <c r="E217" t="s" s="2">
-        <v>14</v>
+        <v>35</v>
       </c>
       <c r="F217" t="s" s="2">
         <v>14</v>
@@ -8070,7 +8709,7 @@
         <v>14</v>
       </c>
       <c r="H217" t="s" s="2">
-        <v>30</v>
+        <v>36</v>
       </c>
       <c r="I217" t="s" s="2">
         <v>18</v>
@@ -8087,7 +8726,7 @@
         <v>14</v>
       </c>
       <c r="B218" t="s" s="2">
-        <v>79</v>
+        <v>266</v>
       </c>
       <c r="C218" t="s" s="2">
         <v>14</v>
@@ -8096,7 +8735,7 @@
         <v>14</v>
       </c>
       <c r="E218" t="s" s="2">
-        <v>14</v>
+        <v>272</v>
       </c>
       <c r="F218" t="s" s="2">
         <v>14</v>
@@ -8105,7 +8744,7 @@
         <v>14</v>
       </c>
       <c r="H218" t="s" s="2">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="I218" t="s" s="2">
         <v>18</v>
@@ -8122,7 +8761,7 @@
         <v>14</v>
       </c>
       <c r="B219" t="s" s="2">
-        <v>79</v>
+        <v>266</v>
       </c>
       <c r="C219" t="s" s="2">
         <v>14</v>
@@ -8131,7 +8770,7 @@
         <v>14</v>
       </c>
       <c r="E219" t="s" s="2">
-        <v>14</v>
+        <v>40</v>
       </c>
       <c r="F219" t="s" s="2">
         <v>14</v>
@@ -8140,7 +8779,7 @@
         <v>14</v>
       </c>
       <c r="H219" t="s" s="2">
-        <v>30</v>
+        <v>36</v>
       </c>
       <c r="I219" t="s" s="2">
         <v>18</v>
@@ -8157,7 +8796,7 @@
         <v>14</v>
       </c>
       <c r="B220" t="s" s="2">
-        <v>79</v>
+        <v>266</v>
       </c>
       <c r="C220" t="s" s="2">
         <v>14</v>
@@ -8166,7 +8805,7 @@
         <v>14</v>
       </c>
       <c r="E220" t="s" s="2">
-        <v>14</v>
+        <v>273</v>
       </c>
       <c r="F220" t="s" s="2">
         <v>14</v>
@@ -8175,7 +8814,7 @@
         <v>14</v>
       </c>
       <c r="H220" t="s" s="2">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="I220" t="s" s="2">
         <v>18</v>
@@ -8192,7 +8831,7 @@
         <v>14</v>
       </c>
       <c r="B221" t="s" s="2">
-        <v>79</v>
+        <v>266</v>
       </c>
       <c r="C221" t="s" s="2">
         <v>14</v>
@@ -8201,7 +8840,7 @@
         <v>14</v>
       </c>
       <c r="E221" t="s" s="2">
-        <v>14</v>
+        <v>274</v>
       </c>
       <c r="F221" t="s" s="2">
         <v>14</v>
@@ -8210,7 +8849,7 @@
         <v>14</v>
       </c>
       <c r="H221" t="s" s="2">
-        <v>26</v>
+        <v>29</v>
       </c>
       <c r="I221" t="s" s="2">
         <v>18</v>
@@ -8227,7 +8866,7 @@
         <v>14</v>
       </c>
       <c r="B222" t="s" s="2">
-        <v>79</v>
+        <v>266</v>
       </c>
       <c r="C222" t="s" s="2">
         <v>14</v>
@@ -8236,7 +8875,7 @@
         <v>14</v>
       </c>
       <c r="E222" t="s" s="2">
-        <v>14</v>
+        <v>44</v>
       </c>
       <c r="F222" t="s" s="2">
         <v>14</v>
@@ -8245,7 +8884,7 @@
         <v>14</v>
       </c>
       <c r="H222" t="s" s="2">
-        <v>26</v>
+        <v>36</v>
       </c>
       <c r="I222" t="s" s="2">
         <v>18</v>
@@ -8262,7 +8901,7 @@
         <v>14</v>
       </c>
       <c r="B223" t="s" s="2">
-        <v>79</v>
+        <v>266</v>
       </c>
       <c r="C223" t="s" s="2">
         <v>14</v>
@@ -8271,7 +8910,7 @@
         <v>14</v>
       </c>
       <c r="E223" t="s" s="2">
-        <v>14</v>
+        <v>45</v>
       </c>
       <c r="F223" t="s" s="2">
         <v>14</v>
@@ -8280,7 +8919,7 @@
         <v>14</v>
       </c>
       <c r="H223" t="s" s="2">
-        <v>26</v>
+        <v>36</v>
       </c>
       <c r="I223" t="s" s="2">
         <v>18</v>
@@ -8297,7 +8936,7 @@
         <v>14</v>
       </c>
       <c r="B224" t="s" s="2">
-        <v>79</v>
+        <v>266</v>
       </c>
       <c r="C224" t="s" s="2">
         <v>14</v>
@@ -8306,7 +8945,7 @@
         <v>14</v>
       </c>
       <c r="E224" t="s" s="2">
-        <v>14</v>
+        <v>46</v>
       </c>
       <c r="F224" t="s" s="2">
         <v>14</v>
@@ -8315,7 +8954,7 @@
         <v>14</v>
       </c>
       <c r="H224" t="s" s="2">
-        <v>30</v>
+        <v>36</v>
       </c>
       <c r="I224" t="s" s="2">
         <v>18</v>
@@ -8332,7 +8971,7 @@
         <v>14</v>
       </c>
       <c r="B225" t="s" s="2">
-        <v>79</v>
+        <v>266</v>
       </c>
       <c r="C225" t="s" s="2">
         <v>14</v>
@@ -8341,7 +8980,7 @@
         <v>14</v>
       </c>
       <c r="E225" t="s" s="2">
-        <v>14</v>
+        <v>47</v>
       </c>
       <c r="F225" t="s" s="2">
         <v>14</v>
@@ -8350,7 +8989,7 @@
         <v>14</v>
       </c>
       <c r="H225" t="s" s="2">
-        <v>26</v>
+        <v>36</v>
       </c>
       <c r="I225" t="s" s="2">
         <v>18</v>
@@ -8367,7 +9006,7 @@
         <v>14</v>
       </c>
       <c r="B226" t="s" s="2">
-        <v>79</v>
+        <v>266</v>
       </c>
       <c r="C226" t="s" s="2">
         <v>14</v>
@@ -8376,7 +9015,7 @@
         <v>14</v>
       </c>
       <c r="E226" t="s" s="2">
-        <v>14</v>
+        <v>48</v>
       </c>
       <c r="F226" t="s" s="2">
         <v>14</v>
@@ -8385,7 +9024,7 @@
         <v>14</v>
       </c>
       <c r="H226" t="s" s="2">
-        <v>26</v>
+        <v>36</v>
       </c>
       <c r="I226" t="s" s="2">
         <v>18</v>
@@ -8402,7 +9041,7 @@
         <v>14</v>
       </c>
       <c r="B227" t="s" s="2">
-        <v>79</v>
+        <v>266</v>
       </c>
       <c r="C227" t="s" s="2">
         <v>14</v>
@@ -8411,7 +9050,7 @@
         <v>14</v>
       </c>
       <c r="E227" t="s" s="2">
-        <v>14</v>
+        <v>49</v>
       </c>
       <c r="F227" t="s" s="2">
         <v>14</v>
@@ -8420,7 +9059,7 @@
         <v>14</v>
       </c>
       <c r="H227" t="s" s="2">
-        <v>30</v>
+        <v>36</v>
       </c>
       <c r="I227" t="s" s="2">
         <v>18</v>
@@ -8434,28 +9073,28 @@
     </row>
     <row r="228">
       <c r="A228" t="s" s="2">
-        <v>80</v>
+        <v>14</v>
       </c>
       <c r="B228" t="s" s="2">
-        <v>81</v>
+        <v>266</v>
       </c>
       <c r="C228" t="s" s="2">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="D228" t="s" s="2">
         <v>14</v>
       </c>
       <c r="E228" t="s" s="2">
-        <v>14</v>
+        <v>50</v>
       </c>
       <c r="F228" t="s" s="2">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="G228" t="s" s="2">
-        <v>21</v>
+        <v>14</v>
       </c>
       <c r="H228" t="s" s="2">
-        <v>29</v>
+        <v>36</v>
       </c>
       <c r="I228" t="s" s="2">
         <v>18</v>
@@ -8472,7 +9111,7 @@
         <v>14</v>
       </c>
       <c r="B229" t="s" s="2">
-        <v>81</v>
+        <v>266</v>
       </c>
       <c r="C229" t="s" s="2">
         <v>14</v>
@@ -8481,7 +9120,7 @@
         <v>14</v>
       </c>
       <c r="E229" t="s" s="2">
-        <v>14</v>
+        <v>275</v>
       </c>
       <c r="F229" t="s" s="2">
         <v>14</v>
@@ -8490,7 +9129,7 @@
         <v>14</v>
       </c>
       <c r="H229" t="s" s="2">
-        <v>26</v>
+        <v>36</v>
       </c>
       <c r="I229" t="s" s="2">
         <v>18</v>
@@ -8507,7 +9146,7 @@
         <v>14</v>
       </c>
       <c r="B230" t="s" s="2">
-        <v>81</v>
+        <v>266</v>
       </c>
       <c r="C230" t="s" s="2">
         <v>14</v>
@@ -8516,7 +9155,7 @@
         <v>14</v>
       </c>
       <c r="E230" t="s" s="2">
-        <v>82</v>
+        <v>51</v>
       </c>
       <c r="F230" t="s" s="2">
         <v>14</v>
@@ -8525,7 +9164,7 @@
         <v>14</v>
       </c>
       <c r="H230" t="s" s="2">
-        <v>26</v>
+        <v>36</v>
       </c>
       <c r="I230" t="s" s="2">
         <v>18</v>
@@ -8542,7 +9181,7 @@
         <v>14</v>
       </c>
       <c r="B231" t="s" s="2">
-        <v>81</v>
+        <v>266</v>
       </c>
       <c r="C231" t="s" s="2">
         <v>14</v>
@@ -8551,7 +9190,7 @@
         <v>14</v>
       </c>
       <c r="E231" t="s" s="2">
-        <v>83</v>
+        <v>64</v>
       </c>
       <c r="F231" t="s" s="2">
         <v>14</v>
@@ -8560,7 +9199,7 @@
         <v>14</v>
       </c>
       <c r="H231" t="s" s="2">
-        <v>30</v>
+        <v>36</v>
       </c>
       <c r="I231" t="s" s="2">
         <v>18</v>
@@ -8577,7 +9216,7 @@
         <v>14</v>
       </c>
       <c r="B232" t="s" s="2">
-        <v>81</v>
+        <v>266</v>
       </c>
       <c r="C232" t="s" s="2">
         <v>14</v>
@@ -8586,7 +9225,7 @@
         <v>14</v>
       </c>
       <c r="E232" t="s" s="2">
-        <v>84</v>
+        <v>276</v>
       </c>
       <c r="F232" t="s" s="2">
         <v>14</v>
@@ -8595,7 +9234,7 @@
         <v>14</v>
       </c>
       <c r="H232" t="s" s="2">
-        <v>30</v>
+        <v>36</v>
       </c>
       <c r="I232" t="s" s="2">
         <v>18</v>
@@ -8612,7 +9251,7 @@
         <v>14</v>
       </c>
       <c r="B233" t="s" s="2">
-        <v>81</v>
+        <v>266</v>
       </c>
       <c r="C233" t="s" s="2">
         <v>14</v>
@@ -8621,7 +9260,7 @@
         <v>14</v>
       </c>
       <c r="E233" t="s" s="2">
-        <v>85</v>
+        <v>39</v>
       </c>
       <c r="F233" t="s" s="2">
         <v>14</v>
@@ -8630,7 +9269,7 @@
         <v>14</v>
       </c>
       <c r="H233" t="s" s="2">
-        <v>30</v>
+        <v>36</v>
       </c>
       <c r="I233" t="s" s="2">
         <v>18</v>
@@ -8647,7 +9286,7 @@
         <v>14</v>
       </c>
       <c r="B234" t="s" s="2">
-        <v>81</v>
+        <v>266</v>
       </c>
       <c r="C234" t="s" s="2">
         <v>14</v>
@@ -8656,7 +9295,7 @@
         <v>14</v>
       </c>
       <c r="E234" t="s" s="2">
-        <v>86</v>
+        <v>234</v>
       </c>
       <c r="F234" t="s" s="2">
         <v>14</v>
@@ -8665,7 +9304,7 @@
         <v>14</v>
       </c>
       <c r="H234" t="s" s="2">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="I234" t="s" s="2">
         <v>18</v>
@@ -8682,7 +9321,7 @@
         <v>14</v>
       </c>
       <c r="B235" t="s" s="2">
-        <v>81</v>
+        <v>266</v>
       </c>
       <c r="C235" t="s" s="2">
         <v>14</v>
@@ -8691,7 +9330,7 @@
         <v>14</v>
       </c>
       <c r="E235" t="s" s="2">
-        <v>87</v>
+        <v>233</v>
       </c>
       <c r="F235" t="s" s="2">
         <v>14</v>
@@ -8700,7 +9339,7 @@
         <v>14</v>
       </c>
       <c r="H235" t="s" s="2">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="I235" t="s" s="2">
         <v>18</v>
@@ -8717,7 +9356,7 @@
         <v>14</v>
       </c>
       <c r="B236" t="s" s="2">
-        <v>81</v>
+        <v>266</v>
       </c>
       <c r="C236" t="s" s="2">
         <v>14</v>
@@ -8726,7 +9365,7 @@
         <v>14</v>
       </c>
       <c r="E236" t="s" s="2">
-        <v>88</v>
+        <v>277</v>
       </c>
       <c r="F236" t="s" s="2">
         <v>14</v>
@@ -8735,7 +9374,7 @@
         <v>14</v>
       </c>
       <c r="H236" t="s" s="2">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="I236" t="s" s="2">
         <v>18</v>
@@ -8752,7 +9391,7 @@
         <v>14</v>
       </c>
       <c r="B237" t="s" s="2">
-        <v>81</v>
+        <v>266</v>
       </c>
       <c r="C237" t="s" s="2">
         <v>14</v>
@@ -8761,7 +9400,7 @@
         <v>14</v>
       </c>
       <c r="E237" t="s" s="2">
-        <v>89</v>
+        <v>278</v>
       </c>
       <c r="F237" t="s" s="2">
         <v>14</v>
@@ -8770,7 +9409,7 @@
         <v>14</v>
       </c>
       <c r="H237" t="s" s="2">
-        <v>30</v>
+        <v>36</v>
       </c>
       <c r="I237" t="s" s="2">
         <v>18</v>
@@ -8787,7 +9426,7 @@
         <v>14</v>
       </c>
       <c r="B238" t="s" s="2">
-        <v>81</v>
+        <v>266</v>
       </c>
       <c r="C238" t="s" s="2">
         <v>14</v>
@@ -8796,7 +9435,7 @@
         <v>14</v>
       </c>
       <c r="E238" t="s" s="2">
-        <v>90</v>
+        <v>279</v>
       </c>
       <c r="F238" t="s" s="2">
         <v>14</v>
@@ -8805,7 +9444,7 @@
         <v>14</v>
       </c>
       <c r="H238" t="s" s="2">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="I238" t="s" s="2">
         <v>18</v>
@@ -8822,7 +9461,7 @@
         <v>14</v>
       </c>
       <c r="B239" t="s" s="2">
-        <v>81</v>
+        <v>266</v>
       </c>
       <c r="C239" t="s" s="2">
         <v>14</v>
@@ -8831,7 +9470,7 @@
         <v>14</v>
       </c>
       <c r="E239" t="s" s="2">
-        <v>91</v>
+        <v>280</v>
       </c>
       <c r="F239" t="s" s="2">
         <v>14</v>
@@ -8840,7 +9479,7 @@
         <v>14</v>
       </c>
       <c r="H239" t="s" s="2">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="I239" t="s" s="2">
         <v>18</v>
@@ -8854,28 +9493,28 @@
     </row>
     <row r="240">
       <c r="A240" t="s" s="2">
-        <v>92</v>
+        <v>14</v>
       </c>
       <c r="B240" t="s" s="2">
-        <v>93</v>
+        <v>266</v>
       </c>
       <c r="C240" t="s" s="2">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="D240" t="s" s="2">
         <v>14</v>
       </c>
       <c r="E240" t="s" s="2">
-        <v>94</v>
+        <v>281</v>
       </c>
       <c r="F240" t="s" s="2">
         <v>14</v>
       </c>
       <c r="G240" t="s" s="2">
-        <v>21</v>
+        <v>14</v>
       </c>
       <c r="H240" t="s" s="2">
-        <v>95</v>
+        <v>36</v>
       </c>
       <c r="I240" t="s" s="2">
         <v>18</v>
@@ -8889,28 +9528,28 @@
     </row>
     <row r="241">
       <c r="A241" t="s" s="2">
-        <v>14</v>
+        <v>282</v>
       </c>
       <c r="B241" t="s" s="2">
-        <v>93</v>
+        <v>283</v>
       </c>
       <c r="C241" t="s" s="2">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="D241" t="s" s="2">
         <v>14</v>
       </c>
       <c r="E241" t="s" s="2">
-        <v>14</v>
+        <v>284</v>
       </c>
       <c r="F241" t="s" s="2">
         <v>14</v>
       </c>
       <c r="G241" t="s" s="2">
-        <v>14</v>
+        <v>22</v>
       </c>
       <c r="H241" t="s" s="2">
-        <v>30</v>
+        <v>34</v>
       </c>
       <c r="I241" t="s" s="2">
         <v>18</v>
@@ -8927,7 +9566,7 @@
         <v>14</v>
       </c>
       <c r="B242" t="s" s="2">
-        <v>93</v>
+        <v>283</v>
       </c>
       <c r="C242" t="s" s="2">
         <v>14</v>
@@ -8936,7 +9575,7 @@
         <v>14</v>
       </c>
       <c r="E242" t="s" s="2">
-        <v>14</v>
+        <v>285</v>
       </c>
       <c r="F242" t="s" s="2">
         <v>14</v>
@@ -8945,7 +9584,7 @@
         <v>14</v>
       </c>
       <c r="H242" t="s" s="2">
-        <v>26</v>
+        <v>29</v>
       </c>
       <c r="I242" t="s" s="2">
         <v>18</v>
@@ -8962,7 +9601,7 @@
         <v>14</v>
       </c>
       <c r="B243" t="s" s="2">
-        <v>93</v>
+        <v>283</v>
       </c>
       <c r="C243" t="s" s="2">
         <v>14</v>
@@ -8971,7 +9610,7 @@
         <v>14</v>
       </c>
       <c r="E243" t="s" s="2">
-        <v>96</v>
+        <v>286</v>
       </c>
       <c r="F243" t="s" s="2">
         <v>14</v>
@@ -8980,7 +9619,7 @@
         <v>14</v>
       </c>
       <c r="H243" t="s" s="2">
-        <v>26</v>
+        <v>29</v>
       </c>
       <c r="I243" t="s" s="2">
         <v>18</v>
@@ -8997,7 +9636,7 @@
         <v>14</v>
       </c>
       <c r="B244" t="s" s="2">
-        <v>93</v>
+        <v>283</v>
       </c>
       <c r="C244" t="s" s="2">
         <v>14</v>
@@ -9006,7 +9645,7 @@
         <v>14</v>
       </c>
       <c r="E244" t="s" s="2">
-        <v>14</v>
+        <v>287</v>
       </c>
       <c r="F244" t="s" s="2">
         <v>14</v>
@@ -9015,7 +9654,7 @@
         <v>14</v>
       </c>
       <c r="H244" t="s" s="2">
-        <v>26</v>
+        <v>36</v>
       </c>
       <c r="I244" t="s" s="2">
         <v>18</v>
@@ -9032,7 +9671,7 @@
         <v>14</v>
       </c>
       <c r="B245" t="s" s="2">
-        <v>93</v>
+        <v>283</v>
       </c>
       <c r="C245" t="s" s="2">
         <v>14</v>
@@ -9041,7 +9680,7 @@
         <v>14</v>
       </c>
       <c r="E245" t="s" s="2">
-        <v>14</v>
+        <v>288</v>
       </c>
       <c r="F245" t="s" s="2">
         <v>14</v>
@@ -9050,7 +9689,7 @@
         <v>14</v>
       </c>
       <c r="H245" t="s" s="2">
-        <v>97</v>
+        <v>36</v>
       </c>
       <c r="I245" t="s" s="2">
         <v>18</v>
@@ -9064,28 +9703,28 @@
     </row>
     <row r="246">
       <c r="A246" t="s" s="2">
-        <v>98</v>
+        <v>14</v>
       </c>
       <c r="B246" t="s" s="2">
-        <v>99</v>
+        <v>283</v>
       </c>
       <c r="C246" t="s" s="2">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="D246" t="s" s="2">
         <v>14</v>
       </c>
       <c r="E246" t="s" s="2">
-        <v>87</v>
+        <v>289</v>
       </c>
       <c r="F246" t="s" s="2">
         <v>14</v>
       </c>
       <c r="G246" t="s" s="2">
-        <v>21</v>
+        <v>14</v>
       </c>
       <c r="H246" t="s" s="2">
-        <v>22</v>
+        <v>36</v>
       </c>
       <c r="I246" t="s" s="2">
         <v>18</v>
@@ -9099,28 +9738,28 @@
     </row>
     <row r="247">
       <c r="A247" t="s" s="2">
-        <v>100</v>
+        <v>14</v>
       </c>
       <c r="B247" t="s" s="2">
-        <v>101</v>
+        <v>283</v>
       </c>
       <c r="C247" t="s" s="2">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="D247" t="s" s="2">
         <v>14</v>
       </c>
       <c r="E247" t="s" s="2">
-        <v>14</v>
+        <v>290</v>
       </c>
       <c r="F247" t="s" s="2">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="G247" t="s" s="2">
-        <v>16</v>
+        <v>14</v>
       </c>
       <c r="H247" t="s" s="2">
-        <v>14</v>
+        <v>36</v>
       </c>
       <c r="I247" t="s" s="2">
         <v>18</v>
@@ -9137,7 +9776,7 @@
         <v>14</v>
       </c>
       <c r="B248" t="s" s="2">
-        <v>101</v>
+        <v>283</v>
       </c>
       <c r="C248" t="s" s="2">
         <v>14</v>
@@ -9146,7 +9785,7 @@
         <v>14</v>
       </c>
       <c r="E248" t="s" s="2">
-        <v>14</v>
+        <v>133</v>
       </c>
       <c r="F248" t="s" s="2">
         <v>14</v>
@@ -9155,7 +9794,7 @@
         <v>14</v>
       </c>
       <c r="H248" t="s" s="2">
-        <v>26</v>
+        <v>36</v>
       </c>
       <c r="I248" t="s" s="2">
         <v>18</v>
@@ -9172,7 +9811,7 @@
         <v>14</v>
       </c>
       <c r="B249" t="s" s="2">
-        <v>101</v>
+        <v>283</v>
       </c>
       <c r="C249" t="s" s="2">
         <v>14</v>
@@ -9181,7 +9820,7 @@
         <v>14</v>
       </c>
       <c r="E249" t="s" s="2">
-        <v>14</v>
+        <v>291</v>
       </c>
       <c r="F249" t="s" s="2">
         <v>14</v>
@@ -9190,7 +9829,7 @@
         <v>14</v>
       </c>
       <c r="H249" t="s" s="2">
-        <v>26</v>
+        <v>36</v>
       </c>
       <c r="I249" t="s" s="2">
         <v>18</v>
@@ -9204,28 +9843,28 @@
     </row>
     <row r="250">
       <c r="A250" t="s" s="2">
-        <v>102</v>
+        <v>14</v>
       </c>
       <c r="B250" t="s" s="2">
-        <v>103</v>
+        <v>283</v>
       </c>
       <c r="C250" t="s" s="2">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="D250" t="s" s="2">
         <v>14</v>
       </c>
       <c r="E250" t="s" s="2">
-        <v>14</v>
+        <v>292</v>
       </c>
       <c r="F250" t="s" s="2">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="G250" t="s" s="2">
-        <v>16</v>
+        <v>14</v>
       </c>
       <c r="H250" t="s" s="2">
-        <v>14</v>
+        <v>36</v>
       </c>
       <c r="I250" t="s" s="2">
         <v>18</v>
@@ -9242,7 +9881,7 @@
         <v>14</v>
       </c>
       <c r="B251" t="s" s="2">
-        <v>103</v>
+        <v>283</v>
       </c>
       <c r="C251" t="s" s="2">
         <v>14</v>
@@ -9251,7 +9890,7 @@
         <v>14</v>
       </c>
       <c r="E251" t="s" s="2">
-        <v>14</v>
+        <v>293</v>
       </c>
       <c r="F251" t="s" s="2">
         <v>14</v>
@@ -9260,7 +9899,7 @@
         <v>14</v>
       </c>
       <c r="H251" t="s" s="2">
-        <v>26</v>
+        <v>36</v>
       </c>
       <c r="I251" t="s" s="2">
         <v>18</v>
@@ -9277,7 +9916,7 @@
         <v>14</v>
       </c>
       <c r="B252" t="s" s="2">
-        <v>103</v>
+        <v>283</v>
       </c>
       <c r="C252" t="s" s="2">
         <v>14</v>
@@ -9286,7 +9925,7 @@
         <v>14</v>
       </c>
       <c r="E252" t="s" s="2">
-        <v>14</v>
+        <v>294</v>
       </c>
       <c r="F252" t="s" s="2">
         <v>14</v>
@@ -9295,7 +9934,7 @@
         <v>14</v>
       </c>
       <c r="H252" t="s" s="2">
-        <v>26</v>
+        <v>36</v>
       </c>
       <c r="I252" t="s" s="2">
         <v>18</v>
@@ -9309,10 +9948,10 @@
     </row>
     <row r="253">
       <c r="A253" t="s" s="2">
-        <v>104</v>
+        <v>295</v>
       </c>
       <c r="B253" t="s" s="2">
-        <v>105</v>
+        <v>296</v>
       </c>
       <c r="C253" t="s" s="2">
         <v>13</v>
@@ -9321,16 +9960,16 @@
         <v>14</v>
       </c>
       <c r="E253" t="s" s="2">
-        <v>14</v>
+        <v>297</v>
       </c>
       <c r="F253" t="s" s="2">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="G253" t="s" s="2">
-        <v>16</v>
+        <v>22</v>
       </c>
       <c r="H253" t="s" s="2">
-        <v>55</v>
+        <v>298</v>
       </c>
       <c r="I253" t="s" s="2">
         <v>18</v>
@@ -9347,7 +9986,7 @@
         <v>14</v>
       </c>
       <c r="B254" t="s" s="2">
-        <v>105</v>
+        <v>296</v>
       </c>
       <c r="C254" t="s" s="2">
         <v>14</v>
@@ -9356,7 +9995,7 @@
         <v>14</v>
       </c>
       <c r="E254" t="s" s="2">
-        <v>14</v>
+        <v>299</v>
       </c>
       <c r="F254" t="s" s="2">
         <v>14</v>
@@ -9365,7 +10004,7 @@
         <v>14</v>
       </c>
       <c r="H254" t="s" s="2">
-        <v>26</v>
+        <v>36</v>
       </c>
       <c r="I254" t="s" s="2">
         <v>18</v>
@@ -9379,28 +10018,28 @@
     </row>
     <row r="255">
       <c r="A255" t="s" s="2">
-        <v>106</v>
+        <v>14</v>
       </c>
       <c r="B255" t="s" s="2">
-        <v>107</v>
+        <v>296</v>
       </c>
       <c r="C255" t="s" s="2">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="D255" t="s" s="2">
         <v>14</v>
       </c>
       <c r="E255" t="s" s="2">
-        <v>14</v>
+        <v>28</v>
       </c>
       <c r="F255" t="s" s="2">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="G255" t="s" s="2">
-        <v>21</v>
+        <v>14</v>
       </c>
       <c r="H255" t="s" s="2">
-        <v>14</v>
+        <v>29</v>
       </c>
       <c r="I255" t="s" s="2">
         <v>18</v>
@@ -9414,28 +10053,28 @@
     </row>
     <row r="256">
       <c r="A256" t="s" s="2">
-        <v>108</v>
+        <v>14</v>
       </c>
       <c r="B256" t="s" s="2">
-        <v>109</v>
+        <v>296</v>
       </c>
       <c r="C256" t="s" s="2">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="D256" t="s" s="2">
         <v>14</v>
       </c>
       <c r="E256" t="s" s="2">
-        <v>14</v>
+        <v>300</v>
       </c>
       <c r="F256" t="s" s="2">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="G256" t="s" s="2">
-        <v>110</v>
+        <v>14</v>
       </c>
       <c r="H256" t="s" s="2">
-        <v>14</v>
+        <v>29</v>
       </c>
       <c r="I256" t="s" s="2">
         <v>18</v>
@@ -9449,28 +10088,28 @@
     </row>
     <row r="257">
       <c r="A257" t="s" s="2">
-        <v>111</v>
+        <v>14</v>
       </c>
       <c r="B257" t="s" s="2">
-        <v>112</v>
+        <v>296</v>
       </c>
       <c r="C257" t="s" s="2">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="D257" t="s" s="2">
         <v>14</v>
       </c>
       <c r="E257" t="s" s="2">
-        <v>14</v>
+        <v>301</v>
       </c>
       <c r="F257" t="s" s="2">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="G257" t="s" s="2">
-        <v>16</v>
+        <v>14</v>
       </c>
       <c r="H257" t="s" s="2">
-        <v>14</v>
+        <v>29</v>
       </c>
       <c r="I257" t="s" s="2">
         <v>18</v>
@@ -9487,7 +10126,7 @@
         <v>14</v>
       </c>
       <c r="B258" t="s" s="2">
-        <v>112</v>
+        <v>296</v>
       </c>
       <c r="C258" t="s" s="2">
         <v>14</v>
@@ -9496,7 +10135,7 @@
         <v>14</v>
       </c>
       <c r="E258" t="s" s="2">
-        <v>14</v>
+        <v>302</v>
       </c>
       <c r="F258" t="s" s="2">
         <v>14</v>
@@ -9505,7 +10144,7 @@
         <v>14</v>
       </c>
       <c r="H258" t="s" s="2">
-        <v>26</v>
+        <v>303</v>
       </c>
       <c r="I258" t="s" s="2">
         <v>18</v>
@@ -9514,6 +10153,496 @@
         <v>14</v>
       </c>
       <c r="K258" t="s" s="2">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="259">
+      <c r="A259" t="s" s="2">
+        <v>304</v>
+      </c>
+      <c r="B259" t="s" s="2">
+        <v>305</v>
+      </c>
+      <c r="C259" t="s" s="2">
+        <v>13</v>
+      </c>
+      <c r="D259" t="s" s="2">
+        <v>14</v>
+      </c>
+      <c r="E259" t="s" s="2">
+        <v>133</v>
+      </c>
+      <c r="F259" t="s" s="2">
+        <v>14</v>
+      </c>
+      <c r="G259" t="s" s="2">
+        <v>22</v>
+      </c>
+      <c r="H259" t="s" s="2">
+        <v>23</v>
+      </c>
+      <c r="I259" t="s" s="2">
+        <v>18</v>
+      </c>
+      <c r="J259" t="s" s="2">
+        <v>14</v>
+      </c>
+      <c r="K259" t="s" s="2">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="260">
+      <c r="A260" t="s" s="2">
+        <v>306</v>
+      </c>
+      <c r="B260" t="s" s="2">
+        <v>307</v>
+      </c>
+      <c r="C260" t="s" s="2">
+        <v>13</v>
+      </c>
+      <c r="D260" t="s" s="2">
+        <v>14</v>
+      </c>
+      <c r="E260" t="s" s="2">
+        <v>308</v>
+      </c>
+      <c r="F260" t="s" s="2">
+        <v>14</v>
+      </c>
+      <c r="G260" t="s" s="2">
+        <v>16</v>
+      </c>
+      <c r="H260" t="s" s="2">
+        <v>14</v>
+      </c>
+      <c r="I260" t="s" s="2">
+        <v>18</v>
+      </c>
+      <c r="J260" t="s" s="2">
+        <v>14</v>
+      </c>
+      <c r="K260" t="s" s="2">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="261">
+      <c r="A261" t="s" s="2">
+        <v>14</v>
+      </c>
+      <c r="B261" t="s" s="2">
+        <v>307</v>
+      </c>
+      <c r="C261" t="s" s="2">
+        <v>14</v>
+      </c>
+      <c r="D261" t="s" s="2">
+        <v>14</v>
+      </c>
+      <c r="E261" t="s" s="2">
+        <v>30</v>
+      </c>
+      <c r="F261" t="s" s="2">
+        <v>14</v>
+      </c>
+      <c r="G261" t="s" s="2">
+        <v>14</v>
+      </c>
+      <c r="H261" t="s" s="2">
+        <v>29</v>
+      </c>
+      <c r="I261" t="s" s="2">
+        <v>18</v>
+      </c>
+      <c r="J261" t="s" s="2">
+        <v>14</v>
+      </c>
+      <c r="K261" t="s" s="2">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="262">
+      <c r="A262" t="s" s="2">
+        <v>14</v>
+      </c>
+      <c r="B262" t="s" s="2">
+        <v>307</v>
+      </c>
+      <c r="C262" t="s" s="2">
+        <v>14</v>
+      </c>
+      <c r="D262" t="s" s="2">
+        <v>14</v>
+      </c>
+      <c r="E262" t="s" s="2">
+        <v>28</v>
+      </c>
+      <c r="F262" t="s" s="2">
+        <v>14</v>
+      </c>
+      <c r="G262" t="s" s="2">
+        <v>14</v>
+      </c>
+      <c r="H262" t="s" s="2">
+        <v>29</v>
+      </c>
+      <c r="I262" t="s" s="2">
+        <v>18</v>
+      </c>
+      <c r="J262" t="s" s="2">
+        <v>14</v>
+      </c>
+      <c r="K262" t="s" s="2">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="263">
+      <c r="A263" t="s" s="2">
+        <v>309</v>
+      </c>
+      <c r="B263" t="s" s="2">
+        <v>310</v>
+      </c>
+      <c r="C263" t="s" s="2">
+        <v>13</v>
+      </c>
+      <c r="D263" t="s" s="2">
+        <v>14</v>
+      </c>
+      <c r="E263" t="s" s="2">
+        <v>311</v>
+      </c>
+      <c r="F263" t="s" s="2">
+        <v>14</v>
+      </c>
+      <c r="G263" t="s" s="2">
+        <v>16</v>
+      </c>
+      <c r="H263" t="s" s="2">
+        <v>14</v>
+      </c>
+      <c r="I263" t="s" s="2">
+        <v>18</v>
+      </c>
+      <c r="J263" t="s" s="2">
+        <v>14</v>
+      </c>
+      <c r="K263" t="s" s="2">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="264">
+      <c r="A264" t="s" s="2">
+        <v>14</v>
+      </c>
+      <c r="B264" t="s" s="2">
+        <v>310</v>
+      </c>
+      <c r="C264" t="s" s="2">
+        <v>14</v>
+      </c>
+      <c r="D264" t="s" s="2">
+        <v>14</v>
+      </c>
+      <c r="E264" t="s" s="2">
+        <v>30</v>
+      </c>
+      <c r="F264" t="s" s="2">
+        <v>14</v>
+      </c>
+      <c r="G264" t="s" s="2">
+        <v>14</v>
+      </c>
+      <c r="H264" t="s" s="2">
+        <v>29</v>
+      </c>
+      <c r="I264" t="s" s="2">
+        <v>18</v>
+      </c>
+      <c r="J264" t="s" s="2">
+        <v>14</v>
+      </c>
+      <c r="K264" t="s" s="2">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="265">
+      <c r="A265" t="s" s="2">
+        <v>14</v>
+      </c>
+      <c r="B265" t="s" s="2">
+        <v>310</v>
+      </c>
+      <c r="C265" t="s" s="2">
+        <v>14</v>
+      </c>
+      <c r="D265" t="s" s="2">
+        <v>14</v>
+      </c>
+      <c r="E265" t="s" s="2">
+        <v>28</v>
+      </c>
+      <c r="F265" t="s" s="2">
+        <v>14</v>
+      </c>
+      <c r="G265" t="s" s="2">
+        <v>14</v>
+      </c>
+      <c r="H265" t="s" s="2">
+        <v>29</v>
+      </c>
+      <c r="I265" t="s" s="2">
+        <v>18</v>
+      </c>
+      <c r="J265" t="s" s="2">
+        <v>14</v>
+      </c>
+      <c r="K265" t="s" s="2">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="266">
+      <c r="A266" t="s" s="2">
+        <v>312</v>
+      </c>
+      <c r="B266" t="s" s="2">
+        <v>313</v>
+      </c>
+      <c r="C266" t="s" s="2">
+        <v>13</v>
+      </c>
+      <c r="D266" t="s" s="2">
+        <v>14</v>
+      </c>
+      <c r="E266" t="s" s="2">
+        <v>314</v>
+      </c>
+      <c r="F266" t="s" s="2">
+        <v>14</v>
+      </c>
+      <c r="G266" t="s" s="2">
+        <v>16</v>
+      </c>
+      <c r="H266" t="s" s="2">
+        <v>180</v>
+      </c>
+      <c r="I266" t="s" s="2">
+        <v>18</v>
+      </c>
+      <c r="J266" t="s" s="2">
+        <v>14</v>
+      </c>
+      <c r="K266" t="s" s="2">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="267">
+      <c r="A267" t="s" s="2">
+        <v>14</v>
+      </c>
+      <c r="B267" t="s" s="2">
+        <v>313</v>
+      </c>
+      <c r="C267" t="s" s="2">
+        <v>14</v>
+      </c>
+      <c r="D267" t="s" s="2">
+        <v>14</v>
+      </c>
+      <c r="E267" t="s" s="2">
+        <v>315</v>
+      </c>
+      <c r="F267" t="s" s="2">
+        <v>14</v>
+      </c>
+      <c r="G267" t="s" s="2">
+        <v>14</v>
+      </c>
+      <c r="H267" t="s" s="2">
+        <v>29</v>
+      </c>
+      <c r="I267" t="s" s="2">
+        <v>18</v>
+      </c>
+      <c r="J267" t="s" s="2">
+        <v>14</v>
+      </c>
+      <c r="K267" t="s" s="2">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="268">
+      <c r="A268" t="s" s="2">
+        <v>316</v>
+      </c>
+      <c r="B268" t="s" s="2">
+        <v>317</v>
+      </c>
+      <c r="C268" t="s" s="2">
+        <v>13</v>
+      </c>
+      <c r="D268" t="s" s="2">
+        <v>14</v>
+      </c>
+      <c r="E268" t="s" s="2">
+        <v>318</v>
+      </c>
+      <c r="F268" t="s" s="2">
+        <v>14</v>
+      </c>
+      <c r="G268" t="s" s="2">
+        <v>22</v>
+      </c>
+      <c r="H268" t="s" s="2">
+        <v>14</v>
+      </c>
+      <c r="I268" t="s" s="2">
+        <v>18</v>
+      </c>
+      <c r="J268" t="s" s="2">
+        <v>14</v>
+      </c>
+      <c r="K268" t="s" s="2">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="269">
+      <c r="A269" t="s" s="2">
+        <v>319</v>
+      </c>
+      <c r="B269" t="s" s="2">
+        <v>320</v>
+      </c>
+      <c r="C269" t="s" s="2">
+        <v>13</v>
+      </c>
+      <c r="D269" t="s" s="2">
+        <v>14</v>
+      </c>
+      <c r="E269" t="s" s="2">
+        <v>321</v>
+      </c>
+      <c r="F269" t="s" s="2">
+        <v>14</v>
+      </c>
+      <c r="G269" t="s" s="2">
+        <v>322</v>
+      </c>
+      <c r="H269" t="s" s="2">
+        <v>14</v>
+      </c>
+      <c r="I269" t="s" s="2">
+        <v>18</v>
+      </c>
+      <c r="J269" t="s" s="2">
+        <v>14</v>
+      </c>
+      <c r="K269" t="s" s="2">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="270">
+      <c r="A270" t="s" s="2">
+        <v>323</v>
+      </c>
+      <c r="B270" t="s" s="2">
+        <v>324</v>
+      </c>
+      <c r="C270" t="s" s="2">
+        <v>13</v>
+      </c>
+      <c r="D270" t="s" s="2">
+        <v>14</v>
+      </c>
+      <c r="E270" t="s" s="2">
+        <v>325</v>
+      </c>
+      <c r="F270" t="s" s="2">
+        <v>14</v>
+      </c>
+      <c r="G270" t="s" s="2">
+        <v>16</v>
+      </c>
+      <c r="H270" t="s" s="2">
+        <v>14</v>
+      </c>
+      <c r="I270" t="s" s="2">
+        <v>18</v>
+      </c>
+      <c r="J270" t="s" s="2">
+        <v>14</v>
+      </c>
+      <c r="K270" t="s" s="2">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="271">
+      <c r="A271" t="s" s="2">
+        <v>14</v>
+      </c>
+      <c r="B271" t="s" s="2">
+        <v>324</v>
+      </c>
+      <c r="C271" t="s" s="2">
+        <v>14</v>
+      </c>
+      <c r="D271" t="s" s="2">
+        <v>14</v>
+      </c>
+      <c r="E271" t="s" s="2">
+        <v>30</v>
+      </c>
+      <c r="F271" t="s" s="2">
+        <v>14</v>
+      </c>
+      <c r="G271" t="s" s="2">
+        <v>14</v>
+      </c>
+      <c r="H271" t="s" s="2">
+        <v>29</v>
+      </c>
+      <c r="I271" t="s" s="2">
+        <v>18</v>
+      </c>
+      <c r="J271" t="s" s="2">
+        <v>14</v>
+      </c>
+      <c r="K271" t="s" s="2">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="272">
+      <c r="A272" t="s" s="2">
+        <v>14</v>
+      </c>
+      <c r="B272" t="s" s="2">
+        <v>324</v>
+      </c>
+      <c r="C272" t="s" s="2">
+        <v>14</v>
+      </c>
+      <c r="D272" t="s" s="2">
+        <v>14</v>
+      </c>
+      <c r="E272" t="s" s="2">
+        <v>28</v>
+      </c>
+      <c r="F272" t="s" s="2">
+        <v>14</v>
+      </c>
+      <c r="G272" t="s" s="2">
+        <v>14</v>
+      </c>
+      <c r="H272" t="s" s="2">
+        <v>29</v>
+      </c>
+      <c r="I272" t="s" s="2">
+        <v>18</v>
+      </c>
+      <c r="J272" t="s" s="2">
+        <v>14</v>
+      </c>
+      <c r="K272" t="s" s="2">
         <v>14</v>
       </c>
     </row>
